--- a/assignments/sorting/remarks_sorting.xlsx
+++ b/assignments/sorting/remarks_sorting.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UNIVERSITY\2026 - 2027\WebResearch\assignments\sorting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{E95B3E3E-9FB6-43A4-A7CA-DB7309FC5DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBD32582-263C-4A3A-95A3-803F88C21895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Remarks" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,20 @@
     <author>sim_check</author>
   </authors>
   <commentList>
+    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
@@ -180,6 +194,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
         <r>
@@ -726,6 +754,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000035000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000036000000}">
       <text>
         <r>
@@ -810,6 +852,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003D000000}">
       <text>
         <r>
@@ -964,6 +1020,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000048000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000049000000}">
       <text>
         <r>
@@ -1202,6 +1272,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00005A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00005B000000}">
       <text>
         <r>
@@ -1286,6 +1370,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D45" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000061000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E45" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000062000000}">
       <text>
         <r>
@@ -1454,6 +1552,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00006E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E47" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00006F000000}">
       <text>
         <r>
@@ -1608,6 +1720,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00007A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00007B000000}">
       <text>
         <r>
@@ -1759,6 +1885,20 @@
             <scheme val="minor"/>
           </rPr>
           <t>-bubbleSort (00:04:37), -( (00:04:38), -array (00:04:39), -) (00:04:40), -; (00:04:41), -100 (00:07:14), +let (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +startSort (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +startSort (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +await (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +speed (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bike (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +200 (00:00:00), +; (00:00:00), +const (00:00:00), +barWidth (00:00:00), += (00:00:00), +9 (00:00:00), +; (00:00:00), +bike (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +i (00:00:00), +* (00:00:00), +barWidth (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +bike (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +barHeight (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +speed (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000086000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found</t>
         </r>
       </text>
     </comment>
@@ -2016,6 +2156,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000099000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00009A000000}">
       <text>
         <r>
@@ -2086,6 +2240,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D66" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00009F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E66" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A0000000}">
       <text>
         <r>
@@ -2380,6 +2548,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D72" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B5000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E72" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B6000000}">
       <text>
         <r>
@@ -2464,6 +2646,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D73" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000BC000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E73" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000BD000000}">
       <text>
         <r>
@@ -2548,6 +2744,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D75" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C3000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E75" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C4000000}">
       <text>
         <r>
@@ -2982,6 +3192,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D86" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E3000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found, DOCX: cleared author metadata (document.docx)</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E86" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E4000000}">
       <text>
         <r>
@@ -3066,6 +3290,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D87" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000EA000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found, DOCX: cleared author metadata (document.docx)</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E87" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000EB000000}">
       <text>
         <r>
@@ -3150,6 +3388,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D88" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F1000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found, DOCX: cleared author metadata (answer.docx), DOCX: cleared author metadata (document.docx)</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E88" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F2000000}">
       <text>
         <r>
@@ -3174,7 +3426,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>-width (00:01:07), -: (00:01:08), -7px (00:01:09), -; (00:01:10), -height (00:01:11), -: (00:01:12), -100 (00:01:13), -% (00:01:14), -; (00:01:15), -background (00:01:16), -- (00:01:17), -color (00:01:18), -: (00:01:19), -black (00:01:20), -; (00:01:21), -100 (00:07:14), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Speed (00:00:00), +( (00:00:00), +delay (00:00:00), +ms (00:00:00), +) (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +200 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +50 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +" (00:00:00), +&gt; (00:00:00), +50 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +50 (00:00:00), +; (00:00:00), +const (00:00:00), +slider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedDisplay (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +slider (00:00:00), +. (00:00:00), +onchange (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedDisplay (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +highlightIndices (00:00:00), += (00:00:00), +[ (00:00:00), +] (00:00:00), +if (00:00:00), +( (00:00:00), +highlightIndices (00:00:00), +. (00:00:00), +includes (00:00:00), +( (00:00:00), +i (00:00:00), +) (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +comparing (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +remove (00:00:00), +( (00:00:00), +" (00:00:00), +comparing (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Sorting (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +" (00:00:00), +; (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +, (00:00:00), +i (00:00:00), +] (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Sorted (00:00:00), +! (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +Motorcycle (00:00:00), +incoming (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Done (00:00:00), +! (00:00:00), +" (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +container (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +visEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +containerWidth (00:00:00), += (00:00:00), +container (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), +; (00:00:00), +const (00:00:00), +barCount (00:00:00), += (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +barCount (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +barLeft (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), ++ (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +visTop (00:00:00), += (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetTop (00:00:00), +; (00:00:00), +const (00:00:00), +visHeight (00:00:00), += (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +barTopInContainer (00:00:00), += (00:00:00), +visTop (00:00:00), ++ (00:00:00), +( (00:00:00), +visHeight (00:00:00), +- (00:00:00), +barHeight (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motoTop (00:00:00), += (00:00:00), +barTopInContainer (00:00:00), +- (00:00:00), +36 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +( (00:00:00), +barLeft (00:00:00), +- (00:00:00), +10 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +motoTop (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +Math (00:00:00), +. (00:00:00), +max (00:00:00), +( (00:00:00), +10 (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +* (00:00:00), +0 (00:00:00), +. (00:00:00), +5 (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +( (00:00:00), +containerWidth (00:00:00), ++ (00:00:00), +50 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +300 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +" (00:00:00), +- (00:00:00), +40px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +" (00:00:00), +0px (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +1a1a2e (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +eee (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +} (00:00:00), +h1 (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +e0e0ff (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +12px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +label (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +aaa (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +{ (00:00:00), +accent (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +150px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +600px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +220px (00:00:00), +; (00:00:00), +} (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +16213e (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +10px (00:00:00), +8px (00:00:00), +0 (00:00:00), +8px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +, (00:00:00), +# (00:00:00), +a29bfe (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +0 (00:00:00), +0 (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +height (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +. (00:00:00), +comparing (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +fd79a8 (00:00:00), +, (00:00:00), +# (00:00:00), +e84393 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +28px (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +40px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +drop (00:00:00), +- (00:00:00), +shadow (00:00:00), +( (00:00:00), +0 (00:00:00), +0 (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +108 (00:00:00), +, (00:00:00), +99 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +8 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +; (00:00:00), +z (00:00:00), +- (00:00:00), +index (00:00:00), +: (00:00:00), +10 (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +status (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +13px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +888 (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-width (00:01:07), -: (00:01:08), -7px (00:01:09), -; (00:01:10), -height (00:01:11), -: (00:01:12), -100 (00:01:13), -% (00:01:14), -; (00:01:15), -background (00:01:16), -- (00:01:17), -color (00:01:18), -: (00:01:19), -black (00:01:20), -; (00:01:21), -100 (00:07:14), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Speed (00:00:00), +( (00:00:00), +delay (00:00:00), +ms (00:00:00), +) (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +200 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +50 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +" (00:00:00), +&gt; (00:00:00), +50 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +50 (00:00:00), +; (00:00:00), +const (00:00:00), +slider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedDisplay (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +slider (00:00:00), +. (00:00:00), +onchange (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedDisplay (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +highlightIndices (00:00:00), += (00:00:00), +[ (00:00:00), +] (00:00:00), +if (00:00:00), +( (00:00:00), +highlightIndices (00:00:00), +. (00:00:00), +includes (00:00:00), +( (00:00:00), +i (00:00:00), +) (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +comparing (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +remove (00:00:00), +( (00:00:00), +" (00:00:00), +comparing (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Sorting (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +" (00:00:00), +; (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +, (00:00:00), +i (00:00:00), +] (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Sorted (00:00:00), +! (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +Motorcycle (00:00:00), +incoming (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Done (00:00:00), +! (00:00:00), +" (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +container (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +visEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +containerWidth (00:00:00), += (00:00:00), +container (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), +; (00:00:00), +const (00:00:00), +barCount (00:00:00), += (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +barCount (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +barLeft (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), ++ (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +visTop (00:00:00), += (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetTop (00:00:00), +; (00:00:00), +const (00:00:00), +visHeight (00:00:00), += (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +barTopInContainer (00:00:00), += (00:00:00), +visTop (00:00:00), ++ (00:00:00), +( (00:00:00), +visHeight (00:00:00), +- (00:00:00), +barHeight (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motoTop (00:00:00), += (00:00:00), +barTopInContainer (00:00:00), +- (00:00:00), +36 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +( (00:00:00), +barLeft (00:00:00), +- (00:00:00), +10 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +motoTop (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +Math (00:00:00), +. (00:00:00), +max (00:00:00), +( (00:00:00), +10 (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +* (00:00:00), +0 (00:00:00), +. (00:00:00), +5 (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +( (00:00:00), +containerWidth (00:00:00), ++ (00:00:00), +50 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +300 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +" (00:00:00), +- (00:00:00), +40px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +" (00:00:00), +0px (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +1a1a2e (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +eee (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +h1 (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +e0e0ff (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +12px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +label (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +aaa (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +{ (00:00:00), +accent (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +150px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +600px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +220px (00:00:00), +; (00:00:00), +} (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +16213e (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +10px (00:00:00), +8px (00:00:00), +0 (00:00:00), +8px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +, (00:00:00), +# (00:00:00), +a29bfe (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +0 (00:00:00), +0 (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +height (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +. (00:00:00), +comparing (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +fd79a8 (00:00:00), +, (00:00:00), +# (00:00:00), +e84393 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +28px (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +40px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +drop (00:00:00), +- (00:00:00), +shadow (00:00:00), +( (00:00:00), +0 (00:00:00), +0 (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +108 (00:00:00), +, (00:00:00), +99 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +8 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +; (00:00:00), +z (00:00:00), +- (00:00:00), +index (00:00:00), +: (00:00:00), +10 (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +status (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +13px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +888 (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </r>
       </text>
     </comment>
@@ -3202,7 +3454,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>-width (00:01:07), -: (00:01:08), -7px (00:01:09), -; (00:01:10), -height (00:01:11), -: (00:01:12), -100 (00:01:13), -% (00:01:14), -; (00:01:15), -background (00:01:16), -- (00:01:17), -color (00:01:18), -: (00:01:19), -black (00:01:20), -; (00:01:21), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +1a1a2e (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +eee (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +} (00:00:00), +h1 (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +e0e0ff (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +12px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +label (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +aaa (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +{ (00:00:00), +accent (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +150px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +600px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +220px (00:00:00), +; (00:00:00), +} (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +16213e (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +10px (00:00:00), +8px (00:00:00), +0 (00:00:00), +8px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +, (00:00:00), +# (00:00:00), +a29bfe (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +0 (00:00:00), +0 (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +height (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +. (00:00:00), +comparing (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +fd79a8 (00:00:00), +, (00:00:00), +# (00:00:00), +e84393 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +28px (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +40px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +drop (00:00:00), +- (00:00:00), +shadow (00:00:00), +( (00:00:00), +0 (00:00:00), +0 (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +108 (00:00:00), +, (00:00:00), +99 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +8 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +; (00:00:00), +z (00:00:00), +- (00:00:00), +index (00:00:00), +: (00:00:00), +10 (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +status (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +13px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +888 (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-width (00:01:07), -: (00:01:08), -7px (00:01:09), -; (00:01:10), -height (00:01:11), -: (00:01:12), -100 (00:01:13), -% (00:01:14), -; (00:01:15), -background (00:01:16), -- (00:01:17), -color (00:01:18), -: (00:01:19), -black (00:01:20), -; (00:01:21), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +1a1a2e (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +eee (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +h1 (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +e0e0ff (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +12px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +label (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +aaa (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +{ (00:00:00), +accent (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +150px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +600px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +220px (00:00:00), +; (00:00:00), +} (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +16213e (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +10px (00:00:00), +8px (00:00:00), +0 (00:00:00), +8px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +, (00:00:00), +# (00:00:00), +a29bfe (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +0 (00:00:00), +0 (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +height (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +. (00:00:00), +comparing (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +fd79a8 (00:00:00), +, (00:00:00), +# (00:00:00), +e84393 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +28px (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +40px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +drop (00:00:00), +- (00:00:00), +shadow (00:00:00), +( (00:00:00), +0 (00:00:00), +0 (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +108 (00:00:00), +, (00:00:00), +99 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +8 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +; (00:00:00), +z (00:00:00), +- (00:00:00), +index (00:00:00), +: (00:00:00), +10 (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +status (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +13px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +888 (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </r>
       </text>
     </comment>
@@ -3234,6 +3486,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D89" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F8000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>No code files found in submission</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="H89" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F9000000}">
       <text>
         <r>
@@ -3244,7 +3510,21 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>-width (00:01:07), -: (00:01:08), -7px (00:01:09), -; (00:01:10), -height (00:01:11), -: (00:01:12), -100 (00:01:13), -% (00:01:14), -; (00:01:15), -background (00:01:16), -- (00:01:17), -color (00:01:18), -: (00:01:19), -black (00:01:20), -; (00:01:21), -100 (00:07:14), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Speed (00:00:00), +( (00:00:00), +delay (00:00:00), +ms (00:00:00), +) (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +200 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +50 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +" (00:00:00), +&gt; (00:00:00), +50 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +50 (00:00:00), +; (00:00:00), +const (00:00:00), +slider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedDisplay (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +slider (00:00:00), +. (00:00:00), +onchange (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedDisplay (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +highlightIndices (00:00:00), += (00:00:00), +[ (00:00:00), +] (00:00:00), +if (00:00:00), +( (00:00:00), +highlightIndices (00:00:00), +. (00:00:00), +includes (00:00:00), +( (00:00:00), +i (00:00:00), +) (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +comparing (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +remove (00:00:00), +( (00:00:00), +" (00:00:00), +comparing (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Sorting (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +" (00:00:00), +; (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +, (00:00:00), +i (00:00:00), +] (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Sorted (00:00:00), +! (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +Motorcycle (00:00:00), +incoming (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Done (00:00:00), +! (00:00:00), +" (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +container (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +visEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +containerWidth (00:00:00), += (00:00:00), +container (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), +; (00:00:00), +const (00:00:00), +barCount (00:00:00), += (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +barCount (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +barLeft (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), ++ (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +visTop (00:00:00), += (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetTop (00:00:00), +; (00:00:00), +const (00:00:00), +visHeight (00:00:00), += (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +barTopInContainer (00:00:00), += (00:00:00), +visTop (00:00:00), ++ (00:00:00), +( (00:00:00), +visHeight (00:00:00), +- (00:00:00), +barHeight (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motoTop (00:00:00), += (00:00:00), +barTopInContainer (00:00:00), +- (00:00:00), +36 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +( (00:00:00), +barLeft (00:00:00), +- (00:00:00), +10 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +motoTop (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +Math (00:00:00), +. (00:00:00), +max (00:00:00), +( (00:00:00), +10 (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +* (00:00:00), +0 (00:00:00), +. (00:00:00), +5 (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +( (00:00:00), +containerWidth (00:00:00), ++ (00:00:00), +50 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +300 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +" (00:00:00), +- (00:00:00), +40px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +" (00:00:00), +0px (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +1a1a2e (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +eee (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +} (00:00:00), +h1 (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +e0e0ff (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +12px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +label (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +aaa (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +{ (00:00:00), +accent (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +150px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +600px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +220px (00:00:00), +; (00:00:00), +} (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +16213e (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +10px (00:00:00), +8px (00:00:00), +0 (00:00:00), +8px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +, (00:00:00), +# (00:00:00), +a29bfe (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +0 (00:00:00), +0 (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +height (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +. (00:00:00), +comparing (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +fd79a8 (00:00:00), +, (00:00:00), +# (00:00:00), +e84393 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +28px (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +40px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +drop (00:00:00), +- (00:00:00), +shadow (00:00:00), +( (00:00:00), +0 (00:00:00), +0 (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +108 (00:00:00), +, (00:00:00), +99 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +8 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +; (00:00:00), +z (00:00:00), +- (00:00:00), +index (00:00:00), +: (00:00:00), +10 (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +status (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +13px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +888 (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-width (00:01:07), -: (00:01:08), -7px (00:01:09), -; (00:01:10), -height (00:01:11), -: (00:01:12), -100 (00:01:13), -% (00:01:14), -; (00:01:15), -background (00:01:16), -- (00:01:17), -color (00:01:18), -: (00:01:19), -black (00:01:20), -; (00:01:21), -100 (00:07:14), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Speed (00:00:00), +( (00:00:00), +delay (00:00:00), +ms (00:00:00), +) (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +200 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +50 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +" (00:00:00), +&gt; (00:00:00), +50 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +50 (00:00:00), +; (00:00:00), +const (00:00:00), +slider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedDisplay (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +slider (00:00:00), +. (00:00:00), +onchange (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedDisplay (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +highlightIndices (00:00:00), += (00:00:00), +[ (00:00:00), +] (00:00:00), +if (00:00:00), +( (00:00:00), +highlightIndices (00:00:00), +. (00:00:00), +includes (00:00:00), +( (00:00:00), +i (00:00:00), +) (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +comparing (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +remove (00:00:00), +( (00:00:00), +" (00:00:00), +comparing (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Sorting (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +" (00:00:00), +; (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +, (00:00:00), +i (00:00:00), +] (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Sorted (00:00:00), +! (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +Motorcycle (00:00:00), +incoming (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Done (00:00:00), +! (00:00:00), +" (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +container (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +visEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +containerWidth (00:00:00), += (00:00:00), +container (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), +; (00:00:00), +const (00:00:00), +barCount (00:00:00), += (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +barCount (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +barLeft (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), ++ (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +visTop (00:00:00), += (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetTop (00:00:00), +; (00:00:00), +const (00:00:00), +visHeight (00:00:00), += (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +barTopInContainer (00:00:00), += (00:00:00), +visTop (00:00:00), ++ (00:00:00), +( (00:00:00), +visHeight (00:00:00), +- (00:00:00), +barHeight (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motoTop (00:00:00), += (00:00:00), +barTopInContainer (00:00:00), +- (00:00:00), +36 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +( (00:00:00), +barLeft (00:00:00), +- (00:00:00), +10 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +motoTop (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +Math (00:00:00), +. (00:00:00), +max (00:00:00), +( (00:00:00), +10 (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +* (00:00:00), +0 (00:00:00), +. (00:00:00), +5 (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +( (00:00:00), +containerWidth (00:00:00), ++ (00:00:00), +50 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +300 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +" (00:00:00), +- (00:00:00), +40px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +" (00:00:00), +0px (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +1a1a2e (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +eee (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +h1 (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +e0e0ff (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +12px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +label (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +aaa (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +{ (00:00:00), +accent (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +150px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +600px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +220px (00:00:00), +; (00:00:00), +} (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +16213e (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +10px (00:00:00), +8px (00:00:00), +0 (00:00:00), +8px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +, (00:00:00), +# (00:00:00), +a29bfe (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +0 (00:00:00), +0 (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +height (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +. (00:00:00), +comparing (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +fd79a8 (00:00:00), +, (00:00:00), +# (00:00:00), +e84393 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +28px (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +40px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +drop (00:00:00), +- (00:00:00), +shadow (00:00:00), +( (00:00:00), +0 (00:00:00), +0 (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +108 (00:00:00), +, (00:00:00), +99 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +8 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +; (00:00:00), +z (00:00:00), +- (00:00:00), +index (00:00:00), +: (00:00:00), +10 (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +status (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +13px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +888 (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D90" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000FA000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found, DOCX: cleared author metadata (answer.docx)</t>
         </r>
       </text>
     </comment>
@@ -3332,6 +3612,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D91" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found, Short name part(s) not auto-redacted (verify manually): v3, DOCX: cleared author metadata (answer.docx)</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E91" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002010000}">
       <text>
         <r>
@@ -3416,6 +3710,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="D92" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found, DOCX: cleared author metadata (answer.docx)</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E92" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009010000}">
       <text>
         <r>
@@ -3487,6 +3795,594 @@
       </text>
     </comment>
     <comment ref="X92" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>!var_speed</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D93" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found, DOCX: cleared author metadata (document.docx)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E93" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>" (x52), #, % (x4), ( (x38), ) (x38), * (x4), + (x16), , (x5), - (x18), . (x39), / (x4), 0 (x7), 1 (x5), 10 (x2), 100 (x5), 12, 123456 (x2), 1px, 20, 200px, 20px, 26px, 50 (x2), 500, 7px, 8, : (x21), ; (x72), &lt; (x9), = (x35), &gt; (x8), Animation, Arial, Array, Georgia, Math (x2), New, Number, Promise, Roman, Times, UTF, [ (x11), ] (x11), _ (x5), absolute, add (x2), align (x2), appendChild (x2), arr (x8), array (x6), async (x2), aux (x2), await (x3), background, bar (x8), barHeight (x2), bars (x7), black, body, bottom (x3), bubbleSort (x2), center, charset, class, classList (x2), color, column, const (x15), content, controls (x2), count (x3), createElement (x2), css, device, direction, display (x2), div (x3), do, document (x7), en, end, events, false, family (x2), flex (x4), font (x3), for (x5), function (x5), getElementById (x3), getElementsByClassName (x2), height (x5), href, i (x27), id (x2), if, initial, input, items (x2), js, label (x2), lang, left (x2), length (x5), let (x7), link, margin (x2), max (x2), meta (x2), milliseconds (x2), min, motorcycle (x8), ms (x2), name, new (x2), none, offsetHeight, offsetWidth, onchange, overflow, parseFloat, pointer, position (x2), px (x2), random, range, rel, relative, resolve (x2), return, rideMotorcycle (x2), sans, scale, script, serif (x2), setTimeout, size, sleep (x3), span (x2), speed (x6), speedSlider (x6), speedValue (x4), src, step, style (x5), stylesheet, swapped (x4), textContent (x2), totalSteps (x2), transform, translateX, true, type, updateBars (x2), value (x2), var (x5), viewport, vis (x2), visible, visualizer (x5), visualizerHeight (x2), visualizerWidth (x2), while, width (x2), x (x2), { (x17), } (x17), ️, 🏍</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H93" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-0px (00:01:24), -var (00:05:48), -new (00:07:04), -Promise (00:07:05), -( (00:07:06), -resolve (00:07:07), -= (00:07:08), -&gt; (00:07:09), -setTimeout (00:07:10), -( (00:07:11), -resolve (00:07:12), -, (00:07:13), -100 (00:07:14), -) (00:07:15), -) (00:07:16), +lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Animation (00:00:00), +speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +500 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +step (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +let (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +speedSlider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedValue (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +onchange (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), ++ (00:00:00), +" (00:00:00), +ms (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +function (00:00:00), +sleep (00:00:00), +( (00:00:00), +milliseconds (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +milliseconds (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +let (00:00:00), +swapped (00:00:00), +; (00:00:00), +sleep (00:00:00), +( (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +await (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +motorcycle (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +motorcycle (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +visualizerWidth (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), +; (00:00:00), +const (00:00:00), +visualizerHeight (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +totalSteps (00:00:00), += (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +- (00:00:00), +1 (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +x (00:00:00), += (00:00:00), +( (00:00:00), +i (00:00:00), +/ (00:00:00), +totalSteps (00:00:00), +) (00:00:00), +* (00:00:00), +visualizerWidth (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +parseFloat (00:00:00), +( (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), +) (00:00:00), +/ (00:00:00), +100 (00:00:00), +* (00:00:00), +visualizerHeight (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +x (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +( (00:00:00), +barHeight (00:00:00), ++ (00:00:00), +12 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +sleep (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +max (00:00:00), +( (00:00:00), +20 (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Georgia (00:00:00), +, (00:00:00), +" (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +" (00:00:00), +, (00:00:00), +serif (00:00:00), +; (00:00:00), +. (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Arial (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +overflow (00:00:00), +: (00:00:00), +visible (00:00:00), +; (00:00:00), +0 (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +bottom (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +26px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateX (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J93" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>+lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Animation (00:00:00), +speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +500 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +step (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L93" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-0px (00:01:24), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Georgia (00:00:00), +, (00:00:00), +" (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +" (00:00:00), +, (00:00:00), +serif (00:00:00), +; (00:00:00), +. (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Arial (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +overflow (00:00:00), +: (00:00:00), +visible (00:00:00), +; (00:00:00), +0 (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +bottom (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +26px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateX (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N93" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-var (00:05:48), -new (00:07:04), -Promise (00:07:05), -( (00:07:06), -resolve (00:07:07), -= (00:07:08), -&gt; (00:07:09), -setTimeout (00:07:10), -( (00:07:11), -resolve (00:07:12), -, (00:07:13), -100 (00:07:14), -) (00:07:15), -) (00:07:16), +let (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +speedSlider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedValue (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +onchange (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), ++ (00:00:00), +" (00:00:00), +ms (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +function (00:00:00), +sleep (00:00:00), +( (00:00:00), +milliseconds (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +milliseconds (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +let (00:00:00), +swapped (00:00:00), +; (00:00:00), +sleep (00:00:00), +( (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +await (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +motorcycle (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +motorcycle (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +visualizerWidth (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), +; (00:00:00), +const (00:00:00), +visualizerHeight (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +totalSteps (00:00:00), += (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +- (00:00:00), +1 (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +x (00:00:00), += (00:00:00), +( (00:00:00), +i (00:00:00), +/ (00:00:00), +totalSteps (00:00:00), +) (00:00:00), +* (00:00:00), +visualizerWidth (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +parseFloat (00:00:00), +( (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), +) (00:00:00), +/ (00:00:00), +100 (00:00:00), +* (00:00:00), +visualizerHeight (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +x (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +( (00:00:00), +barHeight (00:00:00), ++ (00:00:00), +12 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +sleep (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +max (00:00:00), +( (00:00:00), +20 (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X93" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>!var_speed</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D94" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found, DOCX: cleared author metadata (answer.docx), DOCX: cleared author metadata (document.docx)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E94" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>" (x58), # (x3), % (x4), ( (x34), ) (x34), * (x2), + (x17), , (x4), - (x22), . (x42), / (x3), 0 (x5), 1 (x5), 10 (x2), 100 (x4), 123456 (x2), 1px, 2 (x3), 20, 200px, 20px, 260px, 30 (x2), 300, 30px (x2), 50 (x2), 500, 7px, 8, 8px, : (x22), ; (x75), &lt; (x7), = (x37), &gt; (x6), Animation, Array, Georgia, Math (x2), New, Number, Promise, Roman, Times, UTF, [ (x11), ] (x11), _ (x5), absolute, add, align (x2), appendChild (x2), arr (x8), array (x6), async (x2), aux (x2), await (x4), background, bar (x12), bars (x6), black, block, body, bottom (x2), bubbleSort (x2), center, changeSpeed (x2), charset, classList, color, column, const (x12), content, count (x3), createElement (x2), css, device, direction, display (x5), div (x2), do, document (x6), en, end, events, false, family, flex (x4), font (x2), for (x5), function (x5), getElementById (x2), getElementsByClassName (x2), height (x5), href, i (x26), id (x3), if, index, initial, input, items (x2), js, label (x3), lang, left (x2), length (x4), let (x7), line, link, margin (x3), max (x2), meta (x2), min, motorcycle (x13), ms (x3), name, new (x2), none (x3), offsetLeft, offsetTop, offsetWidth (x2), oninput, overflow, pointer, position (x2), px (x3), random, range, rel, relative, resolve (x2), return, rideMotorcycle (x2), scale, script, serif, setTimeout, size, sleep (x4), slider (x3), span (x2), speed (x11), speedValue (x2), src, step, style (x9), stylesheet, swapped (x4), textContent (x2), this, top (x2), transform, translateX, true, type, updateBars (x2), value (x6), var (x5), viewport, vis (x2), visible, visualizer (x4), while, width (x3), x (x2), y (x2), z, { (x18), } (x18), ️, 🏍</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H94" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-0px (00:01:24), -var (00:05:48), -new (00:07:04), -Promise (00:07:05), -( (00:07:06), -resolve (00:07:07), -= (00:07:08), -&gt; (00:07:09), -setTimeout (00:07:10), -( (00:07:11), -resolve (00:07:12), -, (00:07:13), -100 (00:07:14), -) (00:07:15), -) (00:07:16), +lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Animation (00:00:00), +speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +300 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +step (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +oninput (00:00:00), += (00:00:00), +" (00:00:00), +changeSpeed (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +" (00:00:00), +&gt; (00:00:00), +let (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +speedValue (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motorcycle (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +motorcycle (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +changeSpeed (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +sleep (00:00:00), +( (00:00:00), +ms (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +ms (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +let (00:00:00), +swapped (00:00:00), +; (00:00:00), +sleep (00:00:00), +( (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +await (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +x (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), ++ (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), +/ (00:00:00), +2 (00:00:00), +; (00:00:00), +const (00:00:00), +y (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetTop (00:00:00), +- (00:00:00), +30 (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +x (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +y (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +sleep (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +max (00:00:00), +( (00:00:00), +20 (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +/ (00:00:00), +2 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), ++ (00:00:00), +30 (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +" (00:00:00), +- (00:00:00), +30px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +sleep (00:00:00), +( (00:00:00), +500 (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Georgia (00:00:00), +, (00:00:00), +" (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +" (00:00:00), +, (00:00:00), +serif (00:00:00), +; (00:00:00), +label (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +260px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +overflow (00:00:00), +: (00:00:00), +visible (00:00:00), +; (00:00:00), +0 (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +line (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateX (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +z (00:00:00), +- (00:00:00), +index (00:00:00), +: (00:00:00), +2 (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J94" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>+lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Animation (00:00:00), +speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +300 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +step (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +oninput (00:00:00), += (00:00:00), +" (00:00:00), +changeSpeed (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +" (00:00:00), +&gt; (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L94" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-0px (00:01:24), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Georgia (00:00:00), +, (00:00:00), +" (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +" (00:00:00), +, (00:00:00), +serif (00:00:00), +; (00:00:00), +label (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +260px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +overflow (00:00:00), +: (00:00:00), +visible (00:00:00), +; (00:00:00), +0 (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +line (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateX (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +z (00:00:00), +- (00:00:00), +index (00:00:00), +: (00:00:00), +2 (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N94" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001B010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-var (00:05:48), -new (00:07:04), -Promise (00:07:05), -( (00:07:06), -resolve (00:07:07), -= (00:07:08), -&gt; (00:07:09), -setTimeout (00:07:10), -( (00:07:11), -resolve (00:07:12), -, (00:07:13), -100 (00:07:14), -) (00:07:15), -) (00:07:16), +let (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +speedValue (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motorcycle (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +motorcycle (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +changeSpeed (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +sleep (00:00:00), +( (00:00:00), +ms (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +ms (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +let (00:00:00), +swapped (00:00:00), +; (00:00:00), +sleep (00:00:00), +( (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +await (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +x (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), ++ (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), +/ (00:00:00), +2 (00:00:00), +; (00:00:00), +const (00:00:00), +y (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetTop (00:00:00), +- (00:00:00), +30 (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +x (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +y (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +sleep (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +max (00:00:00), +( (00:00:00), +20 (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +/ (00:00:00), +2 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), ++ (00:00:00), +30 (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +" (00:00:00), +- (00:00:00), +30px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +sleep (00:00:00), +( (00:00:00), +500 (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X94" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001C010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>!var_speed</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D95" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001D010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found, DOCX: cleared author metadata (document.docx)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E95" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001E010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>" (x46), # (x5), % (x3), ( (x33), ) (x33), * (x4), + (x17), , (x4), - (x28), . (x41), / (x4), 0 (x6), 05s (x2), 0px (x2), 1 (x5), 100 (x4), 10px, 123456 (x2), 14px (x2), 16px (x2), 1px, 20, 200 (x3), 200px, 201, 20px, 24px, 30px, 4, 400, 50, 60, 60px, 7px, 8, : (x30), ; (x81), &lt; (x7), = (x39), &gt; (x8), Array, Math, Promise (x3), Speed, [ (x11), ] (x11), _ (x3), absolute, add, align (x3), appendChild (x2), arr (x8), array (x6), async (x2), aux (x2), await (x3), background (x2), bar (x8), barHeightPx (x2), barWidth (x3), bars (x7), black, block, body, bottom (x4), bubbleSort (x2), center (x2), classList, color (x2), column, const (x13), controls (x2), count (x3), createElement (x2), css, direction, display (x6), div (x3), do, document (x7), end, events, f9f9f9, false, family, flex (x5), font (x4), for (x5), function (x4), gap, getElementById (x3), getElementsByClassName (x2), h1, height (x5), href, i (x27), id (x4), if, input, items (x3), js, label (x6), left (x4), leftPos (x2), length (x5), let (x5), line, linear (x2), link, margin (x3), max, min (x2), moto (x9), motorcycle (x2), new (x4), none (x3), offsetHeight, onchange, padding, parseInt, pointer, position (x2), px (x3), random, range, rel, relative, resolve (x6), runMotorcycle (x2), sans, script, serif, setTimeout (x3), size (x3), slider (x3), span (x2), speed (x9), speedLabel (x2), speedSlider (x2), src, style (x7), stylesheet, swapped (x3), textContent (x2), this (x2), top, transition, true, type, updateBars (x2), value (x3), var (x5), vis (x2), visualizer (x3), while, width (x2), { (x19), } (x19), ️, 🏍</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H95" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001F010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-100 (00:07:14), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +200 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +label (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +/ (00:00:00), +200 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +moto (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedSlider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedLabel (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +label (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +onchange (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +201 (00:00:00), +- (00:00:00), +parseInt (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedLabel (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), ++ (00:00:00), +" (00:00:00), +/ (00:00:00), +200 (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +barWidth (00:00:00), += (00:00:00), +8 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +barHeightPx (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +leftPos (00:00:00), += (00:00:00), +i (00:00:00), +* (00:00:00), +barWidth (00:00:00), +- (00:00:00), +4 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +leftPos (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +barHeightPx (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +60 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +* (00:00:00), +barWidth (00:00:00), ++ (00:00:00), +20 (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +400 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +f9f9f9 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +h1 (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +# (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +} (00:00:00), +label (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +label (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +60px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +24px (00:00:00), +; (00:00:00), +bottom (00:00:00), +: (00:00:00), +0px (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +30px (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +, (00:00:00), +bottom (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +line (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J95" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000020010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>+&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +200 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +label (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +/ (00:00:00), +200 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L95" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000021010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>+font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +f9f9f9 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +h1 (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +# (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +} (00:00:00), +label (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +label (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +60px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +24px (00:00:00), +; (00:00:00), +bottom (00:00:00), +: (00:00:00), +0px (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +30px (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +, (00:00:00), +bottom (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +line (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N95" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000022010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-100 (00:07:14), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +moto (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedSlider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedLabel (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +label (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +onchange (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +201 (00:00:00), +- (00:00:00), +parseInt (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedLabel (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), ++ (00:00:00), +" (00:00:00), +/ (00:00:00), +200 (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +barWidth (00:00:00), += (00:00:00), +8 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +barHeightPx (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +leftPos (00:00:00), += (00:00:00), +i (00:00:00), +* (00:00:00), +barWidth (00:00:00), +- (00:00:00), +4 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +leftPos (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +barHeightPx (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +60 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +* (00:00:00), +barWidth (00:00:00), ++ (00:00:00), +20 (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +400 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X95" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000023010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>oninput, !var_speed</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D96" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000024010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found, DOCX: cleared author metadata (answer.docx)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E96" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000025010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>" (x40), #, % (x3), ( (x33), ) (x33), * (x3), + (x15), , (x2), - (x14), . (x35), / (x2), 0 (x5), 0px, 1 (x4), 100 (x4), 10px, 123456 (x2), 1px, 200px, 20px, 4px, 50, 500, 7px, : (x15), ; (x63), &lt; (x7), = (x35), &gt; (x7), Array, Math, Promise (x2), Speed, [ (x12), ] (x12), _ (x5), absolute, add (x2), align (x2), appendChild (x2), arr (x8), array (x7), async (x2), aux (x2), await (x2), background, bar (x10), barHeight (x2), barLeft (x2), bars (x6), black, body, bottom, bubbleSort (x2), center, class, classList (x2), clientHeight, color, column, const (x14), controls (x2), count (x3), createElement (x2), css, direction, display (x2), div (x3), do, document (x7), end, false, flex (x4), font, for (x5), function (x4), getElementById (x3), getElementsByClassName (x2), height (x4), href, i (x27), id (x2), if, input, items (x2), js, label (x2), left, length (x4), let (x5), link, margin (x2), max, min, moto (x6), motorcycle (x2), ms (x2), new (x3), offsetLeft, oninput, parseInt, position (x2), px (x2), random, range, rel, relative, resolve (x4), rideMotorcycle (x2), script, setTimeout (x2), size, slider (x6), span (x2), speed (x10), speedLabel (x2), src, style (x4), stylesheet, swapped (x3), textContent (x2), transform, translateY, true, type, updateBars (x2), value (x4), var (x7), vis (x2), visHeight (x2), visualizer (x4), while, width, { (x16), } (x16), ️, 🏍</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H96" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000026010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-100 (00:07:14), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +500 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +slider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedLabel (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +slider (00:00:00), +. (00:00:00), +oninput (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +slider (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedLabel (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), ++ (00:00:00), +" (00:00:00), +ms (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +moto (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +visHeight (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +clientHeight (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +barLeft (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +visHeight (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +barLeft (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +barHeight (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +. (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +: (00:00:00), +10px (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateY (00:00:00), +( (00:00:00), +- (00:00:00), +4px (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J96" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000027010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>+&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +500 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L96" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000028010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>+. (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +: (00:00:00), +10px (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateY (00:00:00), +( (00:00:00), +- (00:00:00), +4px (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N96" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000029010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-100 (00:07:14), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +slider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedLabel (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +slider (00:00:00), +. (00:00:00), +oninput (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +slider (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedLabel (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), ++ (00:00:00), +" (00:00:00), +ms (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +moto (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +visHeight (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +clientHeight (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +barLeft (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +visHeight (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +barLeft (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +barHeight (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X96" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002A010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>!var_speed</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D97" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002B010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found, DOCX: cleared author metadata (answer.docx), DOCX error (~$answer.docx): Package not found at 'C:\UNIVERSITY\2026 - 2027\WebResearch\assignments\sorting\students\gemini 3.5 flash images\~$answer.docx'</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E97" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002C010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>" (x40), # (x3), $ (x3), % (x5), ( (x29), ) (x29), * (x2), + (x13), , (x4), - (x20), . (x38), / (x3), 0 (x7), 0px (x2), 1 (x4), 10, 100 (x6), 123456 (x2), 1px, 1s (x2), 200px, 20px, 24px, 30px, 450px, 50 (x2), 500, 7px, 8, : (x23), ; (x66), &lt; (x10), = (x32), &gt; (x10), Animation, Arial, Array, Delay, Math, Promise (x2), UTF, [ (x11), ] (x11), _ (x3), ` (x6), absolute, add, align (x2), appendChild, arr (x8), array (x6), async (x2), aux (x2), await (x2), background, bar (x8), barHeight (x2), barRect (x3), bars (x6), black, block, body, bottom (x5), bubbleSort (x2), center, charset, class, classList, color, column, const (x12), container (x3), containerRect (x3), control (x2), count (x3), createElement, css, direction, display (x4), div (x6), do, document (x6), en, end, events, false, family, flex (x4), font (x2), for (x5), function (x3), getBoundingClientRect (x2), getElementById (x3), getElementsByClassName (x2), height (x6), href, i (x26), id (x3), if, input, items (x2), js, label (x2), lang, left (x6), length (x4), let (x6), linear (x2), link, margin (x2), max, meta, min, motorcycle (x9), ms, new (x3), none (x2), onchange, panel (x2), pointer, position (x2), px (x3), random, range, rel, relative, relativeLeft (x2), resolve (x4), rideMotorcycle (x2), sans, script, serif, setTimeout (x2), size, slider (x2), speed (x5), src, style (x7), stylesheet, swapped (x3), this, transition, true, type, updateBars (x2), value (x2), var (x3), vis (x4), visualizer (x2), while, width (x4), { (x19), } (x19), ️, 🏍</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H97" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002D010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-200px (00:00:49), -100 (00:07:14), +lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +control (00:00:00), +- (00:00:00), +panel (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Animation (00:00:00), +Delay (00:00:00), +( (00:00:00), +ms (00:00:00), +) (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +500 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +onchange (00:00:00), += (00:00:00), +" (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +let (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +motorcycle (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +containerRect (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +getBoundingClientRect (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +barRect (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +getBoundingClientRect (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +relativeLeft (00:00:00), += (00:00:00), +barRect (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +containerRect (00:00:00), +. (00:00:00), +left (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +barRect (00:00:00), +. (00:00:00), +height (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +` (00:00:00), +$ (00:00:00), +{ (00:00:00), +relativeLeft (00:00:00), +} (00:00:00), +px (00:00:00), +` (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +` (00:00:00), +$ (00:00:00), +{ (00:00:00), +barHeight (00:00:00), +} (00:00:00), +px (00:00:00), +` (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +50 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +` (00:00:00), +$ (00:00:00), +{ (00:00:00), +containerRect (00:00:00), +. (00:00:00), +width (00:00:00), ++ (00:00:00), +10 (00:00:00), +} (00:00:00), +px (00:00:00), +` (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +" (00:00:00), +0px (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Arial (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +450px (00:00:00), +; (00:00:00), +} (00:00:00), +100 (00:00:00), +% (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +bottom (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +30px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +24px (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +1s (00:00:00), +linear (00:00:00), +, (00:00:00), +bottom (00:00:00), +0 (00:00:00), +. (00:00:00), +1s (00:00:00), +linear (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J97" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002E010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>+lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +control (00:00:00), +- (00:00:00), +panel (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Animation (00:00:00), +Delay (00:00:00), +( (00:00:00), +ms (00:00:00), +) (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +500 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +onchange (00:00:00), += (00:00:00), +" (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L97" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002F010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-200px (00:00:49), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Arial (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +450px (00:00:00), +; (00:00:00), +} (00:00:00), +100 (00:00:00), +% (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +bottom (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +30px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +24px (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +1s (00:00:00), +linear (00:00:00), +, (00:00:00), +bottom (00:00:00), +0 (00:00:00), +. (00:00:00), +1s (00:00:00), +linear (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N97" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000030010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-100 (00:07:14), +let (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +motorcycle (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +containerRect (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +getBoundingClientRect (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +barRect (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +getBoundingClientRect (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +relativeLeft (00:00:00), += (00:00:00), +barRect (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +containerRect (00:00:00), +. (00:00:00), +left (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +barRect (00:00:00), +. (00:00:00), +height (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +` (00:00:00), +$ (00:00:00), +{ (00:00:00), +relativeLeft (00:00:00), +} (00:00:00), +px (00:00:00), +` (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +` (00:00:00), +$ (00:00:00), +{ (00:00:00), +barHeight (00:00:00), +} (00:00:00), +px (00:00:00), +` (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +50 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +` (00:00:00), +$ (00:00:00), +{ (00:00:00), +containerRect (00:00:00), +. (00:00:00), +width (00:00:00), ++ (00:00:00), +10 (00:00:00), +} (00:00:00), +px (00:00:00), +` (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +" (00:00:00), +0px (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X97" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000031010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>oninput, !var_speed</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D100" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000032010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Student number not found, Short name part(s) not auto-redacted (verify manually): v3, DOCX: cleared author metadata (answer.docx)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E100" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000033010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>! (x3), " (x116), # (x13), $, % (x19), &amp; (x2), ' (x2), ( (x121), ) (x121), * (x2), + (x12), , (x55), - (x73), . (x117), / (x10), 0 (x55), 05, 05s, 1 (x15), 100 (x9), 100vh, 10px (x2), 123456, 12px (x4), 135deg (x3), 14px (x2), 15px (x3), 16px, 180deg, 1px, 2 (x3), 200, 2000, 200px, 20px (x7), 24px, 25, 255 (x6), 25px (x6), 2px (x6), 2s (x3), 3 (x3), 30, 30px (x2), 32px, 333, 350px, 3px, 40px, 45 (x3), 45px, 46, 49, 4px (x6), 5, 50 (x2), 50px (x3), 5px, 667eea (x3), 6px, 764ba2 (x4), 768px, 8, 80 (x3), 800, 8px (x3), 8s, 9, 94, 95, : (x96), ; (x202), &lt; (x25), = (x80), &gt; (x29), ?, @ (x3), Animation, Array, Bubble (x3), Error, Geneva, Math, Motorcycle, New, Promise, Ride, Segoe, Sort (x3), Sorting (x3), Speed, Start, Tahoma, UI, UTF, Verdana, [ (x10), ] (x10), _ (x2), ` (x2), absolute, across, add (x3), addEventListener (x7), adjusts, align (x5), animateMotorcycle (x2), animation (x3), animationend (x2), appendChild (x4), arr (x8), array (x7), async (x3), await (x3), background (x7), bar (x8), bars (x5), barsContainer (x3), between, bezier, block, body, bold (x3), border (x7), bottom (x2), box (x6), bubbleSortVisual (x2), button (x7), calc, cancelled, catch, center (x6), change, charset, class (x7), classList (x3), click (x4), clientWidth, color (x4), column (x2), comparisons, completed, console, const (x18), container (x5), containerWidth (x2), content (x3), control (x3), controls (x4), controlsDiv (x3), count (x3), createElement (x4), css, cubic, currentSortingPromise, cursor (x2), delay, device, direction (x2), disabled, display (x7), div (x13), do, document (x14), drop, dynamic, e (x6), ease, en, end, error (x2), existingRun (x3), f093fb, f5576c, false (x6), family, faster, filter, finally, firstChild (x2), flex (x8), font (x9), for (x4), forwards (x2), from, function (x12), gap (x4), getElementById (x6), getElementsByClassName, globalSpeed (x12), gradient (x4), h1 (x2), head, height (x6), hideMotorcycle (x7), hover, href, i (x23), id (x6), if (x11), info (x3), initRandomArray (x3), initial, input (x3), interrupted, items (x4), js, justify (x2), keyframes (x3), label (x3), lang, left (x5), len (x3), length (x4), let (x11), linear (x5), link, log, lower, margin (x6), max (x2), media, message, meta (x2), min (x3), motorcycle (x8), motorcycleDiv (x9), motorcycleZone (x8), ms, name, new (x3), none (x5), null, offsetHeight, onFinish (x3), originalReset, overflow, p (x5), padding (x6), parseInt (x4), pointer (x2), position (x3), px, querySelector (x3), races, radius (x6), random, range, rel, relative (x2), remove (x2), removeChild, removeEventListener (x2), renderBars (x3), reset (x4), resetAndStop (x6), resetBtn (x7), resolve (x2), return (x2), rgba (x9), rideAcross (x2), rideAcrossDynamic (x2), right, run (x4), sans, scale (x2), scaleX (x8), script, serif, setTimeout (x2), setupSpeedSlider, shadow (x8), size (x5), slider, sortBtn (x6), sortingInProgress (x11), span (x2), speed (x6), speedSlider (x9), speedValue (x8), src, startSorting (x2), step, style (x9), styleId (x3), styleTag (x7), stylesheet, swapped (x4), target (x3), temp (x2), text (x2), textContent (x7), the, throw, to, top (x2), transform (x10), transition (x2), true (x2), try, type, updateBars (x3), value (x5), var (x2), viewport, vis (x2), visible, visualizer (x5), weight (x3), while (x2), white (x3), width (x6), window (x3), with, wrap (x2), zone (x2), { (x68), |, } (x68), ·, →, ⏩, ⚡ (x2), ✅, ️ (x4), 🏍 (x4), 🔄</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H100" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000034010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-# (00:00:42), -vis (00:00:43), -- (00:00:44), -123456 (00:00:45), -{ (00:00:46), -height (00:00:47), -: (00:00:48), -200px (00:00:49), -; (00:00:50), -display (00:00:51), -: (00:00:52), -flex (00:00:53), -; (00:00:54), -align (00:00:55), -- (00:00:56), -items (00:00:57), -: (00:00:58), -flex (00:00:59), -- (00:01:00), -end (00:01:01), -; (00:01:02), -} (00:01:03), -7px (00:01:09), -height (00:01:11), -: (00:01:12), -100 (00:01:13), -% (00:01:14), -; (00:01:15), -background (00:01:16), -- (00:01:17), -color (00:01:18), -: (00:01:19), -black (00:01:20), -; (00:01:21), -margin (00:01:22), -: (00:01:23), -0px (00:01:24), -1px (00:01:25), -; (00:01:26), -const (00:02:09), -count (00:02:10), -= (00:02:11), -50 (00:02:12), -; (00:02:13), -const (00:02:14), -array (00:02:15), -= (00:02:16), -new (00:02:17), -Array (00:02:18), -( (00:02:19), -count (00:02:20), -) (00:02:21), -; (00:02:22), -for (00:02:23), -( (00:02:24), -let (00:02:25), -i (00:02:26), -= (00:02:27), -0 (00:02:28), -; (00:02:29), -i (00:02:30), -&lt; (00:02:31), -count (00:02:32), -; (00:02:33), -i (00:02:34), -+ (00:02:35), -+ (00:02:36), -) (00:02:37), -{ (00:02:38), -array (00:02:39), -[ (00:02:40), -i (00:02:41), -] (00:02:42), -= (00:02:43), -Math (00:02:44), -. (00:02:45), -random (00:02:46), -( (00:02:47), -) (00:02:48), -; (00:02:49), -} (00:02:57), -const (00:02:58), -visualizer (00:02:59), -= (00:03:00), -document (00:03:01), -. (00:03:02), -getElementById (00:03:03), -( (00:03:04), -" (00:03:05), -vis (00:03:06), -- (00:03:07), -123456 (00:03:08), -" (00:03:09), -) (00:03:10), -; (00:03:11), -for (00:03:12), -( (00:03:13), -let (00:03:14), -i (00:03:15), -= (00:03:16), -0 (00:03:17), -; (00:03:18), -i (00:03:19), -&lt; (00:03:20), -array (00:03:21), -. (00:03:22), -length (00:03:23), -; (00:03:24), -i (00:03:25), -+ (00:03:26), -+ (00:03:27), -) (00:03:28), -{ (00:03:29), -const (00:03:30), -bar (00:03:31), -= (00:03:32), -document (00:03:33), -. (00:03:34), -createElement (00:03:35), -( (00:03:36), -" (00:03:37), -div (00:03:38), -" (00:03:39), -) (00:03:40), -; (00:03:41), -visualizer (00:03:42), -. (00:03:43), -appendChild (00:03:44), -( (00:03:45), -bar (00:03:46), -) (00:03:47), -; (00:03:48), -bar (00:03:49), -. (00:03:50), -classList (00:03:51), -. (00:03:52), -add (00:03:53), -( (00:03:54), -" (00:03:55), -bar (00:03:56), -" (00:03:57), -) (00:03:58), -; (00:03:59), -bar (00:04:00), -. (00:04:01), -style (00:04:02), -. (00:04:03), -height (00:04:04), -= (00:04:05), -array (00:04:06), -[ (00:04:07), -i (00:04:08), -] (00:04:09), -* (00:04:10), -100 (00:04:11), -+ (00:04:12), -" (00:04:13), -% (00:04:14), -" (00:04:15), -; (00:04:16), -} (00:04:36), -bubbleSort (00:04:37), -( (00:04:38), -array (00:04:39), -) (00:04:40), -; (00:04:41), -function (00:04:42), -updateBars (00:04:43), -( (00:04:44), -) (00:04:45), -{ (00:04:46), -const (00:04:47), -bars (00:04:48), -= (00:04:49), -document (00:04:50), -. (00:04:51), -getElementsByClassName (00:04:52), -( (00:04:53), -" (00:04:54), -bar (00:04:55), -" (00:04:56), -) (00:04:57), -; (00:04:58), -for (00:04:59), -( (00:05:00), -let (00:05:01), -i (00:05:02), -= (00:05:03), -0 (00:05:04), -; (00:05:05), -i (00:05:06), -&lt; (00:05:07), -bars (00:05:08), -. (00:05:09), -length (00:05:10), -; (00:05:11), -i (00:05:12), -+ (00:05:13), -+ (00:05:14), -) (00:05:15), -{ (00:05:16), -bars (00:05:17), -[ (00:05:18), -i (00:05:19), -] (00:05:20), -. (00:05:21), -style (00:05:22), -. (00:05:23), -height (00:05:24), -= (00:05:25), -array (00:05:26), -[ (00:05:27), -i (00:05:28), -] (00:05:29), -* (00:05:30), -100 (00:05:31), -+ (00:05:32), -" (00:05:33), -% (00:05:34), -" (00:05:35), -; (00:05:36), -} (00:05:37), -} (00:05:38), -bubbleSort (00:05:41), -var (00:05:48), -arr (00:06:02), -. (00:06:03), -length (00:06:04), -aux (00:06:27), -aux (00:06:53), -100 (00:07:14), +lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +| (00:00:00), +Bubble (00:00:00), +Sort (00:00:00), +with (00:00:00), +Motorcycle (00:00:00), +Ride (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +· (00:00:00), +Bubble (00:00:00), +Sort (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +control (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +⏩ (00:00:00), +Animation (00:00:00), +speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +0 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +200 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +80 (00:00:00), +" (00:00:00), +step (00:00:00), += (00:00:00), +" (00:00:00), +5 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +&gt; (00:00:00), +80 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +button (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +resetBtn (00:00:00), +" (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +reset (00:00:00), +- (00:00:00), +button (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🔄 (00:00:00), +New (00:00:00), +random (00:00:00), +array (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +button (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&gt; (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +bars (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycleZone (00:00:00), +" (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +zone (00:00:00), +" (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +run (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +info (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +&gt; (00:00:00), +✅ (00:00:00), +Sorting (00:00:00), +completed (00:00:00), +→ (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +motorcycle (00:00:00), +races (00:00:00), +across (00:00:00), +the (00:00:00), +bars (00:00:00), +from (00:00:00), +left (00:00:00), +to (00:00:00), +right (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +&gt; (00:00:00), +⚡ (00:00:00), +Speed (00:00:00), +slider (00:00:00), +adjusts (00:00:00), +delay (00:00:00), +between (00:00:00), +comparisons (00:00:00), +( (00:00:00), +lower (00:00:00), += (00:00:00), +faster (00:00:00), +) (00:00:00), +. (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +const (00:00:00), +count (00:00:00), += (00:00:00), +45 (00:00:00), +; (00:00:00), +let (00:00:00), +array (00:00:00), += (00:00:00), +new (00:00:00), +Array (00:00:00), +( (00:00:00), +count (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +let (00:00:00), +currentSortingPromise (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +let (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +80 (00:00:00), +; (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedSlider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedValue (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +resetBtn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +resetBtn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motorcycleZone (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycleZone (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +initRandomArray (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +Math (00:00:00), +. (00:00:00), +random (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +renderBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +while (00:00:00), +( (00:00:00), +visualizer (00:00:00), +. (00:00:00), +firstChild (00:00:00), +) (00:00:00), +{ (00:00:00), +visualizer (00:00:00), +. (00:00:00), +removeChild (00:00:00), +( (00:00:00), +visualizer (00:00:00), +. (00:00:00), +firstChild (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +bar (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +&amp; (00:00:00), +&amp; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +existingRun (00:00:00), += (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +querySelector (00:00:00), +( (00:00:00), +" (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +run (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +existingRun (00:00:00), +) (00:00:00), +{ (00:00:00), +existingRun (00:00:00), +. (00:00:00), +remove (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +animateMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motorcycleDiv (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +run (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +motorcycleDiv (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +barsContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +querySelector (00:00:00), +( (00:00:00), +" (00:00:00), +. (00:00:00), +bars (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +containerWidth (00:00:00), += (00:00:00), +barsContainer (00:00:00), +? (00:00:00), +barsContainer (00:00:00), +. (00:00:00), +clientWidth (00:00:00), +: (00:00:00), +800 (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +animation (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +styleId (00:00:00), += (00:00:00), +" (00:00:00), +dynamic (00:00:00), +- (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +keyframes (00:00:00), +" (00:00:00), +; (00:00:00), +let (00:00:00), +styleTag (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +styleId (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +styleTag (00:00:00), +) (00:00:00), +{ (00:00:00), +styleTag (00:00:00), +. (00:00:00), +remove (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +styleTag (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +style (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +styleTag (00:00:00), +. (00:00:00), +id (00:00:00), += (00:00:00), +styleId (00:00:00), +; (00:00:00), +styleTag (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +` (00:00:00), +@ (00:00:00), +keyframes (00:00:00), +rideAcrossDynamic (00:00:00), +{ (00:00:00), +0 (00:00:00), +% (00:00:00), +{ (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +50px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +45 (00:00:00), +% (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +50 (00:00:00), +% (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +- (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +100 (00:00:00), +% (00:00:00), +{ (00:00:00), +left (00:00:00), +: (00:00:00), +$ (00:00:00), +{ (00:00:00), +containerWidth (00:00:00), ++ (00:00:00), +30 (00:00:00), +} (00:00:00), +px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +- (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +` (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +head (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +styleTag (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +animation (00:00:00), += (00:00:00), +" (00:00:00), +rideAcrossDynamic (00:00:00), +1 (00:00:00), +. (00:00:00), +8s (00:00:00), +cubic (00:00:00), +- (00:00:00), +bezier (00:00:00), +( (00:00:00), +0 (00:00:00), +. (00:00:00), +25 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +46 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +45 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +94 (00:00:00), +) (00:00:00), +forwards (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +onFinish (00:00:00), += (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +) (00:00:00), +{ (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +, (00:00:00), +2000 (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +removeEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +animationend (00:00:00), +" (00:00:00), +, (00:00:00), +onFinish (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +animationend (00:00:00), +" (00:00:00), +, (00:00:00), +onFinish (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +bubbleSortVisual (00:00:00), +let (00:00:00), +len (00:00:00), += (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +let (00:00:00), +swapped (00:00:00), +; (00:00:00), +len (00:00:00), +if (00:00:00), +( (00:00:00), +! (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +throw (00:00:00), +new (00:00:00), +Error (00:00:00), +( (00:00:00), +" (00:00:00), +Sorting (00:00:00), +cancelled (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +temp (00:00:00), +temp (00:00:00), +globalSpeed (00:00:00), +len (00:00:00), +- (00:00:00), +- (00:00:00), +async (00:00:00), +function (00:00:00), +startSorting (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +disabled (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +try (00:00:00), +{ (00:00:00), +await (00:00:00), +bubbleSortVisual (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +animateMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +error (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +Sorting (00:00:00), +interrupted (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +error (00:00:00), +. (00:00:00), +message (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +finally (00:00:00), +{ (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +resetAndStop (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +initRandomArray (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +renderBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +setupSpeedSlider (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +input (00:00:00), +" (00:00:00), +, (00:00:00), +function (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +e (00:00:00), +. (00:00:00), +target (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +change (00:00:00), +" (00:00:00), +, (00:00:00), +function (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +e (00:00:00), +. (00:00:00), +target (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +resetAndStop (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +sortBtn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +button (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +⚡ (00:00:00), +Start (00:00:00), +Bubble (00:00:00), +Sort (00:00:00), +" (00:00:00), +; (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +reset (00:00:00), +- (00:00:00), +button (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +background (00:00:00), += (00:00:00), +" (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +135deg (00:00:00), +, (00:00:00), +# (00:00:00), +f093fb (00:00:00), +0 (00:00:00), +% (00:00:00), +, (00:00:00), +# (00:00:00), +f5576c (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +controlsDiv (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +querySelector (00:00:00), +( (00:00:00), +" (00:00:00), +. (00:00:00), +controls (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +controlsDiv (00:00:00), +) (00:00:00), +{ (00:00:00), +controlsDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +sortBtn (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +async (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +startSorting (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +originalReset (00:00:00), += (00:00:00), +resetAndStop (00:00:00), +; (00:00:00), +window (00:00:00), +. (00:00:00), +resetAndStop (00:00:00), += (00:00:00), +resetAndStop (00:00:00), +; (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +removeEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +resetAndStop (00:00:00), +) (00:00:00), +; (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +initRandomArray (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +renderBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +window (00:00:00), +. (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +input (00:00:00), +" (00:00:00), +, (00:00:00), +function (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +e (00:00:00), +. (00:00:00), +target (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +window (00:00:00), +. (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Segoe (00:00:00), +UI (00:00:00), +' (00:00:00), +, (00:00:00), +Tahoma (00:00:00), +, (00:00:00), +Geneva (00:00:00), +, (00:00:00), +Verdana (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +135deg (00:00:00), +, (00:00:00), +# (00:00:00), +667eea (00:00:00), +0 (00:00:00), +% (00:00:00), +, (00:00:00), +# (00:00:00), +764ba2 (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +h1 (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +4px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +controls (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +15px (00:00:00), +25px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +15px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +wrap (00:00:00), +: (00:00:00), +wrap (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +speed (00:00:00), +- (00:00:00), +control (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +12px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +speed (00:00:00), +- (00:00:00), +control (00:00:00), +label (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speedSlider (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speedValue (00:00:00), +{ (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +45px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +764ba2 (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +reset (00:00:00), +- (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +135deg (00:00:00), +, (00:00:00), +# (00:00:00), +667eea (00:00:00), +0 (00:00:00), +% (00:00:00), +, (00:00:00), +# (00:00:00), +764ba2 (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +padding (0</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J100" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000035010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>+lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +| (00:00:00), +Bubble (00:00:00), +Sort (00:00:00), +with (00:00:00), +Motorcycle (00:00:00), +Ride (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +· (00:00:00), +Bubble (00:00:00), +Sort (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +control (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +⏩ (00:00:00), +Animation (00:00:00), +speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +0 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +200 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +80 (00:00:00), +" (00:00:00), +step (00:00:00), += (00:00:00), +" (00:00:00), +5 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +&gt; (00:00:00), +80 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +button (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +resetBtn (00:00:00), +" (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +reset (00:00:00), +- (00:00:00), +button (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🔄 (00:00:00), +New (00:00:00), +random (00:00:00), +array (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +button (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&gt; (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +bars (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycleZone (00:00:00), +" (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +zone (00:00:00), +" (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +run (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +info (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +&gt; (00:00:00), +✅ (00:00:00), +Sorting (00:00:00), +completed (00:00:00), +→ (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +motorcycle (00:00:00), +races (00:00:00), +across (00:00:00), +the (00:00:00), +bars (00:00:00), +from (00:00:00), +left (00:00:00), +to (00:00:00), +right (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +&gt; (00:00:00), +⚡ (00:00:00), +Speed (00:00:00), +slider (00:00:00), +adjusts (00:00:00), +delay (00:00:00), +between (00:00:00), +comparisons (00:00:00), +( (00:00:00), +lower (00:00:00), += (00:00:00), +faster (00:00:00), +) (00:00:00), +. (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L100" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000036010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-# (00:00:42), -vis (00:00:43), -- (00:00:44), -123456 (00:00:45), -{ (00:00:46), -height (00:00:47), -: (00:00:48), -200px (00:00:49), -; (00:00:50), -display (00:00:51), -: (00:00:52), -flex (00:00:53), -; (00:00:54), -align (00:00:55), -- (00:00:56), -items (00:00:57), -: (00:00:58), -flex (00:00:59), -- (00:01:00), -end (00:01:01), -; (00:01:02), -} (00:01:03), -7px (00:01:09), -height (00:01:11), -: (00:01:12), -100 (00:01:13), -% (00:01:14), -; (00:01:15), -background (00:01:16), -- (00:01:17), -color (00:01:18), -: (00:01:19), -black (00:01:20), -; (00:01:21), -margin (00:01:22), -: (00:01:23), -0px (00:01:24), -1px (00:01:25), -; (00:01:26), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Segoe (00:00:00), +UI (00:00:00), +' (00:00:00), +, (00:00:00), +Tahoma (00:00:00), +, (00:00:00), +Geneva (00:00:00), +, (00:00:00), +Verdana (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +135deg (00:00:00), +, (00:00:00), +# (00:00:00), +667eea (00:00:00), +0 (00:00:00), +% (00:00:00), +, (00:00:00), +# (00:00:00), +764ba2 (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +h1 (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +4px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +controls (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +15px (00:00:00), +25px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +15px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +wrap (00:00:00), +: (00:00:00), +wrap (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +speed (00:00:00), +- (00:00:00), +control (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +12px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +speed (00:00:00), +- (00:00:00), +control (00:00:00), +label (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speedSlider (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speedValue (00:00:00), +{ (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +45px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +764ba2 (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +reset (00:00:00), +- (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +135deg (00:00:00), +, (00:00:00), +# (00:00:00), +667eea (00:00:00), +0 (00:00:00), +% (00:00:00), +, (00:00:00), +# (00:00:00), +764ba2 (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +8px (00:00:00), +20px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +transform (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +, (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +reset (00:00:00), +- (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +1 (00:00:00), +. (00:00:00), +05 (00:00:00), +) (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +12px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +rgba (00:00:00), +( (00:00:00), +255 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +95 (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +8px (00:00:00), +25px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +bars (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +350px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +} (00:00:00), +12px (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +180deg (00:00:00), +, (00:00:00), +# (00:00:00), +667eea (00:00:00), +0 (00:00:00), +% (00:00:00), +, (00:00:00), +# (00:00:00), +764ba2 (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +4px (00:00:00), +0 (00:00:00), +0 (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +height (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +ease (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +1px (00:00:00), +3px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +zone (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +overflow (00:00:00), +: (00:00:00), +visible (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +run (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +32px (00:00:00), +; (00:00:00), +animation (00:00:00), +: (00:00:00), +rideAcross (00:00:00), +2s (00:00:00), +linear (00:00:00), +forwards (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +drop (00:00:00), +- (00:00:00), +shadow (00:00:00), +( (00:00:00), +2px (00:00:00), +2px (00:00:00), +4px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +@ (00:00:00), +keyframes (00:00:00), +rideAcross (00:00:00), +{ (00:00:00), +0 (00:00:00), +% (00:00:00), +{ (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +40px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +49 (00:00:00), +% (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +50 (00:00:00), +% (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +- (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +100 (00:00:00), +% (00:00:00), +{ (00:00:00), +left (00:00:00), +: (00:00:00), +calc (00:00:00), +( (00:00:00), +100 (00:00:00), +% (00:00:00), ++ (00:00:00), +20px (00:00:00), +) (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +- (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +. (00:00:00), +info (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +rgba (00:00:00), +( (00:00:00), +255 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +9 (00:00:00), +) (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +12px (00:00:00), +25px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +align (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +333 (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +2px (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +info (00:00:00), +p (00:00:00), +{ (00:00:00), +margin (00:00:00), +: (00:00:00), +5px (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00), +@ (00:00:00), +media (00:00:00), +( (00:00:00), +max (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +768px (00:00:00), +) (00:00:00), +{ (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +controls (00:00:00), +{ (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +15px (00:00:00), +; (00:00:00), +} (00:00:00), +h1 (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +24px (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N100" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000037010000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>-const (00:02:09), -count (00:02:10), -= (00:02:11), -50 (00:02:12), -; (00:02:13), -const (00:02:14), -array (00:02:15), -= (00:02:16), -new (00:02:17), -Array (00:02:18), -( (00:02:19), -count (00:02:20), -) (00:02:21), -; (00:02:22), -for (00:02:23), -( (00:02:24), -let (00:02:25), -i (00:02:26), -= (00:02:27), -0 (00:02:28), -; (00:02:29), -i (00:02:30), -&lt; (00:02:31), -count (00:02:32), -; (00:02:33), -i (00:02:34), -+ (00:02:35), -+ (00:02:36), -) (00:02:37), -{ (00:02:38), -array (00:02:39), -[ (00:02:40), -i (00:02:41), -] (00:02:42), -= (00:02:43), -Math (00:02:44), -. (00:02:45), -random (00:02:46), -( (00:02:47), -) (00:02:48), -; (00:02:49), -} (00:02:57), -const (00:02:58), -visualizer (00:02:59), -= (00:03:00), -document (00:03:01), -. (00:03:02), -getElementById (00:03:03), -( (00:03:04), -" (00:03:05), -vis (00:03:06), -- (00:03:07), -123456 (00:03:08), -" (00:03:09), -) (00:03:10), -; (00:03:11), -for (00:03:12), -( (00:03:13), -let (00:03:14), -i (00:03:15), -= (00:03:16), -0 (00:03:17), -; (00:03:18), -i (00:03:19), -&lt; (00:03:20), -array (00:03:21), -. (00:03:22), -length (00:03:23), -; (00:03:24), -i (00:03:25), -+ (00:03:26), -+ (00:03:27), -) (00:03:28), -{ (00:03:29), -const (00:03:30), -bar (00:03:31), -= (00:03:32), -document (00:03:33), -. (00:03:34), -createElement (00:03:35), -( (00:03:36), -" (00:03:37), -div (00:03:38), -" (00:03:39), -) (00:03:40), -; (00:03:41), -visualizer (00:03:42), -. (00:03:43), -appendChild (00:03:44), -( (00:03:45), -bar (00:03:46), -) (00:03:47), -; (00:03:48), -bar (00:03:49), -. (00:03:50), -classList (00:03:51), -. (00:03:52), -add (00:03:53), -( (00:03:54), -" (00:03:55), -bar (00:03:56), -" (00:03:57), -) (00:03:58), -; (00:03:59), -bar (00:04:00), -. (00:04:01), -style (00:04:02), -. (00:04:03), -height (00:04:04), -= (00:04:05), -array (00:04:06), -[ (00:04:07), -i (00:04:08), -] (00:04:09), -* (00:04:10), -100 (00:04:11), -+ (00:04:12), -" (00:04:13), -% (00:04:14), -" (00:04:15), -; (00:04:16), -} (00:04:36), -bubbleSort (00:04:37), -( (00:04:38), -array (00:04:39), -) (00:04:40), -; (00:04:41), -function (00:04:42), -updateBars (00:04:43), -( (00:04:44), -) (00:04:45), -{ (00:04:46), -const (00:04:47), -bars (00:04:48), -= (00:04:49), -document (00:04:50), -. (00:04:51), -getElementsByClassName (00:04:52), -( (00:04:53), -" (00:04:54), -bar (00:04:55), -" (00:04:56), -) (00:04:57), -; (00:04:58), -for (00:04:59), -( (00:05:00), -let (00:05:01), -i (00:05:02), -= (00:05:03), -0 (00:05:04), -; (00:05:05), -i (00:05:06), -&lt; (00:05:07), -bars (00:05:08), -. (00:05:09), -length (00:05:10), -; (00:05:11), -i (00:05:12), -+ (00:05:13), -+ (00:05:14), -) (00:05:15), -{ (00:05:16), -bars (00:05:17), -[ (00:05:18), -i (00:05:19), -] (00:05:20), -. (00:05:21), -style (00:05:22), -. (00:05:23), -height (00:05:24), -= (00:05:25), -array (00:05:26), -[ (00:05:27), -i (00:05:28), -] (00:05:29), -* (00:05:30), -100 (00:05:31), -+ (00:05:32), -" (00:05:33), -% (00:05:34), -" (00:05:35), -; (00:05:36), -} (00:05:37), -} (00:05:38), -bubbleSort (00:05:41), -var (00:05:48), -arr (00:06:02), -. (00:06:03), -length (00:06:04), -aux (00:06:27), -aux (00:06:53), -100 (00:07:14), +const (00:00:00), +count (00:00:00), += (00:00:00), +45 (00:00:00), +; (00:00:00), +let (00:00:00), +array (00:00:00), += (00:00:00), +new (00:00:00), +Array (00:00:00), +( (00:00:00), +count (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +let (00:00:00), +currentSortingPromise (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +let (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +80 (00:00:00), +; (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedSlider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedValue (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +resetBtn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +resetBtn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motorcycleZone (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycleZone (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +initRandomArray (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +Math (00:00:00), +. (00:00:00), +random (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +renderBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +while (00:00:00), +( (00:00:00), +visualizer (00:00:00), +. (00:00:00), +firstChild (00:00:00), +) (00:00:00), +{ (00:00:00), +visualizer (00:00:00), +. (00:00:00), +removeChild (00:00:00), +( (00:00:00), +visualizer (00:00:00), +. (00:00:00), +firstChild (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +bar (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +&amp; (00:00:00), +&amp; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +existingRun (00:00:00), += (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +querySelector (00:00:00), +( (00:00:00), +" (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +run (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +existingRun (00:00:00), +) (00:00:00), +{ (00:00:00), +existingRun (00:00:00), +. (00:00:00), +remove (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +animateMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motorcycleDiv (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +run (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +motorcycleDiv (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +barsContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +querySelector (00:00:00), +( (00:00:00), +" (00:00:00), +. (00:00:00), +bars (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +containerWidth (00:00:00), += (00:00:00), +barsContainer (00:00:00), +? (00:00:00), +barsContainer (00:00:00), +. (00:00:00), +clientWidth (00:00:00), +: (00:00:00), +800 (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +animation (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +styleId (00:00:00), += (00:00:00), +" (00:00:00), +dynamic (00:00:00), +- (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +keyframes (00:00:00), +" (00:00:00), +; (00:00:00), +let (00:00:00), +styleTag (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +styleId (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +styleTag (00:00:00), +) (00:00:00), +{ (00:00:00), +styleTag (00:00:00), +. (00:00:00), +remove (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +styleTag (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +style (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +styleTag (00:00:00), +. (00:00:00), +id (00:00:00), += (00:00:00), +styleId (00:00:00), +; (00:00:00), +styleTag (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +` (00:00:00), +@ (00:00:00), +keyframes (00:00:00), +rideAcrossDynamic (00:00:00), +{ (00:00:00), +0 (00:00:00), +% (00:00:00), +{ (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +50px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +45 (00:00:00), +% (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +50 (00:00:00), +% (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +- (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +100 (00:00:00), +% (00:00:00), +{ (00:00:00), +left (00:00:00), +: (00:00:00), +$ (00:00:00), +{ (00:00:00), +containerWidth (00:00:00), ++ (00:00:00), +30 (00:00:00), +} (00:00:00), +px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +- (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +` (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +head (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +styleTag (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +animation (00:00:00), += (00:00:00), +" (00:00:00), +rideAcrossDynamic (00:00:00), +1 (00:00:00), +. (00:00:00), +8s (00:00:00), +cubic (00:00:00), +- (00:00:00), +bezier (00:00:00), +( (00:00:00), +0 (00:00:00), +. (00:00:00), +25 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +46 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +45 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +94 (00:00:00), +) (00:00:00), +forwards (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +onFinish (00:00:00), += (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +) (00:00:00), +{ (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +, (00:00:00), +2000 (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +removeEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +animationend (00:00:00), +" (00:00:00), +, (00:00:00), +onFinish (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +animationend (00:00:00), +" (00:00:00), +, (00:00:00), +onFinish (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +bubbleSortVisual (00:00:00), +let (00:00:00), +len (00:00:00), += (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +let (00:00:00), +swapped (00:00:00), +; (00:00:00), +len (00:00:00), +if (00:00:00), +( (00:00:00), +! (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +throw (00:00:00), +new (00:00:00), +Error (00:00:00), +( (00:00:00), +" (00:00:00), +Sorting (00:00:00), +cancelled (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +temp (00:00:00), +temp (00:00:00), +globalSpeed (00:00:00), +len (00:00:00), +- (00:00:00), +- (00:00:00), +async (00:00:00), +function (00:00:00), +startSorting (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +disabled (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +try (00:00:00), +{ (00:00:00), +await (00:00:00), +bubbleSortVisual (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +animateMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +error (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +Sorting (00:00:00), +interrupted (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +error (00:00:00), +. (00:00:00), +message (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +finally (00:00:00), +{ (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +resetAndStop (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +initRandomArray (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +renderBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +setupSpeedSlider (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +input (00:00:00), +" (00:00:00), +, (00:00:00), +function (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +e (00:00:00), +. (00:00:00), +target (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +change (00:00:00), +" (00:00:00), +, (00:00:00), +function (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +e (00:00:00), +. (00:00:00), +target (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +resetAndStop (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +sortBtn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +button (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +⚡ (00:00:00), +Start (00:00:00), +Bubble (00:00:00), +Sort (00:00:00), +" (00:00:00), +; (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +reset (00:00:00), +- (00:00:00), +button (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +background (00:00:00), += (00:00:00), +" (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +135deg (00:00:00), +, (00:00:00), +# (00:00:00), +f093fb (00:00:00), +0 (00:00:00), +% (00:00:00), +, (00:00:00), +# (00:00:00), +f5576c (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +controlsDiv (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +querySelector (00:00:00), +( (00:00:00), +" (00:00:00), +. (00:00:00), +controls (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +controlsDiv (00:00:00), +) (00:00:00), +{ (00:00:00), +controlsDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +sortBtn (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +async (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +startSorting (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +originalReset (00:00:00), += (00:00:00), +resetAndStop (00:00:00), +; (00:00:00), +window (00:00:00), +. (00:00:00), +resetAndStop (00:00:00), += (00:00:00), +resetAndStop (00:00:00), +; (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +removeEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +resetAndStop (00:00:00), +) (00:00:00), +; (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +initRandomArray (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +renderBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +window (00:00:00), +. (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +input (00:00:00), +" (00:00:00), +, (00:00:00), +function (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +e (00:00:00), +. (00:00:00), +target (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +window (00:00:00), +. (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X100" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000038010000}">
       <text>
         <r>
           <rPr>
@@ -3505,7 +4401,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="414">
   <si>
     <t>ID</t>
   </si>
@@ -3609,6 +4505,9 @@
     <t>Bruce Wayne</t>
   </si>
   <si>
+    <t>🪪</t>
+  </si>
+  <si>
     <t>" (x30), #, % (x2), ( (x31), ) (x31), * (x2), + (x12), , (x2), - (x12), . (x31), 0 (x5), 0px, 1 (x4), 10 (x2), 100 (x3), 123456 (x2), 150px, 1px, 200px, 2s, 40px, 50 (x2), 500, 510, 7px, : (x12), ; (x56), &lt; (x4), = (x30), &gt; (x4), Array, Math, Promise, Speed, [ (x10), ] (x10), _ (x3), absolute, add (x2), align (x2), animateMoto (x2), appendChild (x2), arr (x8), array (x6), async, await, background, bar (x7), bars (x3), black, body (x2), bubbleSort (x2), center, classList (x2), clearInterval, color, column, const (x10), count (x3), createElement (x2), css, direction, display (x2), div (x2), do, document (x6), end, false, flex (x4), font, for (x4), function (x4), getElementById (x2), getElementsByClassName, height (x3), href, i (x22), id, if (x2), innerWidth, input, interval (x2), items (x2), js, label (x2), left (x2), length (x3), let (x7), linear, link, margin, max, min, moto (x9), new (x2), onchange, position, px, random, range, rel, remove, resolve (x2), script, setInterval, setTimeout, size, sliderValue (x2), speed (x3), speedSlider (x2), src, step (x2), style (x4), stylesheet, swapped (x4), temp (x2), textContent, top, transition, true, type, updateBars (x2), updateSpeed (x2), value (x2), var (x3), vis (x2), visualizer (x2), while, width, window, x (x4), { (x16), } (x16), ️, 🏍</t>
   </si>
   <si>
@@ -3630,12 +4529,12 @@
     <t>oninput, !var_speed</t>
   </si>
   <si>
-    <t>1100</t>
-  </si>
-  <si>
     <t>Tony Stark</t>
   </si>
   <si>
+    <t>✅</t>
+  </si>
+  <si>
     <t>" (x32), #, % (x3), ( (x28), ) (x28), * (x2), + (x12), , (x2), - (x11), . (x29), 0 (x4), 0px (x2), 1 (x4), 10, 100 (x3), 123456 (x2), 1px, 200px, 31px, 35px, 5, 50 (x2), 500, 7px, 8, : (x11), ; (x53), &lt; (x4), = (x31), &gt; (x5), Array, Math, Promise, Speed, UTF, [ (x10), ] (x10), absolute, add, align (x2), appendChild (x2), arr (x8), array (x6), async, aux (x2), await, background, bar (x7), bars (x3), bike (x8), black, body, bubbleSort (x2), center, changeSpeed (x2), charset, classList, clearInterval, color, column, const (x8), count (x3), createElement (x2), css, direction, display (x2), div (x2), do, document (x4), end, false, flex (x4), fontSize, for (x4), function (x4), getElementById, getElementsByClassName, height (x4), href, i (x22), if (x2), innerHTML, input, items (x2), js, label (x2), left (x2), length (x3), let (x6), link, margin, max, meta, min, move (x2), new (x2), offsetWidth, oninput, position (x6), px, random, range, rel, relative, resolve (x2), script, setInterval, setTimeout, showMotorcycle (x2), speed (x4), src, style (x7), stylesheet, swapped (x3), this, top, true, type, updateBars (x2), value (x4), var, vis (x2), visualizer (x4), while, width, { (x15), } (x15), ️, 🏍</t>
   </si>
   <si>
@@ -3654,9 +4553,6 @@
     <t>1/1</t>
   </si>
   <si>
-    <t>0010</t>
-  </si>
-  <si>
     <t>Alec Holland</t>
   </si>
   <si>
@@ -3675,9 +4571,6 @@
     <t>-var (00:05:48), -const (00:06:26), -aux (00:06:27), -aux (00:06:53), -100 (00:07:14), +let (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +function (00:00:00), +changeSpeed (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +let (00:00:00), +swapped (00:00:00), +; (00:00:00), +let (00:00:00), +temp (00:00:00), +temp (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bike (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bike (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +bike (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +bike (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +barHeight (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +40 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00)</t>
   </si>
   <si>
-    <t>1110</t>
-  </si>
-  <si>
     <t>Sam Wilson</t>
   </si>
   <si>
@@ -3732,9 +4625,6 @@
     <t>!var_speed</t>
   </si>
   <si>
-    <t>0100</t>
-  </si>
-  <si>
     <t>Lucius Fox</t>
   </si>
   <si>
@@ -3786,9 +4676,6 @@
     <t>-var (00:05:48), -100 (00:07:14), +let (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +20 (00:00:00), +; (00:00:00), +function (00:00:00), +changeSpeed (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +async (00:00:00), +function (00:00:00), +motorcycleRide (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +motor (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motor (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +motor (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +motor (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +( (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetTop (00:00:00), +- (00:00:00), +motor (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +80 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +let (00:00:00), +swapped (00:00:00), +; (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +await (00:00:00), +motorcycleRide (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00)</t>
   </si>
   <si>
-    <t>0110</t>
-  </si>
-  <si>
     <t>Leonard Snart</t>
   </si>
   <si>
@@ -3816,9 +4703,6 @@
     <t>oninput</t>
   </si>
   <si>
-    <t>1101</t>
-  </si>
-  <si>
     <t>Scott Lang</t>
   </si>
   <si>
@@ -3843,9 +4727,6 @@
     <t>-100 (00:07:14), +let (00:00:00), +speed (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +speed (00:00:00), +MotoMovesIt (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +Motorcycle (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +Motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +Motorcycle (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +MovedBars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +MotoMovesIt (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +1 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +MovedBars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +50 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +MovedBars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +Motorcycle (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +var (00:00:00), +slider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +MySlider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +var (00:00:00), +output (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +test (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +output (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +slider (00:00:00), +. (00:00:00), +value (00:00:00), +; (00:00:00), +speed (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +slider (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +slider (00:00:00), +. (00:00:00), +oninput (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +output (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +; (00:00:00), +speed (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
   </si>
   <si>
-    <t>0000</t>
-  </si>
-  <si>
     <t>Gwen Stacy</t>
   </si>
   <si>
@@ -3888,9 +4769,6 @@
     <t>-const (00:02:09), -count (00:02:10), -= (00:02:11), -50 (00:02:12), -; (00:02:13), -const (00:02:14), -array (00:02:15), -= (00:02:16), -new (00:02:17), -Array (00:02:18), -( (00:02:19), -count (00:02:20), -) (00:02:21), -; (00:02:22), -for (00:02:23), -( (00:02:24), -let (00:02:25), -i (00:02:26), -= (00:02:27), -0 (00:02:28), -; (00:02:29), -i (00:02:30), -&lt; (00:02:31), -count (00:02:32), -; (00:02:33), -i (00:02:34), -+ (00:02:35), -+ (00:02:36), -) (00:02:37), -{ (00:02:38), -array (00:02:39), -[ (00:02:40), -i (00:02:41), -] (00:02:42), -= (00:02:43), -Math (00:02:44), -. (00:02:45), -random (00:02:46), -( (00:02:47), -) (00:02:48), -; (00:02:49), -} (00:02:57), -const (00:02:58), -visualizer (00:02:59), -= (00:03:00), -document (00:03:01), -. (00:03:02), -getElementById (00:03:03), -( (00:03:04), -" (00:03:05), -vis (00:03:06), -- (00:03:07), -123456 (00:03:08), -" (00:03:09), -) (00:03:10), -; (00:03:11), -for (00:03:12), -( (00:03:13), -let (00:03:14), -i (00:03:15), -= (00:03:16), -0 (00:03:17), -; (00:03:18), -i (00:03:19), -&lt; (00:03:20), -array (00:03:21), -. (00:03:22), -length (00:03:23), -; (00:03:24), -i (00:03:25), -+ (00:03:26), -+ (00:03:27), -) (00:03:28), -{ (00:03:29), -const (00:03:30), -bar (00:03:31), -= (00:03:32), -document (00:03:33), -. (00:03:34), -createElement (00:03:35), -( (00:03:36), -" (00:03:37), -div (00:03:38), -" (00:03:39), -) (00:03:40), -; (00:03:41), -visualizer (00:03:42), -. (00:03:43), -appendChild (00:03:44), -( (00:03:45), -bar (00:03:46), -) (00:03:47), -; (00:03:48), -bar (00:03:49), -. (00:03:50), -classList (00:03:51), -. (00:03:52), -add (00:03:53), -( (00:03:54), -" (00:03:55), -bar (00:03:56), -" (00:03:57), -) (00:03:58), -; (00:03:59), -bar (00:04:00), -. (00:04:01), -style (00:04:02), -. (00:04:03), -height (00:04:04), -= (00:04:05), -array (00:04:06), -[ (00:04:07), -i (00:04:08), -] (00:04:09), -* (00:04:10), -100 (00:04:11), -+ (00:04:12), -" (00:04:13), -% (00:04:14), -" (00:04:15), -; (00:04:16), -} (00:04:36), -bubbleSort (00:04:37), -( (00:04:38), -array (00:04:39), -) (00:04:40), -; (00:04:41), -function (00:04:42), -updateBars (00:04:43), -( (00:04:44), -) (00:04:45), -{ (00:04:46), -const (00:04:47), -bars (00:04:48), -= (00:04:49), -document (00:04:50), -. (00:04:51), -getElementsByClassName (00:04:52), -( (00:04:53), -" (00:04:54), -bar (00:04:55), -" (00:04:56), -) (00:04:57), -; (00:04:58), -for (00:04:59), -( (00:05:00), -let (00:05:01), -i (00:05:02), -= (00:05:03), -0 (00:05:04), -; (00:05:05), -i (00:05:06), -&lt; (00:05:07), -bars (00:05:08), -. (00:05:09), -length (00:05:10), -; (00:05:11), -i (00:05:12), -+ (00:05:13), -+ (00:05:14), -) (00:05:15), -{ (00:05:16), -bars (00:05:17), -[ (00:05:18), -i (00:05:19), -] (00:05:20), -. (00:05:21), -style (00:05:22), -. (00:05:23), -height (00:05:24), -= (00:05:25), -array (00:05:26), -[ (00:05:27), -i (00:05:28), -] (00:05:29), -* (00:05:30), -100 (00:05:31), -+ (00:05:32), -" (00:05:33), -% (00:05:34), -" (00:05:35), -; (00:05:36), -} (00:05:37), -} (00:05:38), -async (00:05:39), -function (00:05:40), -bubbleSort (00:05:41), -( (00:05:42), -arr (00:05:43), -) (00:05:44), -{ (00:05:45), -do (00:05:46), -{ (00:05:47), -var (00:05:48), -swapped (00:05:49), -= (00:05:50), -false (00:05:51), -; (00:05:52), -for (00:05:53), -( (00:05:54), -let (00:05:55), -i (00:05:56), -= (00:05:57), -1 (00:05:58), -; (00:05:59), -i (00:06:00), -&lt; (00:06:01), -arr (00:06:02), -. (00:06:03), -length (00:06:04), -; (00:06:05), -i (00:06:06), -+ (00:06:07), -+ (00:06:08), -) (00:06:09), -{ (00:06:10), -if (00:06:11), -( (00:06:12), -arr (00:06:13), -[ (00:06:14), -i (00:06:15), -- (00:06:16), -1 (00:06:17), -] (00:06:18), -&gt; (00:06:19), -arr (00:06:20), -[ (00:06:21), -i (00:06:22), -] (00:06:23), -) (00:06:24), -{ (00:06:25), -const (00:06:26), -aux (00:06:27), -= (00:06:28), -arr (00:06:29), -[ (00:06:30), -i (00:06:31), -- (00:06:32), -1 (00:06:33), -] (00:06:34), -; (00:06:35), -arr (00:06:36), -[ (00:06:37), -i (00:06:38), -- (00:06:39), -1 (00:06:40), -] (00:06:41), -= (00:06:42), -arr (00:06:43), -[ (00:06:44), -i (00:06:45), -] (00:06:46), -; (00:06:47), -arr (00:06:48), -[ (00:06:49), -i (00:06:50), -] (00:06:51), -= (00:06:52), -aux (00:06:53), -; (00:06:54), -swapped (00:06:55), -= (00:06:56), -true (00:06:57), -; (00:06:58), -updateBars (00:06:59), -( (00:07:00), -) (00:07:01), -; (00:07:02), -await (00:07:03), -new (00:07:04), -Promise (00:07:05), -( (00:07:06), -resolve (00:07:07), -= (00:07:08), -&gt; (00:07:09), -setTimeout (00:07:10), -( (00:07:11), -resolve (00:07:12), -, (00:07:13), -100 (00:07:14), -) (00:07:15), -) (00:07:16), -; (00:07:17), -} (00:07:18), -} (00:07:19), -} (00:07:20), -while (00:07:21), -( (00:07:22), -swapped (00:07:23), -) (00:07:24), -; (00:07:25), -} (00:07:26), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +function (00:00:00), +updateSpeed (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +let (00:00:00), +values (00:00:00), += (00:00:00), +[ (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +barsContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +bars (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +generateBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +values (00:00:00), += (00:00:00), +[ (00:00:00), +] (00:00:00), +; (00:00:00), +barsContainer (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +" (00:00:00), +" (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +20 (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +let (00:00:00), +height (00:00:00), += (00:00:00), +Math (00:00:00), +. (00:00:00), +floor (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +random (00:00:00), +( (00:00:00), +) (00:00:00), +* (00:00:00), +250 (00:00:00), +) (00:00:00), ++ (00:00:00), +20 (00:00:00), +; (00:00:00), +values (00:00:00), +. (00:00:00), +push (00:00:00), +( (00:00:00), +height (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00), +bar (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +height (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +barsContainer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +bar (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +generateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +startSort (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +values (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +j (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +j (00:00:00), +&lt; (00:00:00), +values (00:00:00), +. (00:00:00), +length (00:00:00), +- (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +; (00:00:00), +j (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +values (00:00:00), +[ (00:00:00), +j (00:00:00), +] (00:00:00), +&gt; (00:00:00), +values (00:00:00), +[ (00:00:00), +j (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +let (00:00:00), +temp (00:00:00), += (00:00:00), +values (00:00:00), +[ (00:00:00), +j (00:00:00), +] (00:00:00), +; (00:00:00), +values (00:00:00), +[ (00:00:00), +j (00:00:00), +] (00:00:00), += (00:00:00), +values (00:00:00), +[ (00:00:00), +j (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +values (00:00:00), +[ (00:00:00), +j (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), += (00:00:00), +temp (00:00:00), +; (00:00:00), +bars (00:00:00), +[ (00:00:00), +j (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +values (00:00:00), +[ (00:00:00), +j (00:00:00), +] (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +bars (00:00:00), +[ (00:00:00), +j (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +values (00:00:00), +[ (00:00:00), +j (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +animateMotorcycleOnBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +async (00:00:00), +function (00:00:00), +animateMotorcycleOnBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +let (00:00:00), +rect (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +getBoundingClientRect (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00), +x (00:00:00), += (00:00:00), +rect (00:00:00), +. (00:00:00), +left (00:00:00), ++ (00:00:00), +rect (00:00:00), +. (00:00:00), +width (00:00:00), +/ (00:00:00), +2 (00:00:00), +- (00:00:00), +20 (00:00:00), +; (00:00:00), +let (00:00:00), +y (00:00:00), += (00:00:00), +rect (00:00:00), +. (00:00:00), +top (00:00:00), +- (00:00:00), +40 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +x (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +y (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +150 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00)</t>
   </si>
   <si>
-    <t>1111</t>
-  </si>
-  <si>
     <t>Steve Rogers</t>
   </si>
   <si>
@@ -3928,9 +4806,6 @@
   </si>
   <si>
     <t>-100 (00:07:14), +let (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +const (00:00:00), +slider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +myRange (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +slider (00:00:00), +. (00:00:00), +oninput (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +speed (00:00:00), += (00:00:00), +101 (00:00:00), +- (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +; (00:00:00), +} (00:00:00), +speed (00:00:00), +var (00:00:00), +slider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +myRange (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +var (00:00:00), +output (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +demo (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +output (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +slider (00:00:00), +. (00:00:00), +value (00:00:00), +; (00:00:00), +slider (00:00:00), +. (00:00:00), +oninput (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +output (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +; (00:00:00), +} (00:00:00)</t>
-  </si>
-  <si>
-    <t>0001</t>
   </si>
   <si>
     <t>Johnny Storm</t>
@@ -4208,6 +5083,9 @@
     <t>Bruce Banner</t>
   </si>
   <si>
+    <t>◼️</t>
+  </si>
+  <si>
     <t>" (x36), #, % (x4), ( (x37), ) (x37), * (x2), + (x16), , (x2), - (x16), . (x35), / (x2), 0 (x4), 0px, 1 (x5), 10 (x2), 100 (x4), 120, 123456 (x3), 1px, 2, 200px, 25px, 300, 4, 50 (x2), 7px, 8, : (x14), ; (x61), &lt; (x5), = (x33), &gt; (x4), Array, Math, Promise (x2), Speed, UTF, [ (x11), ] (x11), absolute, add (x2), align (x2), appendChild (x2), arr (x8), array (x6), async (x2), aux (x2), await (x2), background, bar (x12), bars (x6), bike (x6), black, body, bottom, bubbleSort (x2), center, charset, classList (x2), color, column, const (x13), count (x3), createElement (x2), css, direction, display (x2), div (x2), do, document (x7), end, false, flex (x4), font, for (x5), function (x5), getElementById (x3), getElementsByClassName (x2), height (x4), href, i (x26), id, if, input, items (x2), js, label (x2), left, length (x4), let (x6), link, margin, max (x2), meta, min, motorcycle (x2), ms (x2), new (x3), offsetHeight, offsetLeft, offsetWidth, oninput, position (x2), px (x2), random, range, rel, relative, resolve (x4), return, scaleX, script, setTimeout (x2), showMotorcycleRide (x2), size, sleep (x2), speed (x3), speedSlider (x5), src, style (x4), styles, stylesheet, swapped (x3), textContent, this (x2), transform, translateX, true, type, updateBars (x2), value (x2), var, vis (x3), visualizer (x4), while, width, x (x2), y (x2), { (x16), } (x16), ️, 🏍</t>
   </si>
   <si>
@@ -4337,9 +5215,6 @@
     <t>-const (00:02:09), -count (00:02:10), -= (00:02:11), -50 (00:02:12), -; (00:02:13), -const (00:02:14), -new (00:02:17), -Array (00:02:18), -( (00:02:19), -count (00:02:20), -) (00:02:21), -for (00:02:23), -( (00:02:24), -let (00:02:25), -i (00:02:26), -= (00:02:27), -0 (00:02:28), -; (00:02:29), -i (00:02:30), -&lt; (00:02:31), -count (00:02:32), -; (00:02:33), -i (00:02:34), -+ (00:02:35), -+ (00:02:36), -) (00:02:37), -{ (00:02:38), -array (00:02:39), -[ (00:02:40), -i (00:02:41), -] (00:02:42), -= (00:02:43), -Math (00:02:44), -. (00:02:45), -random (00:02:46), -( (00:02:47), -) (00:02:48), -; (00:02:49), -} (00:02:57), -const (00:02:58), -visualizer (00:02:59), -= (00:03:00), -document (00:03:01), -. (00:03:02), -getElementById (00:03:03), -( (00:03:04), -" (00:03:05), -vis (00:03:06), -- (00:03:07), -123456 (00:03:08), -" (00:03:09), -) (00:03:10), -; (00:03:11), -for (00:03:12), -( (00:03:13), -let (00:03:14), -i (00:03:15), -= (00:03:16), -0 (00:03:17), -; (00:03:18), -i (00:03:19), -&lt; (00:03:20), -array (00:03:21), -. (00:03:22), -length (00:03:23), -; (00:03:24), -i (00:03:25), -+ (00:03:26), -+ (00:03:27), -) (00:03:28), -{ (00:03:29), -const (00:03:30), -bar (00:03:31), -= (00:03:32), -document (00:03:33), -. (00:03:34), -createElement (00:03:35), -( (00:03:36), -" (00:03:37), -div (00:03:38), -" (00:03:39), -) (00:03:40), -; (00:03:41), -visualizer (00:03:42), -. (00:03:43), -appendChild (00:03:44), -( (00:03:45), -bar (00:03:46), -) (00:03:47), -; (00:03:48), -bar (00:03:49), -. (00:03:50), -classList (00:03:51), -. (00:03:52), -add (00:03:53), -( (00:03:54), -" (00:03:55), -bar (00:03:56), -" (00:03:57), -) (00:03:58), -; (00:03:59), -bar (00:04:00), -. (00:04:01), -style (00:04:02), -. (00:04:03), -height (00:04:04), -= (00:04:05), -array (00:04:06), -[ (00:04:07), -i (00:04:08), -] (00:04:09), -* (00:04:10), -100 (00:04:11), -+ (00:04:12), -" (00:04:13), -% (00:04:14), -" (00:04:15), -; (00:04:16), -} (00:04:36), -bubbleSort (00:04:37), -( (00:04:38), -array (00:04:39), -) (00:04:40), -; (00:04:41), -function (00:04:42), -updateBars (00:04:43), -( (00:04:44), -) (00:04:45), -{ (00:04:46), -const (00:04:47), -bars (00:04:48), -= (00:04:49), -document (00:04:50), -. (00:04:51), -getElementsByClassName (00:04:52), -( (00:04:53), -" (00:04:54), -bar (00:04:55), -" (00:04:56), -) (00:04:57), -; (00:04:58), -for (00:04:59), -( (00:05:00), -let (00:05:01), -i (00:05:02), -= (00:05:03), -0 (00:05:04), -; (00:05:05), -i (00:05:06), -&lt; (00:05:07), -bars (00:05:08), -. (00:05:09), -length (00:05:10), -; (00:05:11), -i (00:05:12), -+ (00:05:13), -+ (00:05:14), -) (00:05:15), -{ (00:05:16), -bars (00:05:17), -[ (00:05:18), -i (00:05:19), -] (00:05:20), -. (00:05:21), -style (00:05:22), -. (00:05:23), -height (00:05:24), -= (00:05:25), -array (00:05:26), -[ (00:05:27), -i (00:05:28), -] (00:05:29), -* (00:05:30), -100 (00:05:31), -+ (00:05:32), -" (00:05:33), -% (00:05:34), -" (00:05:35), -; (00:05:36), -} (00:05:37), -} (00:05:38), -async (00:05:39), -function (00:05:40), -bubbleSort (00:05:41), -( (00:05:42), -arr (00:05:43), -) (00:05:44), -{ (00:05:45), -do (00:05:46), -{ (00:05:47), -var (00:05:48), -swapped (00:05:49), -= (00:05:50), -false (00:05:51), -; (00:05:52), -for (00:05:53), -( (00:05:54), -let (00:05:55), -i (00:05:56), -= (00:05:57), -1 (00:05:58), -; (00:05:59), -i (00:06:00), -&lt; (00:06:01), -arr (00:06:02), -. (00:06:03), -length (00:06:04), -; (00:06:05), -i (00:06:06), -+ (00:06:07), -+ (00:06:08), -) (00:06:09), -{ (00:06:10), -if (00:06:11), -( (00:06:12), -arr (00:06:13), -[ (00:06:14), -i (00:06:15), -- (00:06:16), -1 (00:06:17), -] (00:06:18), -&gt; (00:06:19), -arr (00:06:20), -[ (00:06:21), -i (00:06:22), -] (00:06:23), -) (00:06:24), -{ (00:06:25), -const (00:06:26), -aux (00:06:27), -= (00:06:28), -arr (00:06:29), -[ (00:06:30), -i (00:06:31), -- (00:06:32), -1 (00:06:33), -] (00:06:34), -; (00:06:35), -arr (00:06:36), -[ (00:06:37), -i (00:06:38), -- (00:06:39), -1 (00:06:40), -] (00:06:41), -= (00:06:42), -arr (00:06:43), -[ (00:06:44), -i (00:06:45), -] (00:06:46), -; (00:06:47), -arr (00:06:48), -[ (00:06:49), -i (00:06:50), -] (00:06:51), -= (00:06:52), -aux (00:06:53), -; (00:06:54), -swapped (00:06:55), -= (00:06:56), -true (00:06:57), -; (00:06:58), -updateBars (00:06:59), -( (00:07:00), -) (00:07:01), -; (00:07:02), -await (00:07:03), -new (00:07:04), -Promise (00:07:05), -( (00:07:06), -resolve (00:07:07), -= (00:07:08), -&gt; (00:07:09), -setTimeout (00:07:10), -( (00:07:11), -resolve (00:07:12), -, (00:07:13), -100 (00:07:14), -) (00:07:15), -) (00:07:16), -; (00:07:17), -} (00:07:18), -} (00:07:19), -} (00:07:20), -while (00:07:21), -( (00:07:22), -swapped (00:07:23), -) (00:07:24), -; (00:07:25), -} (00:07:26), +let (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +200 (00:00:00), +; (00:00:00), +let (00:00:00), +[ (00:00:00), +] (00:00:00), +function (00:00:00), +changeSpeed (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +value (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +createBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +let (00:00:00), +container (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +bars (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +container (00:00:00), +. (00:00:00), +innerHTML (00:00:00), += (00:00:00), +" (00:00:00), +" (00:00:00), +; (00:00:00), +array (00:00:00), += (00:00:00), +[ (00:00:00), +] (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +20 (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +let (00:00:00), +value (00:00:00), += (00:00:00), +Math (00:00:00), +. (00:00:00), +floor (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +random (00:00:00), +( (00:00:00), +) (00:00:00), +* (00:00:00), +200 (00:00:00), +) (00:00:00), ++ (00:00:00), +20 (00:00:00), +; (00:00:00), +array (00:00:00), +. (00:00:00), +push (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00), +bar (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +value (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +container (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +bar (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +createBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +sleep (00:00:00), +( (00:00:00), +ms (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +ms (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +async (00:00:00), +function (00:00:00), +startSort (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +let (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +j (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +j (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +- (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +; (00:00:00), +j (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +j (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +background (00:00:00), += (00:00:00), +" (00:00:00), +blue (00:00:00), +" (00:00:00), +; (00:00:00), +bars (00:00:00), +[ (00:00:00), +j (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +background (00:00:00), += (00:00:00), +" (00:00:00), +blue (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +sleep (00:00:00), +( (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +array (00:00:00), +[ (00:00:00), +j (00:00:00), +] (00:00:00), +&gt; (00:00:00), +array (00:00:00), +[ (00:00:00), +j (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +let (00:00:00), +temp (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +j (00:00:00), +] (00:00:00), +; (00:00:00), +array (00:00:00), +[ (00:00:00), +j (00:00:00), +] (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +j (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +array (00:00:00), +[ (00:00:00), +j (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), += (00:00:00), +temp (00:00:00), +; (00:00:00), +bars (00:00:00), +[ (00:00:00), +j (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +j (00:00:00), +] (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +bars (00:00:00), +[ (00:00:00), +j (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +j (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +bars (00:00:00), +[ (00:00:00), +j (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +background (00:00:00), += (00:00:00), +" (00:00:00), +black (00:00:00), +" (00:00:00), +; (00:00:00), +bars (00:00:00), +[ (00:00:00), +j (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +background (00:00:00), += (00:00:00), +" (00:00:00), +black (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +showMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +showMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +let (00:00:00), +bike (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bike (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +let (00:00:00), +position (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +let (00:00:00), +move (00:00:00), += (00:00:00), +setInterval (00:00:00), +( (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +position (00:00:00), +&gt; (00:00:00), +window (00:00:00), +. (00:00:00), +innerWidth (00:00:00), +) (00:00:00), +{ (00:00:00), +clearInterval (00:00:00), +( (00:00:00), +move (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +position (00:00:00), ++ (00:00:00), += (00:00:00), +10 (00:00:00), +; (00:00:00), +bike (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +position (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +, (00:00:00), +20 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
   </si>
   <si>
-    <t>0111</t>
-  </si>
-  <si>
     <t>Matt Murdock</t>
   </si>
   <si>
@@ -4469,6 +5344,9 @@
     <t>1000001</t>
   </si>
   <si>
+    <t>🪪⚠️</t>
+  </si>
+  <si>
     <t>! (x2), " (x96), # (x13), $ (x8), ( (x73), ) (x73), * (x2), + (x20), , (x21), - (x47), . (x96), / (x8), 0 (x24), 0deg, 1 (x11), 10 (x3), 100vh, 10px (x3), 12, 120 (x3), 12s, 13, 15px, 16px (x4), 172033, 18, 18px (x3), 190px, 2 (x2), 22, 22px, 24px, 25, 2663ff, 26a269, 28, 280, 28px (x3), 2px, 2s (x2), 30px, 34px, 42, 420px, 45 (x3), 4a7dff, 4px (x2), 500, 50px, 600, 6px, 72, 8, 8deg (x2), 8px (x2), 94vw, 980px, 9aa6c0, : (x63), ; (x139), &lt; (x16), = (x60), &gt; (x17), Animation, Arial, Array, Bars, Bubble (x3), Click (x2), Finished, Generate (x2), Helvetica, Here, Math (x4), New, Number, Promise, Sort (x3), Sorted, Sorting (x3), Start (x3), UTF, [ (x25), ] (x25), _ (x7), ` (x12), absolute, add (x7), again, align (x5), allowed, amount (x2), animateMotorcycle (x2), app (x2), appendChild (x2), aria (x2), async (x2), await (x6), background (x10), bar (x12), barBox (x3), barHeight (x2), bars (x16), body, bold, border (x7), bottom (x2), box (x3), bubbleSort, button (x6), center (x7), charset, class (x2), classList (x9), className (x2), color (x3), comes, comparing (x5), const (x16), content (x4), controls (x3), createElement (x2), css, cursor (x2), dde4f0, device, disabled (x5), display (x3), div (x2), document (x9), drop, ease (x2), eef3fb, en, end, events, f2536d, f4f7fb, f9fbff, false (x4), family, ffb020, filter, flex (x5), floor, font (x4), for (x4), forEach, from, function (x8), gap (x2), generateBars (x3), generateBtn (x5), getBars (x4), getBoundingClientRect (x2), getElementById (x5), gradient, h1, height (x12), hidden, href, i (x13), id (x5), if (x4), index, initial, innerHTML, input (x2), isSorting (x5), items (x3), j (x19), js, justify (x3), label (x5), lang, left (x3), length (x4), let (x7), linear (x2), link, main (x2), margin (x3), markBarsAsSorted (x2), max (x3), meta (x2), milliseconds (x2), min (x5), motorcycle (x11), ms, name, new (x2), newValue (x2), none (x2), not, oldMotorcycle (x3), onchange, onclick (x2), or, overflow, p (x2), padding (x3), pointer (x2), position (x2), push, px (x8), querySelector, querySelectorAll, radius (x4), random, randomHeight (x2), range (x2), rel, relative, remove (x3), resolve (x2), return (x5), rgba (x2), rotate (x3), sans, scale, script, section (x4), serif, setTimeout, shadow (x2), size (x2), sizing, sleep (x6), solid, sort (x3), sortBtn (x5), sorted (x4), span (x2), speed (x8), speedSlider (x2), speedValue (x4), src, status (x3), statusText (x5), step, style (x6), stylesheet, swapping (x5), text (x2), textContent (x6), the (x3), this, to (x2), top, transform (x4), transition (x2), translate (x3), true (x3), type (x2), updateSpeed (x2), value (x2), values (x15), var (x7), viewport, visualizer (x7), visualizerBox (x4), weight, white (x2), width (x6), wrap (x2), x (x3), y (x3), z, { (x37), } (x37), “ (x2), ” (x2), ️, 🏍</t>
   </si>
   <si>
@@ -4517,13 +5395,13 @@
     <t>! (x2), " (x70), # (x20), % (x3), ( (x51), ) (x51), * (x3), + (x18), , (x12), - (x47), . (x70), / (x5), 0 (x15), 05s (x2), 0px (x2), 1 (x7), 10 (x3), 100 (x3), 100vh, 108, 10px, 123456 (x3), 12px, 13px, 14px (x2), 150px, 16213e, 16px, 18px, 1a1a2e, 1px, 200, 200px, 20px (x2), 220px, 255, 28px, 2px (x3), 300, 30px, 36, 40px (x2), 5, 50 (x4), 600px, 6c63ff (x3), 8, 888, 8px (x4), 99, : (x56), ; (x120), &lt; (x13), = (x51), &gt; (x14), Array, Done, Math (x2), Motorcycle, Promise (x3), Sorted, Sorting, Speed, [ (x15), ] (x15), _ (x4), a29bfe, aaa, absolute, accent, add (x2), align (x3), appendChild, arr (x8), array (x6), async (x2), aux (x2), await (x4), background (x4), bar (x12), barCount (x2), barHeight (x2), barLeft (x2), barTopInContainer (x2), bars (x8), block, body, bold, border (x4), bottom (x2), box (x4), bubbleSort (x2), center (x2), classList (x3), color (x6), column, comparing (x3), const (x21), container (x5), containerWidth (x2), controls (x3), count (x3), createElement, css, cursor, delay, direction, display (x8), div (x6), do, document (x12), drop, e0e0ff, e84393, eee, else, end, events, false, family, fd79a8, filter, flex (x6), font (x5), for (x5), function (x4), gap, getElementById (x9), getElementsByClassName (x2), gradient (x2), h1, height (x7), highlightIndices (x2), href, i (x31), id (x6), if (x2), includes, incoming, index, input, items (x3), js, label (x3), left (x5), length (x4), let (x5), letter, linear (x3), link, margin (x5), max (x2), min (x3), moto (x8), motoTop (x2), motorcycle (x3), ms, new (x4), none (x3), offsetHeight (x2), offsetLeft (x2), offsetTop, offsetWidth, onchange, padding (x2), parseInt, pointer (x2), position (x2), px (x3), radius (x2), random, range, rel, relative, remove, resolve (x6), rgba, runMotorcycle (x2), sans, scaleX, script, serif, setTimeout (x3), shadow, size (x3), sizing (x2), slider (x6), spacing, span (x4), speed (x11), speedDisplay (x2), src, status (x5), style (x9), stylesheet, swapped (x3), textContent (x4), this (x2), to (x2), top (x6), transform, transition (x2), true, type, updateBars (x3), value (x3), var (x6), vis (x5), visEl (x4), visHeight (x2), visTop (x2), visualizer (x2), weight, while, width (x4), z, { (x25), } (x25), ️ (x2), 🏍 (x2)</t>
   </si>
   <si>
-    <t>-width (00:01:07), -: (00:01:08), -7px (00:01:09), -; (00:01:10), -height (00:01:11), -: (00:01:12), -100 (00:01:13), -% (00:01:14), -; (00:01:15), -background (00:01:16), -- (00:01:17), -color (00:01:18), -: (00:01:19), -black (00:01:20), -; (00:01:21), -100 (00:07:14), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Speed (00:00:00), +( (00:00:00), +delay (00:00:00), +ms (00:00:00), +) (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +200 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +50 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +" (00:00:00), +&gt; (00:00:00), +50 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +50 (00:00:00), +; (00:00:00), +const (00:00:00), +slider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedDisplay (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +slider (00:00:00), +. (00:00:00), +onchange (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedDisplay (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +highlightIndices (00:00:00), += (00:00:00), +[ (00:00:00), +] (00:00:00), +if (00:00:00), +( (00:00:00), +highlightIndices (00:00:00), +. (00:00:00), +includes (00:00:00), +( (00:00:00), +i (00:00:00), +) (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +comparing (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +remove (00:00:00), +( (00:00:00), +" (00:00:00), +comparing (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Sorting (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +" (00:00:00), +; (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +, (00:00:00), +i (00:00:00), +] (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Sorted (00:00:00), +! (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +Motorcycle (00:00:00), +incoming (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Done (00:00:00), +! (00:00:00), +" (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +container (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +visEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +containerWidth (00:00:00), += (00:00:00), +container (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), +; (00:00:00), +const (00:00:00), +barCount (00:00:00), += (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +barCount (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +barLeft (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), ++ (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +visTop (00:00:00), += (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetTop (00:00:00), +; (00:00:00), +const (00:00:00), +visHeight (00:00:00), += (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +barTopInContainer (00:00:00), += (00:00:00), +visTop (00:00:00), ++ (00:00:00), +( (00:00:00), +visHeight (00:00:00), +- (00:00:00), +barHeight (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motoTop (00:00:00), += (00:00:00), +barTopInContainer (00:00:00), +- (00:00:00), +36 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +( (00:00:00), +barLeft (00:00:00), +- (00:00:00), +10 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +motoTop (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +Math (00:00:00), +. (00:00:00), +max (00:00:00), +( (00:00:00), +10 (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +* (00:00:00), +0 (00:00:00), +. (00:00:00), +5 (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +( (00:00:00), +containerWidth (00:00:00), ++ (00:00:00), +50 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +300 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +" (00:00:00), +- (00:00:00), +40px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +" (00:00:00), +0px (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +1a1a2e (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +eee (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +} (00:00:00), +h1 (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +e0e0ff (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +12px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +label (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +aaa (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +{ (00:00:00), +accent (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +150px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +600px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +220px (00:00:00), +; (00:00:00), +} (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +16213e (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +10px (00:00:00), +8px (00:00:00), +0 (00:00:00), +8px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +, (00:00:00), +# (00:00:00), +a29bfe (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +0 (00:00:00), +0 (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +height (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +. (00:00:00), +comparing (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +fd79a8 (00:00:00), +, (00:00:00), +# (00:00:00), +e84393 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +28px (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +40px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +drop (00:00:00), +- (00:00:00), +shadow (00:00:00), +( (00:00:00), +0 (00:00:00), +0 (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +108 (00:00:00), +, (00:00:00), +99 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +8 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +; (00:00:00), +z (00:00:00), +- (00:00:00), +index (00:00:00), +: (00:00:00), +10 (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +status (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +13px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +888 (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+    <t>-width (00:01:07), -: (00:01:08), -7px (00:01:09), -; (00:01:10), -height (00:01:11), -: (00:01:12), -100 (00:01:13), -% (00:01:14), -; (00:01:15), -background (00:01:16), -- (00:01:17), -color (00:01:18), -: (00:01:19), -black (00:01:20), -; (00:01:21), -100 (00:07:14), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Speed (00:00:00), +( (00:00:00), +delay (00:00:00), +ms (00:00:00), +) (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +200 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +50 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +" (00:00:00), +&gt; (00:00:00), +50 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +50 (00:00:00), +; (00:00:00), +const (00:00:00), +slider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedDisplay (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +slider (00:00:00), +. (00:00:00), +onchange (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedDisplay (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +highlightIndices (00:00:00), += (00:00:00), +[ (00:00:00), +] (00:00:00), +if (00:00:00), +( (00:00:00), +highlightIndices (00:00:00), +. (00:00:00), +includes (00:00:00), +( (00:00:00), +i (00:00:00), +) (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +comparing (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +remove (00:00:00), +( (00:00:00), +" (00:00:00), +comparing (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Sorting (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +" (00:00:00), +; (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +, (00:00:00), +i (00:00:00), +] (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Sorted (00:00:00), +! (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +Motorcycle (00:00:00), +incoming (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Done (00:00:00), +! (00:00:00), +" (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +container (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +visEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +containerWidth (00:00:00), += (00:00:00), +container (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), +; (00:00:00), +const (00:00:00), +barCount (00:00:00), += (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +barCount (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +barLeft (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), ++ (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +visTop (00:00:00), += (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetTop (00:00:00), +; (00:00:00), +const (00:00:00), +visHeight (00:00:00), += (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +barTopInContainer (00:00:00), += (00:00:00), +visTop (00:00:00), ++ (00:00:00), +( (00:00:00), +visHeight (00:00:00), +- (00:00:00), +barHeight (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motoTop (00:00:00), += (00:00:00), +barTopInContainer (00:00:00), +- (00:00:00), +36 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +( (00:00:00), +barLeft (00:00:00), +- (00:00:00), +10 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +motoTop (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +Math (00:00:00), +. (00:00:00), +max (00:00:00), +( (00:00:00), +10 (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +* (00:00:00), +0 (00:00:00), +. (00:00:00), +5 (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +( (00:00:00), +containerWidth (00:00:00), ++ (00:00:00), +50 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +300 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +" (00:00:00), +- (00:00:00), +40px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +" (00:00:00), +0px (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +1a1a2e (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +eee (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +h1 (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +e0e0ff (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +12px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +label (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +aaa (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +{ (00:00:00), +accent (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +150px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +600px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +220px (00:00:00), +; (00:00:00), +} (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +16213e (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +10px (00:00:00), +8px (00:00:00), +0 (00:00:00), +8px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +, (00:00:00), +# (00:00:00), +a29bfe (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +0 (00:00:00), +0 (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +height (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +. (00:00:00), +comparing (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +fd79a8 (00:00:00), +, (00:00:00), +# (00:00:00), +e84393 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +28px (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +40px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +drop (00:00:00), +- (00:00:00), +shadow (00:00:00), +( (00:00:00), +0 (00:00:00), +0 (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +108 (00:00:00), +, (00:00:00), +99 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +8 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +; (00:00:00), +z (00:00:00), +- (00:00:00), +index (00:00:00), +: (00:00:00), +10 (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +status (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +13px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +888 (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
   </si>
   <si>
     <t>+&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Speed (00:00:00), +( (00:00:00), +delay (00:00:00), +ms (00:00:00), +) (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +200 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +50 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +" (00:00:00), +&gt; (00:00:00), +50 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
   </si>
   <si>
-    <t>-width (00:01:07), -: (00:01:08), -7px (00:01:09), -; (00:01:10), -height (00:01:11), -: (00:01:12), -100 (00:01:13), -% (00:01:14), -; (00:01:15), -background (00:01:16), -- (00:01:17), -color (00:01:18), -: (00:01:19), -black (00:01:20), -; (00:01:21), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +1a1a2e (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +eee (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +} (00:00:00), +h1 (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +e0e0ff (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +12px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +label (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +aaa (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +{ (00:00:00), +accent (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +150px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +600px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +220px (00:00:00), +; (00:00:00), +} (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +16213e (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +10px (00:00:00), +8px (00:00:00), +0 (00:00:00), +8px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +, (00:00:00), +# (00:00:00), +a29bfe (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +0 (00:00:00), +0 (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +height (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +. (00:00:00), +comparing (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +fd79a8 (00:00:00), +, (00:00:00), +# (00:00:00), +e84393 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +28px (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +40px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +drop (00:00:00), +- (00:00:00), +shadow (00:00:00), +( (00:00:00), +0 (00:00:00), +0 (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +108 (00:00:00), +, (00:00:00), +99 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +8 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +; (00:00:00), +z (00:00:00), +- (00:00:00), +index (00:00:00), +: (00:00:00), +10 (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +status (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +13px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +888 (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+    <t>-width (00:01:07), -: (00:01:08), -7px (00:01:09), -; (00:01:10), -height (00:01:11), -: (00:01:12), -100 (00:01:13), -% (00:01:14), -; (00:01:15), -background (00:01:16), -- (00:01:17), -color (00:01:18), -: (00:01:19), -black (00:01:20), -; (00:01:21), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +1a1a2e (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +eee (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +h1 (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +letter (00:00:00), +- (00:00:00), +spacing (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +e0e0ff (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +12px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +controls (00:00:00), +label (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +aaa (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +{ (00:00:00), +accent (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +150px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +600px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +220px (00:00:00), +; (00:00:00), +} (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +# (00:00:00), +16213e (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +10px (00:00:00), +8px (00:00:00), +0 (00:00:00), +8px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +sizing (00:00:00), +: (00:00:00), +border (00:00:00), +- (00:00:00), +box (00:00:00), +; (00:00:00), +flex (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +6c63ff (00:00:00), +, (00:00:00), +# (00:00:00), +a29bfe (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +0 (00:00:00), +0 (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +height (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +. (00:00:00), +comparing (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +to (00:00:00), +top (00:00:00), +, (00:00:00), +# (00:00:00), +fd79a8 (00:00:00), +, (00:00:00), +# (00:00:00), +e84393 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +28px (00:00:00), +; (00:00:00), +top (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +40px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +drop (00:00:00), +- (00:00:00), +shadow (00:00:00), +( (00:00:00), +0 (00:00:00), +0 (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +108 (00:00:00), +, (00:00:00), +99 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +8 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +; (00:00:00), +z (00:00:00), +- (00:00:00), +index (00:00:00), +: (00:00:00), +10 (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +status (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +13px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +888 (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +18px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
   </si>
   <si>
     <t>-100 (00:07:14), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +50 (00:00:00), +; (00:00:00), +const (00:00:00), +slider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedDisplay (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +display (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +slider (00:00:00), +. (00:00:00), +onchange (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedDisplay (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +highlightIndices (00:00:00), += (00:00:00), +[ (00:00:00), +] (00:00:00), +if (00:00:00), +( (00:00:00), +highlightIndices (00:00:00), +. (00:00:00), +includes (00:00:00), +( (00:00:00), +i (00:00:00), +) (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +comparing (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +else (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +remove (00:00:00), +( (00:00:00), +" (00:00:00), +comparing (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Sorting (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +" (00:00:00), +; (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +, (00:00:00), +i (00:00:00), +] (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Sorted (00:00:00), +! (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +Motorcycle (00:00:00), +incoming (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +status (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +Done (00:00:00), +! (00:00:00), +" (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +container (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +visEl (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +containerWidth (00:00:00), += (00:00:00), +container (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), +; (00:00:00), +const (00:00:00), +barCount (00:00:00), += (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +barCount (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +barLeft (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), ++ (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +visTop (00:00:00), += (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetTop (00:00:00), +; (00:00:00), +const (00:00:00), +visHeight (00:00:00), += (00:00:00), +visEl (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +barTopInContainer (00:00:00), += (00:00:00), +visTop (00:00:00), ++ (00:00:00), +( (00:00:00), +visHeight (00:00:00), +- (00:00:00), +barHeight (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motoTop (00:00:00), += (00:00:00), +barTopInContainer (00:00:00), +- (00:00:00), +36 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +( (00:00:00), +barLeft (00:00:00), +- (00:00:00), +10 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +motoTop (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +Math (00:00:00), +. (00:00:00), +max (00:00:00), +( (00:00:00), +10 (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +* (00:00:00), +0 (00:00:00), +. (00:00:00), +5 (00:00:00), +) (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +( (00:00:00), +containerWidth (00:00:00), ++ (00:00:00), +50 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +300 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +" (00:00:00), +- (00:00:00), +40px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +" (00:00:00), +0px (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
@@ -4535,6 +5413,9 @@
     <t>1000004</t>
   </si>
   <si>
+    <t>⛔</t>
+  </si>
+  <si>
     <t>gemini 3.5 flash</t>
   </si>
   <si>
@@ -4562,6 +5443,9 @@
     <t>1000006</t>
   </si>
   <si>
+    <t>🪪◼️⚠️</t>
+  </si>
+  <si>
     <t>! (x11), " (x100), # (x20), % (x5), &amp; (x16), ' (x4), ( (x137), ) (x137), * (x3), + (x19), , (x66), - (x95), . (x131), / (x10), 0 (x81), 02s, 05 (x3), 08, 08s, 0f2b3d, 0px, 1 (x10), 10 (x2), 100 (x4), 100vh, 1200px, 12px (x6), 145deg, 14px (x2), 15px, 16px, 18, 180deg, 180px, 18px, 1d4ed8, 1e293b, 1e2a3e, 1e40af, 1px (x7), 1rem, 2 (x2), 20, 20px (x6), 220px, 235, 240, 24px, 25, 255 (x8), 2563eb (x2), 280px, 28px (x4), 2c3e50, 2px (x9), 2rem (x4), 2s, 3, 300, 320px, 32px (x2), 35px, 36px, 37, 3b82f6, 3px (x3), 4, 400, 40px, 45px, 48, 48px, 4b5563, 4px (x4), 5 (x3), 50, 500 (x2), 55, 56px, 5px (x2), 5rem (x2), 6, 600 (x2), 60px, 6px (x6), 7, 700px, 7rem, 8 (x2), 80 (x3), 85, 85rem, 85vw, 8px (x6), 8rem, 95, 95vw, 96, 99, 9rem (x2), : (x136), ; (x264), &lt; (x26), = (x109), &gt; (x32), @, Animation, Array, Bubble (x2), COUNT (x4), DOMContentLoaded, Helvetica, Math (x4), Moto, Neue, Promise, Roboto, Segoe, Sort (x3), Sorting, UI, UTF, Watch, [ (x13), ] (x13), _ (x8), a, absolute, accent, across, add (x2), addEventListener (x6), after, align (x6), all, allowed, animation (x2), appears, appendChild (x2), aria, array (x14), async, auto, await, backdrop, background (x12), bar (x7), bars (x3), blur, body, bold, border (x15), bottom (x4), box (x8), btn (x8), bubble, bubbleSort (x2), button (x7), by, cancelSortFlag (x6), cancelled, catch, cbd5e1, ceil, center (x7), change (x2), changes, charset, class (x8), classList (x2), clearInterval (x5), click (x2), color (x8), column (x2), console (x2), const (x17), container (x16), containerRect (x4), contains (x2), content (x4), control (x3), controls (x3), createElement (x2), css, currentDelay (x2), currentLeft (x4), currentPos (x4), cursor (x3), defer, device, direction (x2), disabled (x9), display (x5), div (x9), do, document (x10), drop, e (x4), e9eef3, ease (x2), eef2f5, eef2ff, else (x3), en, end, endLeft (x5), endPos (x4), ends, err (x2), error, events, f1f5f9, f5f7fc, false (x11), family (x2), fffef7, ffffffaa, filter (x3), finally, firstChild (x2), flex (x10), fly, font (x14), for (x5), function (x9), gap (x5), generate, generateBtn (x7), generateRandomArray (x2), get, getBoundingClientRect, getElementById (x5), gradient (x2), grayscale, group (x3), h1, handleGenerateNewArray (x2), height (x7), hidden, hover (x2), href, i (x27), id (x4), if (x23), index, info (x2), inherit, init (x3), initSpeedSlider (x2), initial, input (x2), inset, interrupted, isNaN (x2), items (x5), js, justify (x3), label (x4), lang, left (x8), length (x4), let (x18), letter, linear (x3), link, liveVal (x3), loading, log, margin (x5), max (x4), media, meta (x2), min (x5), motoDiv (x9), motoWidth (x3), motorElement (x24), motorInterval (x14), motorcycle (x6), ms, n (x3), name, nbsp (x2), new (x2), newVal (x3), no, none (x4), not (x3), note (x2), nowrap, null (x10), offsetWidth, on, opacity, out, overflow, p (x2), padding (x8), parentNode (x2), parseInt (x2), pointer (x3), position (x3), primary (x3), px (x5), querySelectorAll, radius (x9), random (x2), range, readyState, rel, relative (x2), remove (x5), removeChild, removeElement (x2), renderBars (x3), resize, resolve (x2), return (x8), rgba (x13), rides, sans, scalable, scale (x2), script, select, serif, setAttribute, setInterval (x2), setTimeout (x3), shadow (x9), size (x8), sizing, slider, solid (x3), sort, sortBtn (x7), sorted, sorting, sortingActive (x7), space, spacing, span (x4), speed (x13), speedSlider (x9), speedValue (x3), speedValueSpan (x4), src, start, startLeft (x3), startMotorcycleRide (x2), startPos, step (x3), stopMotorcycleAnimation (x6), stretch, style (x9), stylesheet, subtitle (x2), swapped (x4), target (x2), text (x3), textContent (x4), the (x2), then, top, transform (x3), transition (x3), translateY (x2), true (x10), try, type, updateBars (x4), updateSpeed (x2), user (x2), value (x4), var (x8), viewport, vis (x3), warn, weight (x4), while (x2), white (x4), width (x13), will, window (x2), with, wrap (x2), z, { (x69), | (x5), } (x69), ·, ‑ (x2), —, •, →, ✨, ️ (x2), 🎲, 🏍 (x2), 🐇, 🐢, 💡, 💨</t>
   </si>
   <si>
@@ -4592,30 +5476,105 @@
     <t>1000008</t>
   </si>
   <si>
+    <t>" (x52), #, % (x4), ( (x38), ) (x38), * (x4), + (x16), , (x5), - (x18), . (x39), / (x4), 0 (x7), 1 (x5), 10 (x2), 100 (x5), 12, 123456 (x2), 1px, 20, 200px, 20px, 26px, 50 (x2), 500, 7px, 8, : (x21), ; (x72), &lt; (x9), = (x35), &gt; (x8), Animation, Arial, Array, Georgia, Math (x2), New, Number, Promise, Roman, Times, UTF, [ (x11), ] (x11), _ (x5), absolute, add (x2), align (x2), appendChild (x2), arr (x8), array (x6), async (x2), aux (x2), await (x3), background, bar (x8), barHeight (x2), bars (x7), black, body, bottom (x3), bubbleSort (x2), center, charset, class, classList (x2), color, column, const (x15), content, controls (x2), count (x3), createElement (x2), css, device, direction, display (x2), div (x3), do, document (x7), en, end, events, false, family (x2), flex (x4), font (x3), for (x5), function (x5), getElementById (x3), getElementsByClassName (x2), height (x5), href, i (x27), id (x2), if, initial, input, items (x2), js, label (x2), lang, left (x2), length (x5), let (x7), link, margin (x2), max (x2), meta (x2), milliseconds (x2), min, motorcycle (x8), ms (x2), name, new (x2), none, offsetHeight, offsetWidth, onchange, overflow, parseFloat, pointer, position (x2), px (x2), random, range, rel, relative, resolve (x2), return, rideMotorcycle (x2), sans, scale, script, serif (x2), setTimeout, size, sleep (x3), span (x2), speed (x6), speedSlider (x6), speedValue (x4), src, step, style (x5), stylesheet, swapped (x4), textContent (x2), totalSteps (x2), transform, translateX, true, type, updateBars (x2), value (x2), var (x5), viewport, vis (x2), visible, visualizer (x5), visualizerHeight (x2), visualizerWidth (x2), while, width (x2), x (x2), { (x17), } (x17), ️, 🏍</t>
+  </si>
+  <si>
+    <t>-0px (00:01:24), -var (00:05:48), -new (00:07:04), -Promise (00:07:05), -( (00:07:06), -resolve (00:07:07), -= (00:07:08), -&gt; (00:07:09), -setTimeout (00:07:10), -( (00:07:11), -resolve (00:07:12), -, (00:07:13), -100 (00:07:14), -) (00:07:15), -) (00:07:16), +lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Animation (00:00:00), +speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +500 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +step (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +let (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +speedSlider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedValue (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +onchange (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), ++ (00:00:00), +" (00:00:00), +ms (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +function (00:00:00), +sleep (00:00:00), +( (00:00:00), +milliseconds (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +milliseconds (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +let (00:00:00), +swapped (00:00:00), +; (00:00:00), +sleep (00:00:00), +( (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +await (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +motorcycle (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +motorcycle (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +visualizerWidth (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), +; (00:00:00), +const (00:00:00), +visualizerHeight (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +totalSteps (00:00:00), += (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +- (00:00:00), +1 (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +x (00:00:00), += (00:00:00), +( (00:00:00), +i (00:00:00), +/ (00:00:00), +totalSteps (00:00:00), +) (00:00:00), +* (00:00:00), +visualizerWidth (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +parseFloat (00:00:00), +( (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), +) (00:00:00), +/ (00:00:00), +100 (00:00:00), +* (00:00:00), +visualizerHeight (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +x (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +( (00:00:00), +barHeight (00:00:00), ++ (00:00:00), +12 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +sleep (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +max (00:00:00), +( (00:00:00), +20 (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Georgia (00:00:00), +, (00:00:00), +" (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +" (00:00:00), +, (00:00:00), +serif (00:00:00), +; (00:00:00), +. (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Arial (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +overflow (00:00:00), +: (00:00:00), +visible (00:00:00), +; (00:00:00), +0 (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +bottom (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +26px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateX (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
+    <t>+lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Animation (00:00:00), +speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +500 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +step (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+  </si>
+  <si>
+    <t>-0px (00:01:24), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Georgia (00:00:00), +, (00:00:00), +" (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +" (00:00:00), +, (00:00:00), +serif (00:00:00), +; (00:00:00), +. (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Arial (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +overflow (00:00:00), +: (00:00:00), +visible (00:00:00), +; (00:00:00), +0 (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +bottom (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +26px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateX (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
+    <t>-var (00:05:48), -new (00:07:04), -Promise (00:07:05), -( (00:07:06), -resolve (00:07:07), -= (00:07:08), -&gt; (00:07:09), -setTimeout (00:07:10), -( (00:07:11), -resolve (00:07:12), -, (00:07:13), -100 (00:07:14), -) (00:07:15), -) (00:07:16), +let (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +speedSlider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedValue (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +onchange (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), ++ (00:00:00), +" (00:00:00), +ms (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +function (00:00:00), +sleep (00:00:00), +( (00:00:00), +milliseconds (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +milliseconds (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +let (00:00:00), +swapped (00:00:00), +; (00:00:00), +sleep (00:00:00), +( (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +await (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +motorcycle (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +motorcycle (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +visualizerWidth (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), +; (00:00:00), +const (00:00:00), +visualizerHeight (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +totalSteps (00:00:00), += (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +- (00:00:00), +1 (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +x (00:00:00), += (00:00:00), +( (00:00:00), +i (00:00:00), +/ (00:00:00), +totalSteps (00:00:00), +) (00:00:00), +* (00:00:00), +visualizerWidth (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +parseFloat (00:00:00), +( (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), +) (00:00:00), +/ (00:00:00), +100 (00:00:00), +* (00:00:00), +visualizerHeight (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +x (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +( (00:00:00), +barHeight (00:00:00), ++ (00:00:00), +12 (00:00:00), +) (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +sleep (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +max (00:00:00), +( (00:00:00), +20 (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
     <t>chatgpt 5.5 thinking images</t>
   </si>
   <si>
     <t>1000009</t>
   </si>
   <si>
+    <t>" (x58), # (x3), % (x4), ( (x34), ) (x34), * (x2), + (x17), , (x4), - (x22), . (x42), / (x3), 0 (x5), 1 (x5), 10 (x2), 100 (x4), 123456 (x2), 1px, 2 (x3), 20, 200px, 20px, 260px, 30 (x2), 300, 30px (x2), 50 (x2), 500, 7px, 8, 8px, : (x22), ; (x75), &lt; (x7), = (x37), &gt; (x6), Animation, Array, Georgia, Math (x2), New, Number, Promise, Roman, Times, UTF, [ (x11), ] (x11), _ (x5), absolute, add, align (x2), appendChild (x2), arr (x8), array (x6), async (x2), aux (x2), await (x4), background, bar (x12), bars (x6), black, block, body, bottom (x2), bubbleSort (x2), center, changeSpeed (x2), charset, classList, color, column, const (x12), content, count (x3), createElement (x2), css, device, direction, display (x5), div (x2), do, document (x6), en, end, events, false, family, flex (x4), font (x2), for (x5), function (x5), getElementById (x2), getElementsByClassName (x2), height (x5), href, i (x26), id (x3), if, index, initial, input, items (x2), js, label (x3), lang, left (x2), length (x4), let (x7), line, link, margin (x3), max (x2), meta (x2), min, motorcycle (x13), ms (x3), name, new (x2), none (x3), offsetLeft, offsetTop, offsetWidth (x2), oninput, overflow, pointer, position (x2), px (x3), random, range, rel, relative, resolve (x2), return, rideMotorcycle (x2), scale, script, serif, setTimeout, size, sleep (x4), slider (x3), span (x2), speed (x11), speedValue (x2), src, step, style (x9), stylesheet, swapped (x4), textContent (x2), this, top (x2), transform, translateX, true, type, updateBars (x2), value (x6), var (x5), viewport, vis (x2), visible, visualizer (x4), while, width (x3), x (x2), y (x2), z, { (x18), } (x18), ️, 🏍</t>
+  </si>
+  <si>
+    <t>-0px (00:01:24), -var (00:05:48), -new (00:07:04), -Promise (00:07:05), -( (00:07:06), -resolve (00:07:07), -= (00:07:08), -&gt; (00:07:09), -setTimeout (00:07:10), -( (00:07:11), -resolve (00:07:12), -, (00:07:13), -100 (00:07:14), -) (00:07:15), -) (00:07:16), +lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Animation (00:00:00), +speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +300 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +step (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +oninput (00:00:00), += (00:00:00), +" (00:00:00), +changeSpeed (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +" (00:00:00), +&gt; (00:00:00), +let (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +speedValue (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motorcycle (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +motorcycle (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +changeSpeed (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +sleep (00:00:00), +( (00:00:00), +ms (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +ms (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +let (00:00:00), +swapped (00:00:00), +; (00:00:00), +sleep (00:00:00), +( (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +await (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +x (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), ++ (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), +/ (00:00:00), +2 (00:00:00), +; (00:00:00), +const (00:00:00), +y (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetTop (00:00:00), +- (00:00:00), +30 (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +x (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +y (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +sleep (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +max (00:00:00), +( (00:00:00), +20 (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +/ (00:00:00), +2 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), ++ (00:00:00), +30 (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +" (00:00:00), +- (00:00:00), +30px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +sleep (00:00:00), +( (00:00:00), +500 (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Georgia (00:00:00), +, (00:00:00), +" (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +" (00:00:00), +, (00:00:00), +serif (00:00:00), +; (00:00:00), +label (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +260px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +overflow (00:00:00), +: (00:00:00), +visible (00:00:00), +; (00:00:00), +0 (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +line (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateX (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +z (00:00:00), +- (00:00:00), +index (00:00:00), +: (00:00:00), +2 (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
+    <t>+lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Animation (00:00:00), +speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +300 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +step (00:00:00), += (00:00:00), +" (00:00:00), +10 (00:00:00), +" (00:00:00), +oninput (00:00:00), += (00:00:00), +" (00:00:00), +changeSpeed (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +" (00:00:00), +&gt; (00:00:00)</t>
+  </si>
+  <si>
+    <t>-0px (00:01:24), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Georgia (00:00:00), +, (00:00:00), +" (00:00:00), +Times (00:00:00), +New (00:00:00), +Roman (00:00:00), +" (00:00:00), +, (00:00:00), +serif (00:00:00), +; (00:00:00), +label (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +8px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +260px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +overflow (00:00:00), +: (00:00:00), +visible (00:00:00), +; (00:00:00), +0 (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +line (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateX (00:00:00), +( (00:00:00), +- (00:00:00), +50 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +z (00:00:00), +- (00:00:00), +index (00:00:00), +: (00:00:00), +2 (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
+    <t>-var (00:05:48), -new (00:07:04), -Promise (00:07:05), -( (00:07:06), -resolve (00:07:07), -= (00:07:08), -&gt; (00:07:09), -setTimeout (00:07:10), -( (00:07:11), -resolve (00:07:12), -, (00:07:13), -100 (00:07:14), -) (00:07:15), -) (00:07:16), +let (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +speedValue (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motorcycle (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +motorcycle (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +changeSpeed (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +sleep (00:00:00), +( (00:00:00), +ms (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +ms (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +let (00:00:00), +swapped (00:00:00), +; (00:00:00), +sleep (00:00:00), +( (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +await (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +x (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), ++ (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), +/ (00:00:00), +2 (00:00:00), +; (00:00:00), +const (00:00:00), +y (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetTop (00:00:00), +- (00:00:00), +30 (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +x (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +y (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +sleep (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +max (00:00:00), +( (00:00:00), +20 (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +/ (00:00:00), +2 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +offsetWidth (00:00:00), ++ (00:00:00), +30 (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +top (00:00:00), += (00:00:00), +" (00:00:00), +- (00:00:00), +30px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +sleep (00:00:00), +( (00:00:00), +500 (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
     <t>sonnet 4.6 images</t>
   </si>
   <si>
     <t>1000010</t>
   </si>
   <si>
+    <t>" (x46), # (x5), % (x3), ( (x33), ) (x33), * (x4), + (x17), , (x4), - (x28), . (x41), / (x4), 0 (x6), 05s (x2), 0px (x2), 1 (x5), 100 (x4), 10px, 123456 (x2), 14px (x2), 16px (x2), 1px, 20, 200 (x3), 200px, 201, 20px, 24px, 30px, 4, 400, 50, 60, 60px, 7px, 8, : (x30), ; (x81), &lt; (x7), = (x39), &gt; (x8), Array, Math, Promise (x3), Speed, [ (x11), ] (x11), _ (x3), absolute, add, align (x3), appendChild (x2), arr (x8), array (x6), async (x2), aux (x2), await (x3), background (x2), bar (x8), barHeightPx (x2), barWidth (x3), bars (x7), black, block, body, bottom (x4), bubbleSort (x2), center (x2), classList, color (x2), column, const (x13), controls (x2), count (x3), createElement (x2), css, direction, display (x6), div (x3), do, document (x7), end, events, f9f9f9, false, family, flex (x5), font (x4), for (x5), function (x4), gap, getElementById (x3), getElementsByClassName (x2), h1, height (x5), href, i (x27), id (x4), if, input, items (x3), js, label (x6), left (x4), leftPos (x2), length (x5), let (x5), line, linear (x2), link, margin (x3), max, min (x2), moto (x9), motorcycle (x2), new (x4), none (x3), offsetHeight, onchange, padding, parseInt, pointer, position (x2), px (x3), random, range, rel, relative, resolve (x6), runMotorcycle (x2), sans, script, serif, setTimeout (x3), size (x3), slider (x3), span (x2), speed (x9), speedLabel (x2), speedSlider (x2), src, style (x7), stylesheet, swapped (x3), textContent (x2), this (x2), top, transition, true, type, updateBars (x2), value (x3), var (x5), vis (x2), visualizer (x3), while, width (x2), { (x19), } (x19), ️, 🏍</t>
+  </si>
+  <si>
+    <t>-100 (00:07:14), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +200 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +label (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +/ (00:00:00), +200 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +moto (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedSlider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedLabel (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +label (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +onchange (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +201 (00:00:00), +- (00:00:00), +parseInt (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedLabel (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), ++ (00:00:00), +" (00:00:00), +/ (00:00:00), +200 (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +barWidth (00:00:00), += (00:00:00), +8 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +barHeightPx (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +leftPos (00:00:00), += (00:00:00), +i (00:00:00), +* (00:00:00), +barWidth (00:00:00), +- (00:00:00), +4 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +leftPos (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +barHeightPx (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +60 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +* (00:00:00), +barWidth (00:00:00), ++ (00:00:00), +20 (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +400 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +f9f9f9 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +h1 (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +# (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +} (00:00:00), +label (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +label (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +60px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +24px (00:00:00), +; (00:00:00), +bottom (00:00:00), +: (00:00:00), +0px (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +30px (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +, (00:00:00), +bottom (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +line (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
+    <t>+&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +200 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +label (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +/ (00:00:00), +200 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+  </si>
+  <si>
+    <t>+font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +f9f9f9 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +h1 (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +# (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +} (00:00:00), +label (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speed (00:00:00), +- (00:00:00), +label (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +60px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +24px (00:00:00), +; (00:00:00), +bottom (00:00:00), +: (00:00:00), +0px (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +30px (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +, (00:00:00), +bottom (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +linear (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +line (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +1 (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
+    <t>-100 (00:07:14), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +moto (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedSlider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedLabel (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +label (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +onchange (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +201 (00:00:00), +- (00:00:00), +parseInt (00:00:00), +( (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedLabel (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), ++ (00:00:00), +" (00:00:00), +/ (00:00:00), +200 (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +runMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +barWidth (00:00:00), += (00:00:00), +8 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +barHeightPx (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +leftPos (00:00:00), += (00:00:00), +i (00:00:00), +* (00:00:00), +barWidth (00:00:00), +- (00:00:00), +4 (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +leftPos (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +barHeightPx (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +60 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +* (00:00:00), +barWidth (00:00:00), ++ (00:00:00), +20 (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +400 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
     <t>opus 4.7 images</t>
   </si>
   <si>
     <t>1000011</t>
   </si>
   <si>
+    <t>" (x40), #, % (x3), ( (x33), ) (x33), * (x3), + (x15), , (x2), - (x14), . (x35), / (x2), 0 (x5), 0px, 1 (x4), 100 (x4), 10px, 123456 (x2), 1px, 200px, 20px, 4px, 50, 500, 7px, : (x15), ; (x63), &lt; (x7), = (x35), &gt; (x7), Array, Math, Promise (x2), Speed, [ (x12), ] (x12), _ (x5), absolute, add (x2), align (x2), appendChild (x2), arr (x8), array (x7), async (x2), aux (x2), await (x2), background, bar (x10), barHeight (x2), barLeft (x2), bars (x6), black, body, bottom, bubbleSort (x2), center, class, classList (x2), clientHeight, color, column, const (x14), controls (x2), count (x3), createElement (x2), css, direction, display (x2), div (x3), do, document (x7), end, false, flex (x4), font, for (x5), function (x4), getElementById (x3), getElementsByClassName (x2), height (x4), href, i (x27), id (x2), if, input, items (x2), js, label (x2), left, length (x4), let (x5), link, margin (x2), max, min, moto (x6), motorcycle (x2), ms (x2), new (x3), offsetLeft, oninput, parseInt, position (x2), px (x2), random, range, rel, relative, resolve (x4), rideMotorcycle (x2), script, setTimeout (x2), size, slider (x6), span (x2), speed (x10), speedLabel (x2), src, style (x4), stylesheet, swapped (x3), textContent (x2), transform, translateY, true, type, updateBars (x2), value (x4), var (x7), vis (x2), visHeight (x2), visualizer (x4), while, width, { (x16), } (x16), ️, 🏍</t>
+  </si>
+  <si>
+    <t>-100 (00:07:14), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +500 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +slider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedLabel (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +slider (00:00:00), +. (00:00:00), +oninput (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +slider (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedLabel (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), ++ (00:00:00), +" (00:00:00), +ms (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +moto (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +visHeight (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +clientHeight (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +barLeft (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +visHeight (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +barLeft (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +barHeight (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +. (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +: (00:00:00), +10px (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateY (00:00:00), +( (00:00:00), +- (00:00:00), +4px (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
+    <t>+&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +500 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +&gt; (00:00:00), +100 (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+  </si>
+  <si>
+    <t>+. (00:00:00), +controls (00:00:00), +{ (00:00:00), +margin (00:00:00), +: (00:00:00), +10px (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +translateY (00:00:00), +( (00:00:00), +- (00:00:00), +4px (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
+    <t>-100 (00:07:14), +var (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +const (00:00:00), +slider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedLabel (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +value (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +slider (00:00:00), +. (00:00:00), +oninput (00:00:00), += (00:00:00), +function (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +slider (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedLabel (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), ++ (00:00:00), +" (00:00:00), +ms (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +moto (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +moto (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +visHeight (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +clientHeight (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +const (00:00:00), +barLeft (00:00:00), += (00:00:00), +bar (00:00:00), +. (00:00:00), +offsetLeft (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +visHeight (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +barLeft (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +moto (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +barHeight (00:00:00), ++ (00:00:00), +" (00:00:00), +px (00:00:00), +" (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
     <t>gemini 3.5 flash images</t>
   </si>
   <si>
     <t>1000012</t>
   </si>
   <si>
+    <t>" (x40), # (x3), $ (x3), % (x5), ( (x29), ) (x29), * (x2), + (x13), , (x4), - (x20), . (x38), / (x3), 0 (x7), 0px (x2), 1 (x4), 10, 100 (x6), 123456 (x2), 1px, 1s (x2), 200px, 20px, 24px, 30px, 450px, 50 (x2), 500, 7px, 8, : (x23), ; (x66), &lt; (x10), = (x32), &gt; (x10), Animation, Arial, Array, Delay, Math, Promise (x2), UTF, [ (x11), ] (x11), _ (x3), ` (x6), absolute, add, align (x2), appendChild, arr (x8), array (x6), async (x2), aux (x2), await (x2), background, bar (x8), barHeight (x2), barRect (x3), bars (x6), black, block, body, bottom (x5), bubbleSort (x2), center, charset, class, classList, color, column, const (x12), container (x3), containerRect (x3), control (x2), count (x3), createElement, css, direction, display (x4), div (x6), do, document (x6), en, end, events, false, family, flex (x4), font (x2), for (x5), function (x3), getBoundingClientRect (x2), getElementById (x3), getElementsByClassName (x2), height (x6), href, i (x26), id (x3), if, input, items (x2), js, label (x2), lang, left (x6), length (x4), let (x6), linear (x2), link, margin (x2), max, meta, min, motorcycle (x9), ms, new (x3), none (x2), onchange, panel (x2), pointer, position (x2), px (x3), random, range, rel, relative, relativeLeft (x2), resolve (x4), rideMotorcycle (x2), sans, script, serif, setTimeout (x2), size, slider (x2), speed (x5), src, style (x7), stylesheet, swapped (x3), this, transition, true, type, updateBars (x2), value (x2), var (x3), vis (x4), visualizer (x2), while, width (x4), { (x19), } (x19), ️, 🏍</t>
+  </si>
+  <si>
+    <t>-200px (00:00:49), -100 (00:07:14), +lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +control (00:00:00), +- (00:00:00), +panel (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Animation (00:00:00), +Delay (00:00:00), +( (00:00:00), +ms (00:00:00), +) (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +500 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +onchange (00:00:00), += (00:00:00), +" (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +let (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +motorcycle (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +containerRect (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +getBoundingClientRect (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +barRect (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +getBoundingClientRect (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +relativeLeft (00:00:00), += (00:00:00), +barRect (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +containerRect (00:00:00), +. (00:00:00), +left (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +barRect (00:00:00), +. (00:00:00), +height (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +` (00:00:00), +$ (00:00:00), +{ (00:00:00), +relativeLeft (00:00:00), +} (00:00:00), +px (00:00:00), +` (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +` (00:00:00), +$ (00:00:00), +{ (00:00:00), +barHeight (00:00:00), +} (00:00:00), +px (00:00:00), +` (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +50 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +` (00:00:00), +$ (00:00:00), +{ (00:00:00), +containerRect (00:00:00), +. (00:00:00), +width (00:00:00), ++ (00:00:00), +10 (00:00:00), +} (00:00:00), +px (00:00:00), +` (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +" (00:00:00), +0px (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Arial (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +450px (00:00:00), +; (00:00:00), +} (00:00:00), +100 (00:00:00), +% (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +bottom (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +30px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +24px (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +1s (00:00:00), +linear (00:00:00), +, (00:00:00), +bottom (00:00:00), +0 (00:00:00), +. (00:00:00), +1s (00:00:00), +linear (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
+    <t>+lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +control (00:00:00), +- (00:00:00), +panel (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +Animation (00:00:00), +Delay (00:00:00), +( (00:00:00), +ms (00:00:00), +) (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +slider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +1 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +500 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +100 (00:00:00), +" (00:00:00), +onchange (00:00:00), += (00:00:00), +" (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +this (00:00:00), +. (00:00:00), +value (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+  </si>
+  <si>
+    <t>-200px (00:00:49), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +Arial (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +width (00:00:00), +: (00:00:00), +450px (00:00:00), +; (00:00:00), +} (00:00:00), +100 (00:00:00), +% (00:00:00), +width (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +# (00:00:00), +motorcycle (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +bottom (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +30px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +24px (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +left (00:00:00), +0 (00:00:00), +. (00:00:00), +1s (00:00:00), +linear (00:00:00), +, (00:00:00), +bottom (00:00:00), +0 (00:00:00), +. (00:00:00), +1s (00:00:00), +linear (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +pointer (00:00:00), +- (00:00:00), +events (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
+    <t>-100 (00:07:14), +let (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +100 (00:00:00), +; (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +rideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +motorcycle (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +containerRect (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +. (00:00:00), +getBoundingClientRect (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +barRect (00:00:00), += (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +getBoundingClientRect (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +relativeLeft (00:00:00), += (00:00:00), +barRect (00:00:00), +. (00:00:00), +left (00:00:00), +- (00:00:00), +containerRect (00:00:00), +. (00:00:00), +left (00:00:00), +; (00:00:00), +const (00:00:00), +barHeight (00:00:00), += (00:00:00), +barRect (00:00:00), +. (00:00:00), +height (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +` (00:00:00), +$ (00:00:00), +{ (00:00:00), +relativeLeft (00:00:00), +} (00:00:00), +px (00:00:00), +` (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +` (00:00:00), +$ (00:00:00), +{ (00:00:00), +barHeight (00:00:00), +} (00:00:00), +px (00:00:00), +` (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +50 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +left (00:00:00), += (00:00:00), +` (00:00:00), +$ (00:00:00), +{ (00:00:00), +containerRect (00:00:00), +. (00:00:00), +width (00:00:00), ++ (00:00:00), +10 (00:00:00), +} (00:00:00), +px (00:00:00), +` (00:00:00), +; (00:00:00), +motorcycle (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +bottom (00:00:00), += (00:00:00), +" (00:00:00), +0px (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
     <t>chatgpt 5.5 instant no code</t>
   </si>
   <si>
@@ -4628,14 +5587,71 @@
     <t>1000014</t>
   </si>
   <si>
-    <t>!</t>
+    <t>deepseek v3 images</t>
+  </si>
+  <si>
+    <t>1000015</t>
+  </si>
+  <si>
+    <t>! (x3), " (x116), # (x13), $, % (x19), &amp; (x2), ' (x2), ( (x121), ) (x121), * (x2), + (x12), , (x55), - (x73), . (x117), / (x10), 0 (x55), 05, 05s, 1 (x15), 100 (x9), 100vh, 10px (x2), 123456, 12px (x4), 135deg (x3), 14px (x2), 15px (x3), 16px, 180deg, 1px, 2 (x3), 200, 2000, 200px, 20px (x7), 24px, 25, 255 (x6), 25px (x6), 2px (x6), 2s (x3), 3 (x3), 30, 30px (x2), 32px, 333, 350px, 3px, 40px, 45 (x3), 45px, 46, 49, 4px (x6), 5, 50 (x2), 50px (x3), 5px, 667eea (x3), 6px, 764ba2 (x4), 768px, 8, 80 (x3), 800, 8px (x3), 8s, 9, 94, 95, : (x96), ; (x202), &lt; (x25), = (x80), &gt; (x29), ?, @ (x3), Animation, Array, Bubble (x3), Error, Geneva, Math, Motorcycle, New, Promise, Ride, Segoe, Sort (x3), Sorting (x3), Speed, Start, Tahoma, UI, UTF, Verdana, [ (x10), ] (x10), _ (x2), ` (x2), absolute, across, add (x3), addEventListener (x7), adjusts, align (x5), animateMotorcycle (x2), animation (x3), animationend (x2), appendChild (x4), arr (x8), array (x7), async (x3), await (x3), background (x7), bar (x8), bars (x5), barsContainer (x3), between, bezier, block, body, bold (x3), border (x7), bottom (x2), box (x6), bubbleSortVisual (x2), button (x7), calc, cancelled, catch, center (x6), change, charset, class (x7), classList (x3), click (x4), clientWidth, color (x4), column (x2), comparisons, completed, console, const (x18), container (x5), containerWidth (x2), content (x3), control (x3), controls (x4), controlsDiv (x3), count (x3), createElement (x4), css, cubic, currentSortingPromise, cursor (x2), delay, device, direction (x2), disabled, display (x7), div (x13), do, document (x14), drop, dynamic, e (x6), ease, en, end, error (x2), existingRun (x3), f093fb, f5576c, false (x6), family, faster, filter, finally, firstChild (x2), flex (x8), font (x9), for (x4), forwards (x2), from, function (x12), gap (x4), getElementById (x6), getElementsByClassName, globalSpeed (x12), gradient (x4), h1 (x2), head, height (x6), hideMotorcycle (x7), hover, href, i (x23), id (x6), if (x11), info (x3), initRandomArray (x3), initial, input (x3), interrupted, items (x4), js, justify (x2), keyframes (x3), label (x3), lang, left (x5), len (x3), length (x4), let (x11), linear (x5), link, log, lower, margin (x6), max (x2), media, message, meta (x2), min (x3), motorcycle (x8), motorcycleDiv (x9), motorcycleZone (x8), ms, name, new (x3), none (x5), null, offsetHeight, onFinish (x3), originalReset, overflow, p (x5), padding (x6), parseInt (x4), pointer (x2), position (x3), px, querySelector (x3), races, radius (x6), random, range, rel, relative (x2), remove (x2), removeChild, removeEventListener (x2), renderBars (x3), reset (x4), resetAndStop (x6), resetBtn (x7), resolve (x2), return (x2), rgba (x9), rideAcross (x2), rideAcrossDynamic (x2), right, run (x4), sans, scale (x2), scaleX (x8), script, serif, setTimeout (x2), setupSpeedSlider, shadow (x8), size (x5), slider, sortBtn (x6), sortingInProgress (x11), span (x2), speed (x6), speedSlider (x9), speedValue (x8), src, startSorting (x2), step, style (x9), styleId (x3), styleTag (x7), stylesheet, swapped (x4), target (x3), temp (x2), text (x2), textContent (x7), the, throw, to, top (x2), transform (x10), transition (x2), true (x2), try, type, updateBars (x3), value (x5), var (x2), viewport, vis (x2), visible, visualizer (x5), weight (x3), while (x2), white (x3), width (x6), window (x3), with, wrap (x2), zone (x2), { (x68), |, } (x68), ·, →, ⏩, ⚡ (x2), ✅, ️ (x4), 🏍 (x4), 🔄</t>
+  </si>
+  <si>
+    <t>-# (00:00:42), -vis (00:00:43), -- (00:00:44), -123456 (00:00:45), -{ (00:00:46), -height (00:00:47), -: (00:00:48), -200px (00:00:49), -; (00:00:50), -display (00:00:51), -: (00:00:52), -flex (00:00:53), -; (00:00:54), -align (00:00:55), -- (00:00:56), -items (00:00:57), -: (00:00:58), -flex (00:00:59), -- (00:01:00), -end (00:01:01), -; (00:01:02), -} (00:01:03), -7px (00:01:09), -height (00:01:11), -: (00:01:12), -100 (00:01:13), -% (00:01:14), -; (00:01:15), -background (00:01:16), -- (00:01:17), -color (00:01:18), -: (00:01:19), -black (00:01:20), -; (00:01:21), -margin (00:01:22), -: (00:01:23), -0px (00:01:24), -1px (00:01:25), -; (00:01:26), -const (00:02:09), -count (00:02:10), -= (00:02:11), -50 (00:02:12), -; (00:02:13), -const (00:02:14), -array (00:02:15), -= (00:02:16), -new (00:02:17), -Array (00:02:18), -( (00:02:19), -count (00:02:20), -) (00:02:21), -; (00:02:22), -for (00:02:23), -( (00:02:24), -let (00:02:25), -i (00:02:26), -= (00:02:27), -0 (00:02:28), -; (00:02:29), -i (00:02:30), -&lt; (00:02:31), -count (00:02:32), -; (00:02:33), -i (00:02:34), -+ (00:02:35), -+ (00:02:36), -) (00:02:37), -{ (00:02:38), -array (00:02:39), -[ (00:02:40), -i (00:02:41), -] (00:02:42), -= (00:02:43), -Math (00:02:44), -. (00:02:45), -random (00:02:46), -( (00:02:47), -) (00:02:48), -; (00:02:49), -} (00:02:57), -const (00:02:58), -visualizer (00:02:59), -= (00:03:00), -document (00:03:01), -. (00:03:02), -getElementById (00:03:03), -( (00:03:04), -" (00:03:05), -vis (00:03:06), -- (00:03:07), -123456 (00:03:08), -" (00:03:09), -) (00:03:10), -; (00:03:11), -for (00:03:12), -( (00:03:13), -let (00:03:14), -i (00:03:15), -= (00:03:16), -0 (00:03:17), -; (00:03:18), -i (00:03:19), -&lt; (00:03:20), -array (00:03:21), -. (00:03:22), -length (00:03:23), -; (00:03:24), -i (00:03:25), -+ (00:03:26), -+ (00:03:27), -) (00:03:28), -{ (00:03:29), -const (00:03:30), -bar (00:03:31), -= (00:03:32), -document (00:03:33), -. (00:03:34), -createElement (00:03:35), -( (00:03:36), -" (00:03:37), -div (00:03:38), -" (00:03:39), -) (00:03:40), -; (00:03:41), -visualizer (00:03:42), -. (00:03:43), -appendChild (00:03:44), -( (00:03:45), -bar (00:03:46), -) (00:03:47), -; (00:03:48), -bar (00:03:49), -. (00:03:50), -classList (00:03:51), -. (00:03:52), -add (00:03:53), -( (00:03:54), -" (00:03:55), -bar (00:03:56), -" (00:03:57), -) (00:03:58), -; (00:03:59), -bar (00:04:00), -. (00:04:01), -style (00:04:02), -. (00:04:03), -height (00:04:04), -= (00:04:05), -array (00:04:06), -[ (00:04:07), -i (00:04:08), -] (00:04:09), -* (00:04:10), -100 (00:04:11), -+ (00:04:12), -" (00:04:13), -% (00:04:14), -" (00:04:15), -; (00:04:16), -} (00:04:36), -bubbleSort (00:04:37), -( (00:04:38), -array (00:04:39), -) (00:04:40), -; (00:04:41), -function (00:04:42), -updateBars (00:04:43), -( (00:04:44), -) (00:04:45), -{ (00:04:46), -const (00:04:47), -bars (00:04:48), -= (00:04:49), -document (00:04:50), -. (00:04:51), -getElementsByClassName (00:04:52), -( (00:04:53), -" (00:04:54), -bar (00:04:55), -" (00:04:56), -) (00:04:57), -; (00:04:58), -for (00:04:59), -( (00:05:00), -let (00:05:01), -i (00:05:02), -= (00:05:03), -0 (00:05:04), -; (00:05:05), -i (00:05:06), -&lt; (00:05:07), -bars (00:05:08), -. (00:05:09), -length (00:05:10), -; (00:05:11), -i (00:05:12), -+ (00:05:13), -+ (00:05:14), -) (00:05:15), -{ (00:05:16), -bars (00:05:17), -[ (00:05:18), -i (00:05:19), -] (00:05:20), -. (00:05:21), -style (00:05:22), -. (00:05:23), -height (00:05:24), -= (00:05:25), -array (00:05:26), -[ (00:05:27), -i (00:05:28), -] (00:05:29), -* (00:05:30), -100 (00:05:31), -+ (00:05:32), -" (00:05:33), -% (00:05:34), -" (00:05:35), -; (00:05:36), -} (00:05:37), -} (00:05:38), -bubbleSort (00:05:41), -var (00:05:48), -arr (00:06:02), -. (00:06:03), -length (00:06:04), -aux (00:06:27), -aux (00:06:53), -100 (00:07:14), +lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +| (00:00:00), +Bubble (00:00:00), +Sort (00:00:00), +with (00:00:00), +Motorcycle (00:00:00), +Ride (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +· (00:00:00), +Bubble (00:00:00), +Sort (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +control (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +⏩ (00:00:00), +Animation (00:00:00), +speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +0 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +200 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +80 (00:00:00), +" (00:00:00), +step (00:00:00), += (00:00:00), +" (00:00:00), +5 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +&gt; (00:00:00), +80 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +button (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +resetBtn (00:00:00), +" (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +reset (00:00:00), +- (00:00:00), +button (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🔄 (00:00:00), +New (00:00:00), +random (00:00:00), +array (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +button (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&gt; (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +bars (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycleZone (00:00:00), +" (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +zone (00:00:00), +" (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +run (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +info (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +&gt; (00:00:00), +✅ (00:00:00), +Sorting (00:00:00), +completed (00:00:00), +→ (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +motorcycle (00:00:00), +races (00:00:00), +across (00:00:00), +the (00:00:00), +bars (00:00:00), +from (00:00:00), +left (00:00:00), +to (00:00:00), +right (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +&gt; (00:00:00), +⚡ (00:00:00), +Speed (00:00:00), +slider (00:00:00), +adjusts (00:00:00), +delay (00:00:00), +between (00:00:00), +comparisons (00:00:00), +( (00:00:00), +lower (00:00:00), += (00:00:00), +faster (00:00:00), +) (00:00:00), +. (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +const (00:00:00), +count (00:00:00), += (00:00:00), +45 (00:00:00), +; (00:00:00), +let (00:00:00), +array (00:00:00), += (00:00:00), +new (00:00:00), +Array (00:00:00), +( (00:00:00), +count (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +let (00:00:00), +currentSortingPromise (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +let (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +80 (00:00:00), +; (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedSlider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedValue (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +resetBtn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +resetBtn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motorcycleZone (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycleZone (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +initRandomArray (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +Math (00:00:00), +. (00:00:00), +random (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +renderBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +while (00:00:00), +( (00:00:00), +visualizer (00:00:00), +. (00:00:00), +firstChild (00:00:00), +) (00:00:00), +{ (00:00:00), +visualizer (00:00:00), +. (00:00:00), +removeChild (00:00:00), +( (00:00:00), +visualizer (00:00:00), +. (00:00:00), +firstChild (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +bar (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +&amp; (00:00:00), +&amp; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +existingRun (00:00:00), += (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +querySelector (00:00:00), +( (00:00:00), +" (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +run (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +existingRun (00:00:00), +) (00:00:00), +{ (00:00:00), +existingRun (00:00:00), +. (00:00:00), +remove (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +animateMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motorcycleDiv (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +run (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +motorcycleDiv (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +barsContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +querySelector (00:00:00), +( (00:00:00), +" (00:00:00), +. (00:00:00), +bars (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +containerWidth (00:00:00), += (00:00:00), +barsContainer (00:00:00), +? (00:00:00), +barsContainer (00:00:00), +. (00:00:00), +clientWidth (00:00:00), +: (00:00:00), +800 (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +animation (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +styleId (00:00:00), += (00:00:00), +" (00:00:00), +dynamic (00:00:00), +- (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +keyframes (00:00:00), +" (00:00:00), +; (00:00:00), +let (00:00:00), +styleTag (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +styleId (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +styleTag (00:00:00), +) (00:00:00), +{ (00:00:00), +styleTag (00:00:00), +. (00:00:00), +remove (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +styleTag (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +style (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +styleTag (00:00:00), +. (00:00:00), +id (00:00:00), += (00:00:00), +styleId (00:00:00), +; (00:00:00), +styleTag (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +` (00:00:00), +@ (00:00:00), +keyframes (00:00:00), +rideAcrossDynamic (00:00:00), +{ (00:00:00), +0 (00:00:00), +% (00:00:00), +{ (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +50px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +45 (00:00:00), +% (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +50 (00:00:00), +% (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +- (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +100 (00:00:00), +% (00:00:00), +{ (00:00:00), +left (00:00:00), +: (00:00:00), +$ (00:00:00), +{ (00:00:00), +containerWidth (00:00:00), ++ (00:00:00), +30 (00:00:00), +} (00:00:00), +px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +- (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +` (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +head (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +styleTag (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +animation (00:00:00), += (00:00:00), +" (00:00:00), +rideAcrossDynamic (00:00:00), +1 (00:00:00), +. (00:00:00), +8s (00:00:00), +cubic (00:00:00), +- (00:00:00), +bezier (00:00:00), +( (00:00:00), +0 (00:00:00), +. (00:00:00), +25 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +46 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +45 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +94 (00:00:00), +) (00:00:00), +forwards (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +onFinish (00:00:00), += (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +) (00:00:00), +{ (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +, (00:00:00), +2000 (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +removeEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +animationend (00:00:00), +" (00:00:00), +, (00:00:00), +onFinish (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +animationend (00:00:00), +" (00:00:00), +, (00:00:00), +onFinish (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +bubbleSortVisual (00:00:00), +let (00:00:00), +len (00:00:00), += (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +let (00:00:00), +swapped (00:00:00), +; (00:00:00), +len (00:00:00), +if (00:00:00), +( (00:00:00), +! (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +throw (00:00:00), +new (00:00:00), +Error (00:00:00), +( (00:00:00), +" (00:00:00), +Sorting (00:00:00), +cancelled (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +temp (00:00:00), +temp (00:00:00), +globalSpeed (00:00:00), +len (00:00:00), +- (00:00:00), +- (00:00:00), +async (00:00:00), +function (00:00:00), +startSorting (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +disabled (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +try (00:00:00), +{ (00:00:00), +await (00:00:00), +bubbleSortVisual (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +animateMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +error (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +Sorting (00:00:00), +interrupted (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +error (00:00:00), +. (00:00:00), +message (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +finally (00:00:00), +{ (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +resetAndStop (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +initRandomArray (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +renderBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +setupSpeedSlider (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +input (00:00:00), +" (00:00:00), +, (00:00:00), +function (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +e (00:00:00), +. (00:00:00), +target (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +change (00:00:00), +" (00:00:00), +, (00:00:00), +function (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +e (00:00:00), +. (00:00:00), +target (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +resetAndStop (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +sortBtn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +button (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +⚡ (00:00:00), +Start (00:00:00), +Bubble (00:00:00), +Sort (00:00:00), +" (00:00:00), +; (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +reset (00:00:00), +- (00:00:00), +button (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +background (00:00:00), += (00:00:00), +" (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +135deg (00:00:00), +, (00:00:00), +# (00:00:00), +f093fb (00:00:00), +0 (00:00:00), +% (00:00:00), +, (00:00:00), +# (00:00:00), +f5576c (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +controlsDiv (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +querySelector (00:00:00), +( (00:00:00), +" (00:00:00), +. (00:00:00), +controls (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +controlsDiv (00:00:00), +) (00:00:00), +{ (00:00:00), +controlsDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +sortBtn (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +async (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +startSorting (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +originalReset (00:00:00), += (00:00:00), +resetAndStop (00:00:00), +; (00:00:00), +window (00:00:00), +. (00:00:00), +resetAndStop (00:00:00), += (00:00:00), +resetAndStop (00:00:00), +; (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +removeEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +resetAndStop (00:00:00), +) (00:00:00), +; (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +initRandomArray (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +renderBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +window (00:00:00), +. (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +input (00:00:00), +" (00:00:00), +, (00:00:00), +function (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +e (00:00:00), +. (00:00:00), +target (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +window (00:00:00), +. (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Segoe (00:00:00), +UI (00:00:00), +' (00:00:00), +, (00:00:00), +Tahoma (00:00:00), +, (00:00:00), +Geneva (00:00:00), +, (00:00:00), +Verdana (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +135deg (00:00:00), +, (00:00:00), +# (00:00:00), +667eea (00:00:00), +0 (00:00:00), +% (00:00:00), +, (00:00:00), +# (00:00:00), +764ba2 (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +h1 (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +4px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +controls (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +15px (00:00:00), +25px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +15px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +wrap (00:00:00), +: (00:00:00), +wrap (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +speed (00:00:00), +- (00:00:00), +control (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +12px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +speed (00:00:00), +- (00:00:00), +control (00:00:00), +label (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speedSlider (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speedValue (00:00:00), +{ (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +45px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +764ba2 (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +reset (00:00:00), +- (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +135deg (00:00:00), +, (00:00:00), +# (00:00:00), +667eea (00:00:00), +0 (00:00:00), +% (00:00:00), +, (00:00:00), +# (00:00:00), +764ba2 (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +padding (0</t>
+  </si>
+  <si>
+    <t>+lang (00:00:00), += (00:00:00), +" (00:00:00), +en (00:00:00), +" (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +charset (00:00:00), += (00:00:00), +" (00:00:00), +UTF (00:00:00), +- (00:00:00), +8 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +meta (00:00:00), +name (00:00:00), += (00:00:00), +" (00:00:00), +viewport (00:00:00), +" (00:00:00), +content (00:00:00), += (00:00:00), +" (00:00:00), +width (00:00:00), += (00:00:00), +device (00:00:00), +- (00:00:00), +width (00:00:00), +, (00:00:00), +initial (00:00:00), +- (00:00:00), +scale (00:00:00), += (00:00:00), +1 (00:00:00), +. (00:00:00), +0 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +| (00:00:00), +Bubble (00:00:00), +Sort (00:00:00), +with (00:00:00), +Motorcycle (00:00:00), +Ride (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +· (00:00:00), +Bubble (00:00:00), +Sort (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +controls (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +speed (00:00:00), +- (00:00:00), +control (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +label (00:00:00), +for (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +&gt; (00:00:00), +⏩ (00:00:00), +Animation (00:00:00), +speed (00:00:00), +: (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +label (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +input (00:00:00), +type (00:00:00), += (00:00:00), +" (00:00:00), +range (00:00:00), +" (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +min (00:00:00), += (00:00:00), +" (00:00:00), +0 (00:00:00), +" (00:00:00), +max (00:00:00), += (00:00:00), +" (00:00:00), +200 (00:00:00), +" (00:00:00), +value (00:00:00), += (00:00:00), +" (00:00:00), +80 (00:00:00), +" (00:00:00), +step (00:00:00), += (00:00:00), +" (00:00:00), +5 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +span (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +&gt; (00:00:00), +80 (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +span (00:00:00), +&gt; (00:00:00), +ms (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +button (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +resetBtn (00:00:00), +" (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +reset (00:00:00), +- (00:00:00), +button (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🔄 (00:00:00), +New (00:00:00), +random (00:00:00), +array (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +button (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&gt; (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +bars (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +motorcycleZone (00:00:00), +" (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +zone (00:00:00), +" (00:00:00), +style (00:00:00), += (00:00:00), +" (00:00:00), +display (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +run (00:00:00), +" (00:00:00), +&gt; (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +class (00:00:00), += (00:00:00), +" (00:00:00), +info (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +&gt; (00:00:00), +✅ (00:00:00), +Sorting (00:00:00), +completed (00:00:00), +→ (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +motorcycle (00:00:00), +races (00:00:00), +across (00:00:00), +the (00:00:00), +bars (00:00:00), +from (00:00:00), +left (00:00:00), +to (00:00:00), +right (00:00:00), +! (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +p (00:00:00), +&gt; (00:00:00), +⚡ (00:00:00), +Speed (00:00:00), +slider (00:00:00), +adjusts (00:00:00), +delay (00:00:00), +between (00:00:00), +comparisons (00:00:00), +( (00:00:00), +lower (00:00:00), += (00:00:00), +faster (00:00:00), +) (00:00:00), +. (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +p (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+  </si>
+  <si>
+    <t>-# (00:00:42), -vis (00:00:43), -- (00:00:44), -123456 (00:00:45), -{ (00:00:46), -height (00:00:47), -: (00:00:48), -200px (00:00:49), -; (00:00:50), -display (00:00:51), -: (00:00:52), -flex (00:00:53), -; (00:00:54), -align (00:00:55), -- (00:00:56), -items (00:00:57), -: (00:00:58), -flex (00:00:59), -- (00:01:00), -end (00:01:01), -; (00:01:02), -} (00:01:03), -7px (00:01:09), -height (00:01:11), -: (00:01:12), -100 (00:01:13), -% (00:01:14), -; (00:01:15), -background (00:01:16), -- (00:01:17), -color (00:01:18), -: (00:01:19), -black (00:01:20), -; (00:01:21), -margin (00:01:22), -: (00:01:23), -0px (00:01:24), -1px (00:01:25), -; (00:01:26), +font (00:00:00), +- (00:00:00), +family (00:00:00), +: (00:00:00), +' (00:00:00), +Segoe (00:00:00), +UI (00:00:00), +' (00:00:00), +, (00:00:00), +Tahoma (00:00:00), +, (00:00:00), +Geneva (00:00:00), +, (00:00:00), +Verdana (00:00:00), +, (00:00:00), +sans (00:00:00), +- (00:00:00), +serif (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +135deg (00:00:00), +, (00:00:00), +# (00:00:00), +667eea (00:00:00), +0 (00:00:00), +% (00:00:00), +, (00:00:00), +# (00:00:00), +764ba2 (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +min (00:00:00), +- (00:00:00), +height (00:00:00), +: (00:00:00), +100vh (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +h1 (00:00:00), +{ (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +2px (00:00:00), +2px (00:00:00), +4px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +controls (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +15px (00:00:00), +25px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +15px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +bottom (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +flex (00:00:00), +- (00:00:00), +wrap (00:00:00), +: (00:00:00), +wrap (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +speed (00:00:00), +- (00:00:00), +control (00:00:00), +{ (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +12px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +speed (00:00:00), +- (00:00:00), +control (00:00:00), +label (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +16px (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speedSlider (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +speedValue (00:00:00), +{ (00:00:00), +min (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +45px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +764ba2 (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +reset (00:00:00), +- (00:00:00), +button (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +135deg (00:00:00), +, (00:00:00), +# (00:00:00), +667eea (00:00:00), +0 (00:00:00), +% (00:00:00), +, (00:00:00), +# (00:00:00), +764ba2 (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +white (00:00:00), +; (00:00:00), +border (00:00:00), +: (00:00:00), +none (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +8px (00:00:00), +20px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +cursor (00:00:00), +: (00:00:00), +pointer (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +weight (00:00:00), +: (00:00:00), +bold (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +transform (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +, (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +0 (00:00:00), +. (00:00:00), +2s (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +reset (00:00:00), +- (00:00:00), +button (00:00:00), +: (00:00:00), +hover (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scale (00:00:00), +( (00:00:00), +1 (00:00:00), +. (00:00:00), +05 (00:00:00), +) (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +4px (00:00:00), +12px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +rgba (00:00:00), +( (00:00:00), +255 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +95 (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +8px (00:00:00), +25px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +bars (00:00:00), +- (00:00:00), +container (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +350px (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +2px (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +} (00:00:00), +12px (00:00:00), +background (00:00:00), +: (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +180deg (00:00:00), +, (00:00:00), +# (00:00:00), +667eea (00:00:00), +0 (00:00:00), +% (00:00:00), +, (00:00:00), +# (00:00:00), +764ba2 (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +4px (00:00:00), +4px (00:00:00), +0 (00:00:00), +0 (00:00:00), +; (00:00:00), +transition (00:00:00), +: (00:00:00), +height (00:00:00), +0 (00:00:00), +. (00:00:00), +05s (00:00:00), +ease (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +1px (00:00:00), +3px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +2 (00:00:00), +) (00:00:00), +; (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +zone (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +relative (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +50px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +10px (00:00:00), +; (00:00:00), +overflow (00:00:00), +: (00:00:00), +visible (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +run (00:00:00), +{ (00:00:00), +position (00:00:00), +: (00:00:00), +absolute (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +32px (00:00:00), +; (00:00:00), +animation (00:00:00), +: (00:00:00), +rideAcross (00:00:00), +2s (00:00:00), +linear (00:00:00), +forwards (00:00:00), +; (00:00:00), +filter (00:00:00), +: (00:00:00), +drop (00:00:00), +- (00:00:00), +shadow (00:00:00), +( (00:00:00), +2px (00:00:00), +2px (00:00:00), +4px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +3 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +@ (00:00:00), +keyframes (00:00:00), +rideAcross (00:00:00), +{ (00:00:00), +0 (00:00:00), +% (00:00:00), +{ (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +40px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +49 (00:00:00), +% (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +50 (00:00:00), +% (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +- (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +100 (00:00:00), +% (00:00:00), +{ (00:00:00), +left (00:00:00), +: (00:00:00), +calc (00:00:00), +( (00:00:00), +100 (00:00:00), +% (00:00:00), ++ (00:00:00), +20px (00:00:00), +) (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +- (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +. (00:00:00), +info (00:00:00), +{ (00:00:00), +background (00:00:00), +: (00:00:00), +rgba (00:00:00), +( (00:00:00), +255 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +255 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +9 (00:00:00), +) (00:00:00), +; (00:00:00), +padding (00:00:00), +: (00:00:00), +12px (00:00:00), +25px (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +30px (00:00:00), +; (00:00:00), +margin (00:00:00), +- (00:00:00), +top (00:00:00), +: (00:00:00), +25px (00:00:00), +; (00:00:00), +text (00:00:00), +- (00:00:00), +align (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +14px (00:00:00), +; (00:00:00), +color (00:00:00), +: (00:00:00), +# (00:00:00), +333 (00:00:00), +; (00:00:00), +box (00:00:00), +- (00:00:00), +shadow (00:00:00), +: (00:00:00), +0 (00:00:00), +2px (00:00:00), +8px (00:00:00), +rgba (00:00:00), +( (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +info (00:00:00), +p (00:00:00), +{ (00:00:00), +margin (00:00:00), +: (00:00:00), +5px (00:00:00), +0 (00:00:00), +; (00:00:00), +} (00:00:00), +@ (00:00:00), +media (00:00:00), +( (00:00:00), +max (00:00:00), +- (00:00:00), +width (00:00:00), +: (00:00:00), +768px (00:00:00), +) (00:00:00), +{ (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +6px (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +controls (00:00:00), +{ (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +border (00:00:00), +- (00:00:00), +radius (00:00:00), +: (00:00:00), +20px (00:00:00), +; (00:00:00), +gap (00:00:00), +: (00:00:00), +15px (00:00:00), +; (00:00:00), +} (00:00:00), +h1 (00:00:00), +{ (00:00:00), +font (00:00:00), +- (00:00:00), +size (00:00:00), +: (00:00:00), +24px (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00)</t>
+  </si>
+  <si>
+    <t>-const (00:02:09), -count (00:02:10), -= (00:02:11), -50 (00:02:12), -; (00:02:13), -const (00:02:14), -array (00:02:15), -= (00:02:16), -new (00:02:17), -Array (00:02:18), -( (00:02:19), -count (00:02:20), -) (00:02:21), -; (00:02:22), -for (00:02:23), -( (00:02:24), -let (00:02:25), -i (00:02:26), -= (00:02:27), -0 (00:02:28), -; (00:02:29), -i (00:02:30), -&lt; (00:02:31), -count (00:02:32), -; (00:02:33), -i (00:02:34), -+ (00:02:35), -+ (00:02:36), -) (00:02:37), -{ (00:02:38), -array (00:02:39), -[ (00:02:40), -i (00:02:41), -] (00:02:42), -= (00:02:43), -Math (00:02:44), -. (00:02:45), -random (00:02:46), -( (00:02:47), -) (00:02:48), -; (00:02:49), -} (00:02:57), -const (00:02:58), -visualizer (00:02:59), -= (00:03:00), -document (00:03:01), -. (00:03:02), -getElementById (00:03:03), -( (00:03:04), -" (00:03:05), -vis (00:03:06), -- (00:03:07), -123456 (00:03:08), -" (00:03:09), -) (00:03:10), -; (00:03:11), -for (00:03:12), -( (00:03:13), -let (00:03:14), -i (00:03:15), -= (00:03:16), -0 (00:03:17), -; (00:03:18), -i (00:03:19), -&lt; (00:03:20), -array (00:03:21), -. (00:03:22), -length (00:03:23), -; (00:03:24), -i (00:03:25), -+ (00:03:26), -+ (00:03:27), -) (00:03:28), -{ (00:03:29), -const (00:03:30), -bar (00:03:31), -= (00:03:32), -document (00:03:33), -. (00:03:34), -createElement (00:03:35), -( (00:03:36), -" (00:03:37), -div (00:03:38), -" (00:03:39), -) (00:03:40), -; (00:03:41), -visualizer (00:03:42), -. (00:03:43), -appendChild (00:03:44), -( (00:03:45), -bar (00:03:46), -) (00:03:47), -; (00:03:48), -bar (00:03:49), -. (00:03:50), -classList (00:03:51), -. (00:03:52), -add (00:03:53), -( (00:03:54), -" (00:03:55), -bar (00:03:56), -" (00:03:57), -) (00:03:58), -; (00:03:59), -bar (00:04:00), -. (00:04:01), -style (00:04:02), -. (00:04:03), -height (00:04:04), -= (00:04:05), -array (00:04:06), -[ (00:04:07), -i (00:04:08), -] (00:04:09), -* (00:04:10), -100 (00:04:11), -+ (00:04:12), -" (00:04:13), -% (00:04:14), -" (00:04:15), -; (00:04:16), -} (00:04:36), -bubbleSort (00:04:37), -( (00:04:38), -array (00:04:39), -) (00:04:40), -; (00:04:41), -function (00:04:42), -updateBars (00:04:43), -( (00:04:44), -) (00:04:45), -{ (00:04:46), -const (00:04:47), -bars (00:04:48), -= (00:04:49), -document (00:04:50), -. (00:04:51), -getElementsByClassName (00:04:52), -( (00:04:53), -" (00:04:54), -bar (00:04:55), -" (00:04:56), -) (00:04:57), -; (00:04:58), -for (00:04:59), -( (00:05:00), -let (00:05:01), -i (00:05:02), -= (00:05:03), -0 (00:05:04), -; (00:05:05), -i (00:05:06), -&lt; (00:05:07), -bars (00:05:08), -. (00:05:09), -length (00:05:10), -; (00:05:11), -i (00:05:12), -+ (00:05:13), -+ (00:05:14), -) (00:05:15), -{ (00:05:16), -bars (00:05:17), -[ (00:05:18), -i (00:05:19), -] (00:05:20), -. (00:05:21), -style (00:05:22), -. (00:05:23), -height (00:05:24), -= (00:05:25), -array (00:05:26), -[ (00:05:27), -i (00:05:28), -] (00:05:29), -* (00:05:30), -100 (00:05:31), -+ (00:05:32), -" (00:05:33), -% (00:05:34), -" (00:05:35), -; (00:05:36), -} (00:05:37), -} (00:05:38), -bubbleSort (00:05:41), -var (00:05:48), -arr (00:06:02), -. (00:06:03), -length (00:06:04), -aux (00:06:27), -aux (00:06:53), -100 (00:07:14), +const (00:00:00), +count (00:00:00), += (00:00:00), +45 (00:00:00), +; (00:00:00), +let (00:00:00), +array (00:00:00), += (00:00:00), +new (00:00:00), +Array (00:00:00), +( (00:00:00), +count (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +let (00:00:00), +currentSortingPromise (00:00:00), += (00:00:00), +null (00:00:00), +; (00:00:00), +let (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +80 (00:00:00), +; (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedSlider (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedSlider (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +speedValue (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +speedValue (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +resetBtn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +resetBtn (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motorcycleZone (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycleZone (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +function (00:00:00), +initRandomArray (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +Math (00:00:00), +. (00:00:00), +random (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +renderBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +while (00:00:00), +( (00:00:00), +visualizer (00:00:00), +. (00:00:00), +firstChild (00:00:00), +) (00:00:00), +{ (00:00:00), +visualizer (00:00:00), +. (00:00:00), +removeChild (00:00:00), +( (00:00:00), +visualizer (00:00:00), +. (00:00:00), +firstChild (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +bar (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +&amp; (00:00:00), +&amp; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +existingRun (00:00:00), += (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +querySelector (00:00:00), +( (00:00:00), +" (00:00:00), +. (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +run (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +existingRun (00:00:00), +) (00:00:00), +{ (00:00:00), +existingRun (00:00:00), +. (00:00:00), +remove (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +animateMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +motorcycleDiv (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +run (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +🏍 (00:00:00), +️ (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +motorcycleDiv (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), += (00:00:00), +" (00:00:00), +block (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +barsContainer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +querySelector (00:00:00), +( (00:00:00), +" (00:00:00), +. (00:00:00), +bars (00:00:00), +- (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +containerWidth (00:00:00), += (00:00:00), +barsContainer (00:00:00), +? (00:00:00), +barsContainer (00:00:00), +. (00:00:00), +clientWidth (00:00:00), +: (00:00:00), +800 (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +animation (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +offsetHeight (00:00:00), +; (00:00:00), +const (00:00:00), +styleId (00:00:00), += (00:00:00), +" (00:00:00), +dynamic (00:00:00), +- (00:00:00), +motorcycle (00:00:00), +- (00:00:00), +keyframes (00:00:00), +" (00:00:00), +; (00:00:00), +let (00:00:00), +styleTag (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +styleId (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +styleTag (00:00:00), +) (00:00:00), +{ (00:00:00), +styleTag (00:00:00), +. (00:00:00), +remove (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +styleTag (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +style (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +styleTag (00:00:00), +. (00:00:00), +id (00:00:00), += (00:00:00), +styleId (00:00:00), +; (00:00:00), +styleTag (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +` (00:00:00), +@ (00:00:00), +keyframes (00:00:00), +rideAcrossDynamic (00:00:00), +{ (00:00:00), +0 (00:00:00), +% (00:00:00), +{ (00:00:00), +left (00:00:00), +: (00:00:00), +- (00:00:00), +50px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +45 (00:00:00), +% (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +50 (00:00:00), +% (00:00:00), +{ (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +- (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +100 (00:00:00), +% (00:00:00), +{ (00:00:00), +left (00:00:00), +: (00:00:00), +$ (00:00:00), +{ (00:00:00), +containerWidth (00:00:00), ++ (00:00:00), +30 (00:00:00), +} (00:00:00), +px (00:00:00), +; (00:00:00), +transform (00:00:00), +: (00:00:00), +scaleX (00:00:00), +( (00:00:00), +- (00:00:00), +1 (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +` (00:00:00), +; (00:00:00), +document (00:00:00), +. (00:00:00), +head (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +styleTag (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +animation (00:00:00), += (00:00:00), +" (00:00:00), +rideAcrossDynamic (00:00:00), +1 (00:00:00), +. (00:00:00), +8s (00:00:00), +cubic (00:00:00), +- (00:00:00), +bezier (00:00:00), +( (00:00:00), +0 (00:00:00), +. (00:00:00), +25 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +46 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +45 (00:00:00), +, (00:00:00), +0 (00:00:00), +. (00:00:00), +94 (00:00:00), +) (00:00:00), +forwards (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +onFinish (00:00:00), += (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +motorcycleZone (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +display (00:00:00), +! (00:00:00), += (00:00:00), += (00:00:00), +" (00:00:00), +none (00:00:00), +" (00:00:00), +) (00:00:00), +{ (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +, (00:00:00), +2000 (00:00:00), +) (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +removeEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +animationend (00:00:00), +" (00:00:00), +, (00:00:00), +onFinish (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +; (00:00:00), +motorcycleDiv (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +animationend (00:00:00), +" (00:00:00), +, (00:00:00), +onFinish (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +bubbleSortVisual (00:00:00), +let (00:00:00), +len (00:00:00), += (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +let (00:00:00), +swapped (00:00:00), +; (00:00:00), +len (00:00:00), +if (00:00:00), +( (00:00:00), +! (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +throw (00:00:00), +new (00:00:00), +Error (00:00:00), +( (00:00:00), +" (00:00:00), +Sorting (00:00:00), +cancelled (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +temp (00:00:00), +temp (00:00:00), +globalSpeed (00:00:00), +len (00:00:00), +- (00:00:00), +- (00:00:00), +async (00:00:00), +function (00:00:00), +startSorting (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +disabled (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +try (00:00:00), +{ (00:00:00), +await (00:00:00), +bubbleSortVisual (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +animateMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +catch (00:00:00), +( (00:00:00), +error (00:00:00), +) (00:00:00), +{ (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +Sorting (00:00:00), +interrupted (00:00:00), +: (00:00:00), +" (00:00:00), +, (00:00:00), +error (00:00:00), +. (00:00:00), +message (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +finally (00:00:00), +{ (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +function (00:00:00), +resetAndStop (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +initRandomArray (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +renderBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +function (00:00:00), +setupSpeedSlider (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +input (00:00:00), +" (00:00:00), +, (00:00:00), +function (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +e (00:00:00), +. (00:00:00), +target (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +change (00:00:00), +" (00:00:00), +, (00:00:00), +function (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +e (00:00:00), +. (00:00:00), +target (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +resetAndStop (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +sortBtn (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +button (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +" (00:00:00), +⚡ (00:00:00), +Start (00:00:00), +Bubble (00:00:00), +Sort (00:00:00), +" (00:00:00), +; (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +reset (00:00:00), +- (00:00:00), +button (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +background (00:00:00), += (00:00:00), +" (00:00:00), +linear (00:00:00), +- (00:00:00), +gradient (00:00:00), +( (00:00:00), +135deg (00:00:00), +, (00:00:00), +# (00:00:00), +f093fb (00:00:00), +0 (00:00:00), +% (00:00:00), +, (00:00:00), +# (00:00:00), +f5576c (00:00:00), +100 (00:00:00), +% (00:00:00), +) (00:00:00), +" (00:00:00), +; (00:00:00), +const (00:00:00), +controlsDiv (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +querySelector (00:00:00), +( (00:00:00), +" (00:00:00), +. (00:00:00), +controls (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +if (00:00:00), +( (00:00:00), +controlsDiv (00:00:00), +) (00:00:00), +{ (00:00:00), +controlsDiv (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +sortBtn (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +sortBtn (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +async (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +return (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +startSorting (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +const (00:00:00), +originalReset (00:00:00), += (00:00:00), +resetAndStop (00:00:00), +; (00:00:00), +window (00:00:00), +. (00:00:00), +resetAndStop (00:00:00), += (00:00:00), +resetAndStop (00:00:00), +; (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +removeEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +resetAndStop (00:00:00), +) (00:00:00), +; (00:00:00), +resetBtn (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +click (00:00:00), +" (00:00:00), +, (00:00:00), +( (00:00:00), +) (00:00:00), += (00:00:00), +&gt; (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +sortingInProgress (00:00:00), +) (00:00:00), +{ (00:00:00), +sortingInProgress (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +} (00:00:00), +hideMotorcycle (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +initRandomArray (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +renderBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00), +window (00:00:00), +. (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +speedSlider (00:00:00), +. (00:00:00), +addEventListener (00:00:00), +( (00:00:00), +" (00:00:00), +input (00:00:00), +" (00:00:00), +, (00:00:00), +function (00:00:00), +( (00:00:00), +e (00:00:00), +) (00:00:00), +{ (00:00:00), +globalSpeed (00:00:00), += (00:00:00), +parseInt (00:00:00), +( (00:00:00), +e (00:00:00), +. (00:00:00), +target (00:00:00), +. (00:00:00), +value (00:00:00), +) (00:00:00), +; (00:00:00), +window (00:00:00), +. (00:00:00), +var (00:00:00), +_ (00:00:00), +speed (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +speedValue (00:00:00), +. (00:00:00), +textContent (00:00:00), += (00:00:00), +globalSpeed (00:00:00), +; (00:00:00), +} (00:00:00), +) (00:00:00), +; (00:00:00)</t>
+  </si>
+  <si>
+    <t>01100</t>
+  </si>
+  <si>
+    <t>00010</t>
+  </si>
+  <si>
+    <t>01110</t>
+  </si>
+  <si>
+    <t>00100</t>
+  </si>
+  <si>
+    <t>00110</t>
+  </si>
+  <si>
+    <t>01101</t>
+  </si>
+  <si>
+    <t>00000</t>
+  </si>
+  <si>
+    <t>11111</t>
+  </si>
+  <si>
+    <t>00001</t>
+  </si>
+  <si>
+    <t>10100</t>
+  </si>
+  <si>
+    <t>10111</t>
+  </si>
+  <si>
+    <t>01111</t>
+  </si>
+  <si>
+    <t>00111</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4649,6 +5665,10 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Segoe UI Emoji"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -4657,7 +5677,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4676,6 +5696,18 @@
         <bgColor rgb="FFFFDD88"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
+        <bgColor rgb="FFCCFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor rgb="FFFFCCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -4689,13 +5721,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5000,8 +6037,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC99"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AC100"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -5029,7 +6066,7 @@
     <col min="28" max="29" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5105,7 +6142,7 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="8" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="1" t="s">
@@ -5118,7 +6155,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5128,12 +6165,12 @@
       <c r="C2" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" s="4"/>
+      <c r="Z2" s="9"/>
       <c r="AC2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5143,12 +6180,12 @@
       <c r="C3" t="s">
         <v>30</v>
       </c>
-      <c r="Z3" s="4"/>
+      <c r="Z3" s="9"/>
       <c r="AC3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5158,11 +6195,14 @@
       <c r="C4" t="s">
         <v>30</v>
       </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
       <c r="E4">
         <v>100</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4">
         <v>38</v>
@@ -5171,25 +6211,25 @@
         <v>44.1</v>
       </c>
       <c r="I4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J4">
         <v>38.9</v>
       </c>
       <c r="K4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L4">
         <v>58.5</v>
       </c>
       <c r="M4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N4">
         <v>42.1</v>
       </c>
       <c r="O4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P4">
         <v>242</v>
@@ -5216,16 +6256,16 @@
         <v>4</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z4" s="5" t="s">
         <v>41</v>
       </c>
+      <c r="Z4" s="10" t="s">
+        <v>401</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5235,11 +6275,14 @@
       <c r="C5" t="s">
         <v>30</v>
       </c>
+      <c r="D5" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E5">
         <v>100</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5">
         <v>38</v>
@@ -5248,25 +6291,25 @@
         <v>52.4</v>
       </c>
       <c r="I5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J5">
         <v>27.8</v>
       </c>
       <c r="K5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L5">
         <v>93.8</v>
       </c>
       <c r="M5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N5">
         <v>49.3</v>
       </c>
       <c r="O5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P5">
         <v>205</v>
@@ -5293,13 +6336,13 @@
         <v>1</v>
       </c>
       <c r="X5" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z5" s="5" t="s">
         <v>49</v>
       </c>
+      <c r="Z5" s="10" t="s">
+        <v>402</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5309,6 +6352,9 @@
       <c r="C6" t="s">
         <v>30</v>
       </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
       <c r="E6">
         <v>100</v>
       </c>
@@ -5367,60 +6413,63 @@
         <v>5</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y6" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z6" s="5" t="s">
-        <v>56</v>
+        <v>41</v>
+      </c>
+      <c r="Z6" s="10" t="s">
+        <v>403</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="Z7" s="4"/>
+      <c r="Z7" s="9"/>
       <c r="AC7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
       </c>
-      <c r="Z8" s="4"/>
+      <c r="Z8" s="9"/>
       <c r="AC8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
         <v>30</v>
       </c>
+      <c r="D9" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E9">
         <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>40</v>
@@ -5429,25 +6478,25 @@
         <v>32.4</v>
       </c>
       <c r="I9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J9">
         <v>4.2</v>
       </c>
       <c r="K9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L9">
         <v>29.2</v>
       </c>
       <c r="M9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N9">
         <v>40.1</v>
       </c>
       <c r="O9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P9">
         <v>291</v>
@@ -5474,57 +6523,60 @@
         <v>2</v>
       </c>
       <c r="X9" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z9" s="5" t="s">
         <v>49</v>
       </c>
+      <c r="Z9" s="10" t="s">
+        <v>402</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
         <v>30</v>
       </c>
-      <c r="Z10" s="4"/>
+      <c r="Z10" s="9"/>
       <c r="AC10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="Z11" s="4"/>
+      <c r="Z11" s="9"/>
       <c r="AC11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
         <v>30</v>
       </c>
+      <c r="D12" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E12">
         <v>100</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G12">
         <v>38.9</v>
@@ -5533,25 +6585,25 @@
         <v>35</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J12">
         <v>34.700000000000003</v>
       </c>
       <c r="K12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L12">
         <v>53.8</v>
       </c>
       <c r="M12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N12">
         <v>30.8</v>
       </c>
       <c r="O12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P12">
         <v>279</v>
@@ -5577,46 +6629,49 @@
       <c r="W12">
         <v>7</v>
       </c>
-      <c r="X12" s="3" t="s">
+      <c r="X12" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y12" t="s">
         <v>73</v>
       </c>
-      <c r="Y12" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z12" s="5" t="s">
-        <v>75</v>
+      <c r="Z12" s="10" t="s">
+        <v>404</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
         <v>30</v>
       </c>
-      <c r="Z13" s="4"/>
+      <c r="Z13" s="9"/>
       <c r="AC13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
         <v>30</v>
       </c>
+      <c r="D14" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E14">
         <v>100</v>
       </c>
       <c r="F14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G14">
         <v>38</v>
@@ -5625,25 +6680,25 @@
         <v>59.9</v>
       </c>
       <c r="I14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J14">
         <v>27.8</v>
       </c>
       <c r="K14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L14">
         <v>66.2</v>
       </c>
       <c r="M14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N14">
         <v>66.400000000000006</v>
       </c>
       <c r="O14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P14">
         <v>173</v>
@@ -5670,87 +6725,90 @@
         <v>1</v>
       </c>
       <c r="X14" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z14" s="5" t="s">
         <v>49</v>
       </c>
+      <c r="Z14" s="10" t="s">
+        <v>402</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
         <v>30</v>
       </c>
-      <c r="Z15" s="4"/>
+      <c r="Z15" s="9"/>
       <c r="AC15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
         <v>30</v>
       </c>
-      <c r="Z16" s="4"/>
+      <c r="Z16" s="9"/>
       <c r="AC16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
         <v>30</v>
       </c>
-      <c r="Z17" s="5"/>
+      <c r="Z17" s="10"/>
       <c r="AC17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
         <v>30</v>
       </c>
-      <c r="Z18" s="4"/>
+      <c r="Z18" s="9"/>
       <c r="AC18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
         <v>30</v>
       </c>
+      <c r="D19" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E19">
         <v>100</v>
       </c>
       <c r="F19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G19">
         <v>38.799999999999997</v>
@@ -5759,25 +6817,25 @@
         <v>41.5</v>
       </c>
       <c r="I19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J19">
         <v>22.2</v>
       </c>
       <c r="K19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L19">
         <v>35.4</v>
       </c>
       <c r="M19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N19">
         <v>47.6</v>
       </c>
       <c r="O19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P19">
         <v>252</v>
@@ -5803,46 +6861,49 @@
       <c r="W19">
         <v>2</v>
       </c>
-      <c r="X19" s="3" t="s">
+      <c r="X19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y19" t="s">
         <v>73</v>
       </c>
-      <c r="Y19" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z19" s="5" t="s">
-        <v>93</v>
+      <c r="Z19" s="10" t="s">
+        <v>405</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
         <v>30</v>
       </c>
-      <c r="Z20" s="4"/>
+      <c r="Z20" s="9"/>
       <c r="AC20" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
         <v>30</v>
       </c>
+      <c r="D21" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E21">
         <v>100</v>
       </c>
       <c r="F21" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G21">
         <v>40.5</v>
@@ -5851,25 +6912,25 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L21">
         <v>69.2</v>
       </c>
       <c r="M21" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="N21">
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P21">
         <v>477</v>
@@ -5896,60 +6957,63 @@
         <v>6</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Y21" t="s">
-        <v>102</v>
-      </c>
-      <c r="Z21" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
+      </c>
+      <c r="Z21" s="10" t="s">
+        <v>406</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
         <v>30</v>
       </c>
-      <c r="Z22" s="5"/>
+      <c r="Z22" s="10"/>
       <c r="AC22" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s">
         <v>30</v>
       </c>
-      <c r="Z23" s="5"/>
+      <c r="Z23" s="10"/>
       <c r="AC23" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
         <v>30</v>
       </c>
+      <c r="D24" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E24">
         <v>100</v>
       </c>
       <c r="F24" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G24">
         <v>41.4</v>
@@ -5958,25 +7022,25 @@
         <v>17.7</v>
       </c>
       <c r="I24" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J24">
         <v>13.9</v>
       </c>
       <c r="K24" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="N24">
         <v>44.9</v>
       </c>
       <c r="O24" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="P24">
         <v>354</v>
@@ -6003,27 +7067,30 @@
         <v>1</v>
       </c>
       <c r="X24" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z24" s="5" t="s">
-        <v>112</v>
+        <v>49</v>
+      </c>
+      <c r="Z24" s="10" t="s">
+        <v>407</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
+      <c r="D25" t="s">
+        <v>34</v>
+      </c>
       <c r="E25">
         <v>100</v>
       </c>
       <c r="F25" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G25">
         <v>39.6</v>
@@ -6032,25 +7099,25 @@
         <v>40.799999999999997</v>
       </c>
       <c r="I25" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="L25">
         <v>40</v>
       </c>
       <c r="M25" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="N25">
         <v>52.1</v>
       </c>
       <c r="O25" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="P25">
         <v>254</v>
@@ -6076,61 +7143,64 @@
       <c r="W25">
         <v>1</v>
       </c>
-      <c r="X25" s="3" t="s">
+      <c r="X25" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y25" t="s">
         <v>73</v>
       </c>
-      <c r="Y25" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z25" s="5" t="s">
-        <v>75</v>
+      <c r="Z25" s="10" t="s">
+        <v>404</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
         <v>30</v>
       </c>
-      <c r="Z26" s="5"/>
+      <c r="Z26" s="10"/>
       <c r="AC26" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s">
         <v>30</v>
       </c>
-      <c r="Z27" s="5"/>
+      <c r="Z27" s="10"/>
       <c r="AC27" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
         <v>30</v>
       </c>
+      <c r="D28" t="s">
+        <v>34</v>
+      </c>
       <c r="E28">
         <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G28">
         <v>34.4</v>
@@ -6139,25 +7209,25 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="N28">
         <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="P28">
         <v>966</v>
@@ -6184,45 +7254,48 @@
         <v>292</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y28" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z28" s="5" t="s">
-        <v>127</v>
+        <v>41</v>
+      </c>
+      <c r="Z28" s="10" t="s">
+        <v>408</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s">
         <v>30</v>
       </c>
-      <c r="Z29" s="5"/>
+      <c r="Z29" s="10"/>
       <c r="AC29" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C30" t="s">
         <v>30</v>
       </c>
+      <c r="D30" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E30">
         <v>100</v>
       </c>
       <c r="F30" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G30">
         <v>38.700000000000003</v>
@@ -6231,25 +7304,25 @@
         <v>62.7</v>
       </c>
       <c r="I30" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="J30">
         <v>5.6</v>
       </c>
       <c r="K30" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="L30">
         <v>30.8</v>
       </c>
       <c r="M30" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="N30">
         <v>83.9</v>
       </c>
       <c r="O30" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="P30">
         <v>161</v>
@@ -6276,27 +7349,30 @@
         <v>1</v>
       </c>
       <c r="X30" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z30" s="5" t="s">
         <v>49</v>
       </c>
+      <c r="Z30" s="10" t="s">
+        <v>402</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C31" t="s">
         <v>30</v>
       </c>
+      <c r="D31" t="s">
+        <v>34</v>
+      </c>
       <c r="E31">
         <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G31">
         <v>34.200000000000003</v>
@@ -6305,25 +7381,25 @@
         <v>22.4</v>
       </c>
       <c r="I31" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="N31">
         <v>71.599999999999994</v>
       </c>
       <c r="O31" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="P31">
         <v>334</v>
@@ -6350,87 +7426,90 @@
         <v>1</v>
       </c>
       <c r="X31" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z31" s="5" t="s">
-        <v>141</v>
+        <v>49</v>
+      </c>
+      <c r="Z31" s="10" t="s">
+        <v>409</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C32" t="s">
         <v>30</v>
       </c>
-      <c r="Z32" s="5"/>
+      <c r="Z32" s="10"/>
       <c r="AC32" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C33" t="s">
         <v>30</v>
       </c>
-      <c r="Z33" s="4"/>
+      <c r="Z33" s="9"/>
       <c r="AC33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C34" t="s">
         <v>30</v>
       </c>
-      <c r="Z34" s="4"/>
+      <c r="Z34" s="9"/>
       <c r="AC34" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C35" t="s">
         <v>30</v>
       </c>
-      <c r="Z35" s="4"/>
+      <c r="Z35" s="9"/>
       <c r="AC35" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C36" t="s">
         <v>30</v>
       </c>
+      <c r="D36" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E36">
         <v>100</v>
       </c>
       <c r="F36" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="G36">
         <v>38.200000000000003</v>
@@ -6439,25 +7518,25 @@
         <v>47.6</v>
       </c>
       <c r="I36" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="J36">
         <v>20.8</v>
       </c>
       <c r="K36" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="L36">
         <v>29.2</v>
       </c>
       <c r="M36" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="N36">
         <v>58.2</v>
       </c>
       <c r="O36" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="P36">
         <v>228</v>
@@ -6484,90 +7563,93 @@
         <v>3</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y36" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z36" s="5" t="s">
-        <v>56</v>
+        <v>41</v>
+      </c>
+      <c r="Z36" s="10" t="s">
+        <v>403</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C37" t="s">
         <v>30</v>
       </c>
-      <c r="Z37" s="5"/>
+      <c r="Z37" s="10"/>
       <c r="AC37" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C38" t="s">
         <v>30</v>
       </c>
-      <c r="Z38" s="4"/>
+      <c r="Z38" s="9"/>
       <c r="AC38" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C39" t="s">
         <v>30</v>
       </c>
-      <c r="Z39" s="5"/>
+      <c r="Z39" s="10"/>
       <c r="AC39" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C40" t="s">
         <v>30</v>
       </c>
-      <c r="Z40" s="4"/>
+      <c r="Z40" s="9"/>
       <c r="AC40" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C41" t="s">
         <v>30</v>
       </c>
+      <c r="D41" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E41">
         <v>100</v>
       </c>
       <c r="F41" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G41">
         <v>41.8</v>
@@ -6576,25 +7658,25 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="L41">
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="N41">
         <v>0</v>
       </c>
       <c r="O41" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="P41">
         <v>664</v>
@@ -6621,30 +7703,33 @@
         <v>102</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y41" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z41" s="5" t="s">
-        <v>103</v>
+        <v>41</v>
+      </c>
+      <c r="Z41" s="10" t="s">
+        <v>406</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C42" t="s">
         <v>30</v>
       </c>
+      <c r="D42" t="s">
+        <v>34</v>
+      </c>
       <c r="E42">
         <v>100</v>
       </c>
       <c r="F42" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="G42">
         <v>40.6</v>
@@ -6653,25 +7738,25 @@
         <v>20</v>
       </c>
       <c r="I42" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="J42">
         <v>6.9</v>
       </c>
       <c r="K42" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="L42">
         <v>6.2</v>
       </c>
       <c r="M42" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="N42">
         <v>26.4</v>
       </c>
       <c r="O42" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="P42">
         <v>345</v>
@@ -6697,61 +7782,64 @@
       <c r="W42">
         <v>3</v>
       </c>
-      <c r="X42" s="3" t="s">
+      <c r="X42" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y42" t="s">
         <v>73</v>
       </c>
-      <c r="Y42" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z42" s="5" t="s">
-        <v>93</v>
+      <c r="Z42" s="10" t="s">
+        <v>405</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C43" t="s">
         <v>30</v>
       </c>
-      <c r="Z43" s="4"/>
+      <c r="Z43" s="9"/>
       <c r="AC43" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C44" t="s">
         <v>30</v>
       </c>
-      <c r="Z44" s="4"/>
+      <c r="Z44" s="9"/>
       <c r="AC44" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C45" t="s">
         <v>30</v>
       </c>
+      <c r="D45" t="s">
+        <v>34</v>
+      </c>
       <c r="E45">
         <v>100</v>
       </c>
       <c r="F45" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="G45">
         <v>38.1</v>
@@ -6760,25 +7848,25 @@
         <v>42</v>
       </c>
       <c r="I45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="J45">
         <v>22.2</v>
       </c>
       <c r="K45" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="L45">
         <v>52.3</v>
       </c>
       <c r="M45" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="N45">
         <v>44.5</v>
       </c>
       <c r="O45" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="P45">
         <v>250</v>
@@ -6804,31 +7892,34 @@
       <c r="W45">
         <v>4</v>
       </c>
-      <c r="X45" s="3" t="s">
+      <c r="X45" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y45" t="s">
         <v>73</v>
       </c>
-      <c r="Y45" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z45" s="5" t="s">
-        <v>93</v>
+      <c r="Z45" s="10" t="s">
+        <v>405</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C46" t="s">
         <v>30</v>
       </c>
+      <c r="D46" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E46">
         <v>100</v>
       </c>
       <c r="F46" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="G46">
         <v>63.4</v>
@@ -6837,25 +7928,25 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J46">
         <v>19.399999999999999</v>
       </c>
       <c r="K46" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="N46">
         <v>0</v>
       </c>
       <c r="O46" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="P46">
         <v>635</v>
@@ -6882,30 +7973,33 @@
         <v>1</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y46" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z46" s="5" t="s">
-        <v>56</v>
+        <v>41</v>
+      </c>
+      <c r="Z46" s="10" t="s">
+        <v>403</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C47" t="s">
         <v>30</v>
       </c>
+      <c r="D47" t="s">
+        <v>34</v>
+      </c>
       <c r="E47">
         <v>100</v>
       </c>
       <c r="F47" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="G47">
         <v>37.6</v>
@@ -6914,25 +8008,25 @@
         <v>63.6</v>
       </c>
       <c r="I47" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="J47">
         <v>22.2</v>
       </c>
       <c r="K47" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="L47">
         <v>78.5</v>
       </c>
       <c r="M47" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="N47">
         <v>70.5</v>
       </c>
       <c r="O47" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="P47">
         <v>156</v>
@@ -6959,30 +8053,33 @@
         <v>1</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y47" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z47" s="5" t="s">
-        <v>56</v>
+        <v>41</v>
+      </c>
+      <c r="Z47" s="10" t="s">
+        <v>403</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C48" t="s">
         <v>30</v>
       </c>
+      <c r="D48" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E48">
         <v>100</v>
       </c>
       <c r="F48" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G48">
         <v>36.700000000000003</v>
@@ -6991,25 +8088,25 @@
         <v>32.4</v>
       </c>
       <c r="I48" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="J48">
         <v>41.7</v>
       </c>
       <c r="K48" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="L48">
         <v>12.3</v>
       </c>
       <c r="M48" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="N48">
         <v>34.6</v>
       </c>
       <c r="O48" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="P48">
         <v>292</v>
@@ -7036,42 +8133,45 @@
         <v>7</v>
       </c>
       <c r="X48" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z48" s="5" t="s">
         <v>49</v>
       </c>
+      <c r="Z48" s="10" t="s">
+        <v>402</v>
+      </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C49" t="s">
         <v>30</v>
       </c>
-      <c r="Z49" s="4"/>
+      <c r="Z49" s="9"/>
       <c r="AC49" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C50" t="s">
         <v>30</v>
       </c>
+      <c r="D50" t="s">
+        <v>34</v>
+      </c>
       <c r="E50">
         <v>100</v>
       </c>
       <c r="F50" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G50">
         <v>100</v>
@@ -7080,25 +8180,25 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L50">
         <v>0</v>
       </c>
       <c r="M50" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="N50">
         <v>10.3</v>
       </c>
       <c r="O50" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="P50">
         <v>470</v>
@@ -7125,30 +8225,33 @@
         <v>0</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y50" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z50" s="5" t="s">
-        <v>56</v>
+        <v>41</v>
+      </c>
+      <c r="Z50" s="10" t="s">
+        <v>403</v>
       </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C51" t="s">
         <v>30</v>
       </c>
+      <c r="D51" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E51">
         <v>100</v>
       </c>
       <c r="F51" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="G51">
         <v>39</v>
@@ -7157,25 +8260,25 @@
         <v>47.1</v>
       </c>
       <c r="I51" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="J51">
         <v>23.6</v>
       </c>
       <c r="K51" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="L51">
         <v>47.7</v>
       </c>
       <c r="M51" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="N51">
         <v>52.7</v>
       </c>
       <c r="O51" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="P51">
         <v>228</v>
@@ -7202,87 +8305,90 @@
         <v>6</v>
       </c>
       <c r="X51" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z51" s="5" t="s">
         <v>49</v>
       </c>
+      <c r="Z51" s="10" t="s">
+        <v>402</v>
+      </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C52" t="s">
         <v>30</v>
       </c>
-      <c r="Z52" s="5"/>
+      <c r="Z52" s="10"/>
       <c r="AC52" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C53" t="s">
         <v>30</v>
       </c>
-      <c r="Z53" s="4"/>
+      <c r="Z53" s="9"/>
       <c r="AC53" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C54" t="s">
         <v>30</v>
       </c>
-      <c r="Z54" s="5"/>
+      <c r="Z54" s="10"/>
       <c r="AC54" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C55" t="s">
         <v>30</v>
       </c>
-      <c r="Z55" s="4"/>
+      <c r="Z55" s="9"/>
       <c r="AC55" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C56" t="s">
         <v>30</v>
       </c>
+      <c r="D56" t="s">
+        <v>34</v>
+      </c>
       <c r="E56">
         <v>100</v>
       </c>
       <c r="F56" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="G56">
         <v>39.1</v>
@@ -7291,25 +8397,25 @@
         <v>27.5</v>
       </c>
       <c r="I56" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="J56">
         <v>34.700000000000003</v>
       </c>
       <c r="K56" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="L56">
         <v>87.7</v>
       </c>
       <c r="M56" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N56">
         <v>12.3</v>
       </c>
       <c r="O56" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="P56">
         <v>311</v>
@@ -7336,60 +8442,63 @@
         <v>2</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y56" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z56" s="5" t="s">
         <v>41</v>
       </c>
+      <c r="Z56" s="10" t="s">
+        <v>401</v>
+      </c>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C57" t="s">
         <v>30</v>
       </c>
-      <c r="Z57" s="4"/>
+      <c r="Z57" s="9"/>
       <c r="AC57" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C58" t="s">
         <v>30</v>
       </c>
-      <c r="Z58" s="4"/>
+      <c r="Z58" s="9"/>
       <c r="AC58" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C59" t="s">
         <v>30</v>
       </c>
+      <c r="D59" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E59">
         <v>100</v>
       </c>
       <c r="F59" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G59">
         <v>38.700000000000003</v>
@@ -7398,25 +8507,25 @@
         <v>49.9</v>
       </c>
       <c r="I59" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="J59">
         <v>34.700000000000003</v>
       </c>
       <c r="K59" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="L59">
         <v>47.7</v>
       </c>
       <c r="M59" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="N59">
         <v>54.1</v>
       </c>
       <c r="O59" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="P59">
         <v>215</v>
@@ -7442,46 +8551,49 @@
       <c r="W59">
         <v>1</v>
       </c>
-      <c r="X59" s="3" t="s">
+      <c r="X59" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y59" t="s">
         <v>73</v>
       </c>
-      <c r="Y59" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z59" s="5" t="s">
-        <v>93</v>
+      <c r="Z59" s="10" t="s">
+        <v>405</v>
       </c>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C60" t="s">
         <v>30</v>
       </c>
-      <c r="Z60" s="5"/>
+      <c r="Z60" s="10"/>
       <c r="AC60" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C61" t="s">
         <v>30</v>
       </c>
+      <c r="D61" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E61">
         <v>100</v>
       </c>
       <c r="F61" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G61">
         <v>37.700000000000003</v>
@@ -7490,25 +8602,25 @@
         <v>37.299999999999997</v>
       </c>
       <c r="I61" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="J61">
         <v>29.2</v>
       </c>
       <c r="K61" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="L61">
         <v>32.299999999999997</v>
       </c>
       <c r="M61" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N61">
         <v>40.4</v>
       </c>
       <c r="O61" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="P61">
         <v>275</v>
@@ -7534,31 +8646,34 @@
       <c r="W61">
         <v>21</v>
       </c>
-      <c r="X61" s="3" t="s">
+      <c r="X61" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y61" t="s">
         <v>73</v>
       </c>
-      <c r="Y61" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z61" s="5" t="s">
-        <v>93</v>
+      <c r="Z61" s="10" t="s">
+        <v>405</v>
       </c>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="C62" t="s">
         <v>30</v>
       </c>
+      <c r="D62" t="s">
+        <v>226</v>
+      </c>
       <c r="E62">
         <v>100</v>
       </c>
       <c r="F62" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G62">
         <v>39.5</v>
@@ -7567,25 +8682,25 @@
         <v>28.9</v>
       </c>
       <c r="I62" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="J62">
         <v>27.8</v>
       </c>
       <c r="K62" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="L62">
         <v>50.8</v>
       </c>
       <c r="M62" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="N62">
         <v>24.3</v>
       </c>
       <c r="O62" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="P62">
         <v>306</v>
@@ -7612,72 +8727,75 @@
         <v>1</v>
       </c>
       <c r="X62" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z62" s="5" t="s">
-        <v>112</v>
+        <v>49</v>
+      </c>
+      <c r="Z62" s="10" t="s">
+        <v>407</v>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C63" t="s">
         <v>30</v>
       </c>
-      <c r="Z63" s="4"/>
+      <c r="Z63" s="9"/>
       <c r="AC63" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C64" t="s">
         <v>30</v>
       </c>
-      <c r="Z64" s="5"/>
+      <c r="Z64" s="10"/>
       <c r="AC64" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C65" t="s">
         <v>30</v>
       </c>
-      <c r="Z65" s="4"/>
+      <c r="Z65" s="9"/>
       <c r="AC65" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C66" t="s">
         <v>30</v>
       </c>
+      <c r="D66" t="s">
+        <v>34</v>
+      </c>
       <c r="E66">
         <v>100</v>
       </c>
       <c r="F66" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G66">
         <v>37.1</v>
@@ -7686,25 +8804,25 @@
         <v>74.599999999999994</v>
       </c>
       <c r="I66" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="J66">
         <v>36.1</v>
       </c>
       <c r="K66" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="L66">
         <v>78.5</v>
       </c>
       <c r="M66" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="N66">
         <v>83.2</v>
       </c>
       <c r="O66" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="P66">
         <v>109</v>
@@ -7731,45 +8849,48 @@
         <v>2</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y66" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z66" s="5" t="s">
-        <v>56</v>
+        <v>41</v>
+      </c>
+      <c r="Z66" s="10" t="s">
+        <v>403</v>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C67" t="s">
         <v>30</v>
       </c>
-      <c r="Z67" s="5"/>
+      <c r="Z67" s="10"/>
       <c r="AC67" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C68" t="s">
         <v>30</v>
       </c>
+      <c r="D68" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E68">
         <v>100</v>
       </c>
       <c r="F68" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G68">
         <v>40</v>
@@ -7778,25 +8899,25 @@
         <v>12.6</v>
       </c>
       <c r="I68" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="J68">
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="L68">
         <v>21.5</v>
       </c>
       <c r="M68" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N68">
         <v>14.4</v>
       </c>
       <c r="O68" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="P68">
         <v>377</v>
@@ -7823,42 +8944,45 @@
         <v>6</v>
       </c>
       <c r="X68" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z68" s="5" t="s">
         <v>49</v>
       </c>
+      <c r="Z68" s="10" t="s">
+        <v>402</v>
+      </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C69" t="s">
         <v>30</v>
       </c>
-      <c r="Z69" s="4"/>
+      <c r="Z69" s="9"/>
       <c r="AC69" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C70" t="s">
         <v>30</v>
       </c>
+      <c r="D70" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E70">
         <v>100</v>
       </c>
       <c r="F70" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="G70">
         <v>58.7</v>
@@ -7867,25 +8991,25 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="J70">
         <v>61.1</v>
       </c>
       <c r="K70" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="L70">
         <v>0</v>
       </c>
       <c r="M70" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="N70">
         <v>0</v>
       </c>
       <c r="O70" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="P70">
         <v>667</v>
@@ -7912,27 +9036,30 @@
         <v>5</v>
       </c>
       <c r="X70" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z70" s="5" t="s">
         <v>49</v>
       </c>
+      <c r="Z70" s="10" t="s">
+        <v>402</v>
+      </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C71" t="s">
         <v>30</v>
       </c>
+      <c r="D71" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E71">
         <v>100</v>
       </c>
       <c r="F71" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G71">
         <v>40</v>
@@ -7941,25 +9068,25 @@
         <v>32.9</v>
       </c>
       <c r="I71" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J71">
         <v>4.2</v>
       </c>
       <c r="K71" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L71">
         <v>29.2</v>
       </c>
       <c r="M71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N71">
         <v>40.799999999999997</v>
       </c>
       <c r="O71" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="P71">
         <v>289</v>
@@ -7986,27 +9113,30 @@
         <v>1</v>
       </c>
       <c r="X71" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z71" s="5" t="s">
         <v>49</v>
       </c>
+      <c r="Z71" s="10" t="s">
+        <v>402</v>
+      </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C72" t="s">
         <v>30</v>
       </c>
+      <c r="D72" t="s">
+        <v>34</v>
+      </c>
       <c r="E72">
         <v>58.3</v>
       </c>
       <c r="F72" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="G72">
         <v>21.4</v>
@@ -8015,25 +9145,25 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="J72">
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="L72">
         <v>67.7</v>
       </c>
       <c r="M72" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="N72">
         <v>0</v>
       </c>
       <c r="O72" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="P72">
         <v>529</v>
@@ -8059,31 +9189,34 @@
       <c r="W72">
         <v>292</v>
       </c>
-      <c r="X72" s="3" t="s">
+      <c r="X72" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y72" t="s">
         <v>73</v>
       </c>
-      <c r="Y72" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z72" s="5" t="s">
-        <v>75</v>
+      <c r="Z72" s="10" t="s">
+        <v>410</v>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C73" t="s">
         <v>30</v>
       </c>
+      <c r="D73" t="s">
+        <v>34</v>
+      </c>
       <c r="E73">
         <v>100</v>
       </c>
       <c r="F73" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="G73">
         <v>33.1</v>
@@ -8092,25 +9225,25 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="J73">
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="L73">
         <v>0</v>
       </c>
       <c r="M73" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="N73">
         <v>0</v>
       </c>
       <c r="O73" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="P73">
         <v>937</v>
@@ -8136,46 +9269,49 @@
       <c r="W73">
         <v>289</v>
       </c>
-      <c r="X73" s="3" t="s">
+      <c r="X73" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y73" t="s">
         <v>73</v>
       </c>
-      <c r="Y73" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z73" s="5" t="s">
-        <v>276</v>
+      <c r="Z73" s="10" t="s">
+        <v>411</v>
       </c>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C74" t="s">
         <v>30</v>
       </c>
-      <c r="Z74" s="4"/>
+      <c r="Z74" s="9"/>
       <c r="AC74" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C75" t="s">
         <v>30</v>
       </c>
+      <c r="D75" t="s">
+        <v>34</v>
+      </c>
       <c r="E75">
         <v>100</v>
       </c>
       <c r="F75" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="G75">
         <v>40.200000000000003</v>
@@ -8184,25 +9320,25 @@
         <v>33.799999999999997</v>
       </c>
       <c r="I75" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="J75">
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="L75">
         <v>7.7</v>
       </c>
       <c r="M75" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="N75">
         <v>49.3</v>
       </c>
       <c r="O75" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P75">
         <v>286</v>
@@ -8229,57 +9365,60 @@
         <v>1</v>
       </c>
       <c r="X75" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z75" s="5" t="s">
         <v>49</v>
       </c>
+      <c r="Z75" s="10" t="s">
+        <v>402</v>
+      </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C76" t="s">
         <v>30</v>
       </c>
-      <c r="Z76" s="4"/>
+      <c r="Z76" s="9"/>
       <c r="AC76" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C77" t="s">
         <v>30</v>
       </c>
-      <c r="Z77" s="5"/>
+      <c r="Z77" s="10"/>
       <c r="AC77" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C78" t="s">
         <v>30</v>
       </c>
+      <c r="D78" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E78">
         <v>100</v>
       </c>
       <c r="F78" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="G78">
         <v>38.9</v>
@@ -8288,25 +9427,25 @@
         <v>30.5</v>
       </c>
       <c r="I78" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="J78">
         <v>19.399999999999999</v>
       </c>
       <c r="K78" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="L78">
         <v>18.5</v>
       </c>
       <c r="M78" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="N78">
         <v>36</v>
       </c>
       <c r="O78" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="P78">
         <v>301</v>
@@ -8333,27 +9472,30 @@
         <v>4</v>
       </c>
       <c r="X78" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z78" s="5" t="s">
         <v>49</v>
       </c>
+      <c r="Z78" s="10" t="s">
+        <v>402</v>
+      </c>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C79" t="s">
         <v>30</v>
       </c>
+      <c r="D79" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E79">
         <v>100</v>
       </c>
       <c r="F79" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="G79">
         <v>40.5</v>
@@ -8362,25 +9504,25 @@
         <v>26.3</v>
       </c>
       <c r="I79" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="J79">
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="L79">
         <v>24.6</v>
       </c>
       <c r="M79" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="N79">
         <v>35.299999999999997</v>
       </c>
       <c r="O79" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="P79">
         <v>317</v>
@@ -8407,42 +9549,45 @@
         <v>1</v>
       </c>
       <c r="X79" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z79" s="5" t="s">
-        <v>112</v>
+        <v>49</v>
+      </c>
+      <c r="Z79" s="10" t="s">
+        <v>407</v>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="C80" t="s">
         <v>30</v>
       </c>
-      <c r="Z80" s="4"/>
+      <c r="Z80" s="9"/>
       <c r="AC80" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C81" t="s">
         <v>30</v>
       </c>
+      <c r="D81" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E81">
         <v>100</v>
       </c>
       <c r="F81" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="G81">
         <v>40</v>
@@ -8451,25 +9596,25 @@
         <v>10</v>
       </c>
       <c r="I81" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="J81">
         <v>5.6</v>
       </c>
       <c r="K81" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="L81">
         <v>55.4</v>
       </c>
       <c r="M81" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="N81">
         <v>1</v>
       </c>
       <c r="O81" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="P81">
         <v>387</v>
@@ -8496,27 +9641,30 @@
         <v>1</v>
       </c>
       <c r="X81" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z81" s="5" t="s">
-        <v>112</v>
+        <v>49</v>
+      </c>
+      <c r="Z81" s="10" t="s">
+        <v>407</v>
       </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C82" t="s">
         <v>30</v>
       </c>
+      <c r="D82" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E82">
         <v>100</v>
       </c>
       <c r="F82" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G82">
         <v>40</v>
@@ -8525,25 +9673,25 @@
         <v>18.2</v>
       </c>
       <c r="I82" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="J82">
         <v>13.9</v>
       </c>
       <c r="K82" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="L82">
         <v>16.899999999999999</v>
       </c>
       <c r="M82" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="N82">
         <v>19.5</v>
       </c>
       <c r="O82" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P82">
         <v>352</v>
@@ -8570,27 +9718,30 @@
         <v>1</v>
       </c>
       <c r="X82" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z82" s="5" t="s">
         <v>49</v>
       </c>
+      <c r="Z82" s="10" t="s">
+        <v>402</v>
+      </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C83" t="s">
         <v>30</v>
       </c>
+      <c r="D83" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="E83">
         <v>100</v>
       </c>
       <c r="F83" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="G83">
         <v>37.6</v>
@@ -8599,25 +9750,25 @@
         <v>39.9</v>
       </c>
       <c r="I83" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="J83">
         <v>29.2</v>
       </c>
       <c r="K83" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="L83">
         <v>47.7</v>
       </c>
       <c r="M83" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="N83">
         <v>40.799999999999997</v>
       </c>
       <c r="O83" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="P83">
         <v>262</v>
@@ -8643,61 +9794,64 @@
       <c r="W83">
         <v>21</v>
       </c>
-      <c r="X83" s="3" t="s">
+      <c r="X83" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y83" t="s">
         <v>73</v>
       </c>
-      <c r="Y83" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z83" s="5" t="s">
-        <v>93</v>
+      <c r="Z83" s="10" t="s">
+        <v>405</v>
       </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C84" t="s">
         <v>30</v>
       </c>
-      <c r="Z84" s="4"/>
+      <c r="Z84" s="9"/>
       <c r="AC84" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C85" t="s">
         <v>30</v>
       </c>
-      <c r="Z85" s="4"/>
+      <c r="Z85" s="9"/>
       <c r="AC85" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C86" t="s">
-        <v>319</v>
+        <v>312</v>
+      </c>
+      <c r="D86" t="s">
+        <v>313</v>
       </c>
       <c r="E86">
         <v>100</v>
       </c>
       <c r="F86" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G86">
         <v>43.2</v>
@@ -8706,25 +9860,25 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="L86">
         <v>0</v>
       </c>
       <c r="M86" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="N86">
         <v>0</v>
       </c>
       <c r="O86" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="P86">
         <v>1992</v>
@@ -8750,34 +9904,37 @@
       <c r="W86">
         <v>292</v>
       </c>
-      <c r="X86" s="3" t="s">
+      <c r="X86" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y86" t="s">
         <v>73</v>
       </c>
-      <c r="Y86" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z86" t="s">
-        <v>127</v>
+      <c r="Z86" s="9" t="s">
+        <v>408</v>
       </c>
       <c r="AC86" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C87" t="s">
-        <v>327</v>
+        <v>321</v>
+      </c>
+      <c r="D87" t="s">
+        <v>313</v>
       </c>
       <c r="E87">
         <v>100</v>
       </c>
       <c r="F87" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="G87">
         <v>44.1</v>
@@ -8786,25 +9943,25 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="J87">
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="L87">
         <v>0</v>
       </c>
       <c r="M87" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="N87">
         <v>0</v>
       </c>
       <c r="O87" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="P87">
         <v>702</v>
@@ -8831,33 +9988,36 @@
         <v>14</v>
       </c>
       <c r="X87" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y87" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z87" t="s">
-        <v>127</v>
+        <v>41</v>
+      </c>
+      <c r="Z87" s="9" t="s">
+        <v>412</v>
       </c>
       <c r="AC87" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C88" t="s">
-        <v>334</v>
+        <v>328</v>
+      </c>
+      <c r="D88" t="s">
+        <v>313</v>
       </c>
       <c r="E88">
         <v>100</v>
       </c>
       <c r="F88" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="G88">
         <v>45.6</v>
@@ -8866,28 +10026,28 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="J88">
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="L88">
         <v>0</v>
       </c>
       <c r="M88" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="N88">
         <v>0</v>
       </c>
       <c r="O88" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="P88">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="Q88">
         <v>16</v>
@@ -8899,7 +10059,7 @@
         <v>0</v>
       </c>
       <c r="T88">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="U88">
         <v>15</v>
@@ -8911,50 +10071,54 @@
         <v>1</v>
       </c>
       <c r="X88" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y88" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z88" t="s">
-        <v>127</v>
+        <v>41</v>
+      </c>
+      <c r="Z88" s="9" t="s">
+        <v>412</v>
       </c>
       <c r="AC88" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C89" t="s">
-        <v>341</v>
-      </c>
-      <c r="D89" t="s">
-        <v>373</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="Z89" s="9"/>
       <c r="AC89" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C90" t="s">
-        <v>343</v>
+        <v>338</v>
+      </c>
+      <c r="D90" t="s">
+        <v>313</v>
       </c>
       <c r="E90">
         <v>100</v>
       </c>
       <c r="F90" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="G90">
         <v>42.8</v>
@@ -8963,25 +10127,25 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="J90">
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="L90">
         <v>0</v>
       </c>
       <c r="M90" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="N90">
         <v>25.7</v>
       </c>
       <c r="O90" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="P90">
         <v>461</v>
@@ -9008,33 +10172,36 @@
         <v>1</v>
       </c>
       <c r="X90" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y90" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z90" t="s">
         <v>41</v>
       </c>
+      <c r="Z90" s="9" t="s">
+        <v>401</v>
+      </c>
       <c r="AC90" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C91" t="s">
-        <v>350</v>
+        <v>345</v>
+      </c>
+      <c r="D91" t="s">
+        <v>346</v>
       </c>
       <c r="E91">
         <v>100</v>
       </c>
       <c r="F91" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G91">
         <v>48.7</v>
@@ -9043,25 +10210,25 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="J91">
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="L91">
         <v>0</v>
       </c>
       <c r="M91" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="N91">
         <v>0</v>
       </c>
       <c r="O91" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="P91">
         <v>3104</v>
@@ -9087,34 +10254,37 @@
       <c r="W91">
         <v>292</v>
       </c>
-      <c r="X91" s="3" t="s">
+      <c r="X91" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y91" t="s">
         <v>73</v>
       </c>
-      <c r="Y91" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z91" t="s">
-        <v>127</v>
+      <c r="Z91" s="9" t="s">
+        <v>408</v>
       </c>
       <c r="AC91" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C92" t="s">
-        <v>357</v>
+        <v>353</v>
+      </c>
+      <c r="D92" t="s">
+        <v>313</v>
       </c>
       <c r="E92">
         <v>100</v>
       </c>
       <c r="F92" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G92">
         <v>36.700000000000003</v>
@@ -9123,25 +10293,25 @@
         <v>39.9</v>
       </c>
       <c r="I92" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="J92">
         <v>29.2</v>
       </c>
       <c r="K92" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="L92">
         <v>47.7</v>
       </c>
       <c r="M92" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="N92">
         <v>40.799999999999997</v>
       </c>
       <c r="O92" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="P92">
         <v>262</v>
@@ -9167,119 +10337,551 @@
       <c r="W92">
         <v>21</v>
       </c>
-      <c r="X92" s="3" t="s">
+      <c r="X92" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y92" t="s">
         <v>73</v>
       </c>
-      <c r="Y92" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z92" t="s">
-        <v>276</v>
+      <c r="Z92" s="9" t="s">
+        <v>413</v>
       </c>
       <c r="AC92" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>355</v>
+      </c>
+      <c r="C93" t="s">
+        <v>356</v>
+      </c>
+      <c r="D93" t="s">
+        <v>313</v>
+      </c>
+      <c r="E93">
+        <v>100</v>
+      </c>
+      <c r="F93" t="s">
+        <v>357</v>
+      </c>
+      <c r="G93">
+        <v>42</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93" t="s">
+        <v>358</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93" t="s">
         <v>359</v>
       </c>
-      <c r="C93" t="s">
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93" t="s">
         <v>360</v>
       </c>
+      <c r="N93">
+        <v>1.7</v>
+      </c>
+      <c r="O93" t="s">
+        <v>361</v>
+      </c>
+      <c r="P93">
+        <v>482</v>
+      </c>
+      <c r="Q93">
+        <v>15</v>
+      </c>
+      <c r="R93">
+        <v>114</v>
+      </c>
+      <c r="S93">
+        <v>0</v>
+      </c>
+      <c r="T93">
+        <v>81</v>
+      </c>
+      <c r="U93">
+        <v>1</v>
+      </c>
+      <c r="V93">
+        <v>287</v>
+      </c>
+      <c r="W93">
+        <v>14</v>
+      </c>
+      <c r="X93" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z93" s="7" t="s">
+        <v>412</v>
+      </c>
       <c r="AC93" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C94" t="s">
-        <v>362</v>
+        <v>363</v>
+      </c>
+      <c r="D94" t="s">
+        <v>313</v>
+      </c>
+      <c r="E94">
+        <v>100</v>
+      </c>
+      <c r="F94" t="s">
+        <v>364</v>
+      </c>
+      <c r="G94">
+        <v>42.7</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94" t="s">
+        <v>365</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94" t="s">
+        <v>366</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94" t="s">
+        <v>367</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94" t="s">
+        <v>368</v>
+      </c>
+      <c r="P94">
+        <v>511</v>
+      </c>
+      <c r="Q94">
+        <v>15</v>
+      </c>
+      <c r="R94">
+        <v>118</v>
+      </c>
+      <c r="S94">
+        <v>0</v>
+      </c>
+      <c r="T94">
+        <v>90</v>
+      </c>
+      <c r="U94">
+        <v>1</v>
+      </c>
+      <c r="V94">
+        <v>303</v>
+      </c>
+      <c r="W94">
+        <v>14</v>
+      </c>
+      <c r="X94" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z94" s="7" t="s">
+        <v>413</v>
       </c>
       <c r="AC94" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C95" t="s">
-        <v>364</v>
+        <v>370</v>
+      </c>
+      <c r="D95" t="s">
+        <v>313</v>
+      </c>
+      <c r="E95">
+        <v>100</v>
+      </c>
+      <c r="F95" t="s">
+        <v>371</v>
+      </c>
+      <c r="G95">
+        <v>42.4</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95" t="s">
+        <v>372</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95" t="s">
+        <v>373</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95" t="s">
+        <v>374</v>
+      </c>
+      <c r="N95">
+        <v>7.9</v>
+      </c>
+      <c r="O95" t="s">
+        <v>375</v>
+      </c>
+      <c r="P95">
+        <v>480</v>
+      </c>
+      <c r="Q95">
+        <v>1</v>
+      </c>
+      <c r="R95">
+        <v>75</v>
+      </c>
+      <c r="S95">
+        <v>0</v>
+      </c>
+      <c r="T95">
+        <v>136</v>
+      </c>
+      <c r="U95">
+        <v>0</v>
+      </c>
+      <c r="V95">
+        <v>269</v>
+      </c>
+      <c r="W95">
+        <v>1</v>
+      </c>
+      <c r="X95" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z95" s="7" t="s">
+        <v>406</v>
       </c>
       <c r="AC95" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="C96" t="s">
-        <v>366</v>
+        <v>377</v>
+      </c>
+      <c r="D96" t="s">
+        <v>313</v>
+      </c>
+      <c r="E96">
+        <v>100</v>
+      </c>
+      <c r="F96" t="s">
+        <v>378</v>
+      </c>
+      <c r="G96">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="H96">
+        <v>21.9</v>
+      </c>
+      <c r="I96" t="s">
+        <v>379</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96" t="s">
+        <v>380</v>
+      </c>
+      <c r="L96">
+        <v>46.2</v>
+      </c>
+      <c r="M96" t="s">
+        <v>381</v>
+      </c>
+      <c r="N96">
+        <v>22.6</v>
+      </c>
+      <c r="O96" t="s">
+        <v>382</v>
+      </c>
+      <c r="P96">
+        <v>335</v>
+      </c>
+      <c r="Q96">
+        <v>1</v>
+      </c>
+      <c r="R96">
+        <v>74</v>
+      </c>
+      <c r="S96">
+        <v>0</v>
+      </c>
+      <c r="T96">
+        <v>35</v>
+      </c>
+      <c r="U96">
+        <v>0</v>
+      </c>
+      <c r="V96">
+        <v>226</v>
+      </c>
+      <c r="W96">
+        <v>1</v>
+      </c>
+      <c r="X96" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z96" s="7" t="s">
+        <v>405</v>
       </c>
       <c r="AC96" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="C97" t="s">
-        <v>368</v>
+        <v>384</v>
+      </c>
+      <c r="D97" t="s">
+        <v>313</v>
+      </c>
+      <c r="E97">
+        <v>100</v>
+      </c>
+      <c r="F97" t="s">
+        <v>385</v>
+      </c>
+      <c r="G97">
+        <v>42.6</v>
+      </c>
+      <c r="H97">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="I97" t="s">
+        <v>386</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97" t="s">
+        <v>387</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97" t="s">
+        <v>388</v>
+      </c>
+      <c r="N97">
+        <v>33.6</v>
+      </c>
+      <c r="O97" t="s">
+        <v>389</v>
+      </c>
+      <c r="P97">
+        <v>395</v>
+      </c>
+      <c r="Q97">
+        <v>2</v>
+      </c>
+      <c r="R97">
+        <v>118</v>
+      </c>
+      <c r="S97">
+        <v>0</v>
+      </c>
+      <c r="T97">
+        <v>83</v>
+      </c>
+      <c r="U97">
+        <v>1</v>
+      </c>
+      <c r="V97">
+        <v>194</v>
+      </c>
+      <c r="W97">
+        <v>1</v>
+      </c>
+      <c r="X97" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z97" s="7" t="s">
+        <v>412</v>
       </c>
       <c r="AC97" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="C98" t="s">
-        <v>370</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="D98" s="6"/>
+      <c r="Z98" s="7"/>
       <c r="AC98" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:29" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="C99" t="s">
-        <v>372</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="D99" s="6"/>
+      <c r="Z99" s="7"/>
       <c r="AC99" t="s">
-        <v>325</v>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="100" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>394</v>
+      </c>
+      <c r="C100" t="s">
+        <v>395</v>
+      </c>
+      <c r="D100" t="s">
+        <v>346</v>
+      </c>
+      <c r="E100">
+        <v>100</v>
+      </c>
+      <c r="F100" t="s">
+        <v>396</v>
+      </c>
+      <c r="G100">
+        <v>51.6</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100" t="s">
+        <v>397</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100" t="s">
+        <v>398</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100" t="s">
+        <v>399</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100" t="s">
+        <v>400</v>
+      </c>
+      <c r="P100">
+        <v>2399</v>
+      </c>
+      <c r="Q100">
+        <v>231</v>
+      </c>
+      <c r="R100">
+        <v>282</v>
+      </c>
+      <c r="S100">
+        <v>0</v>
+      </c>
+      <c r="T100">
+        <v>793</v>
+      </c>
+      <c r="U100">
+        <v>39</v>
+      </c>
+      <c r="V100">
+        <v>1324</v>
+      </c>
+      <c r="W100">
+        <v>192</v>
+      </c>
+      <c r="X100" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z100" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="AC100" t="s">
+        <v>319</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E99">
+  <conditionalFormatting sqref="E2:E100">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9289,7 +10891,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G99">
+  <conditionalFormatting sqref="G2:G100">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9299,7 +10901,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H99">
+  <conditionalFormatting sqref="H2:H100">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -9309,7 +10911,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I99">
+  <conditionalFormatting sqref="I2:I100">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -9319,7 +10921,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J99">
+  <conditionalFormatting sqref="J2:J100">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -9329,7 +10931,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L99">
+  <conditionalFormatting sqref="L2:L100">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -9339,7 +10941,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N99">
+  <conditionalFormatting sqref="N2:N100">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -9349,7 +10951,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P99">
+  <conditionalFormatting sqref="P2:P100">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9359,7 +10961,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q99">
+  <conditionalFormatting sqref="Q2:Q100">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9369,7 +10971,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R99">
+  <conditionalFormatting sqref="R2:R100">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9379,7 +10981,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S99">
+  <conditionalFormatting sqref="S2:S100">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9389,7 +10991,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T99">
+  <conditionalFormatting sqref="T2:T100">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9399,7 +11001,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U99">
+  <conditionalFormatting sqref="U2:U100">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9409,7 +11011,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V99">
+  <conditionalFormatting sqref="V2:V100">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9419,7 +11021,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W99">
+  <conditionalFormatting sqref="W2:W100">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="num" val="0"/>
